--- a/blocks_real.xlsx
+++ b/blocks_real.xlsx
@@ -15521,23 +15521,6 @@
       <c r="L366"/>
       <c r="M366"/>
     </row>
-    <row r="367">
-      <c r="A367" s="1" t="n">
-        <v>46174</v>
-      </c>
-      <c r="B367"/>
-      <c r="C367"/>
-      <c r="D367"/>
-      <c r="E367"/>
-      <c r="F367"/>
-      <c r="G367"/>
-      <c r="H367"/>
-      <c r="I367"/>
-      <c r="J367"/>
-      <c r="K367"/>
-      <c r="L367"/>
-      <c r="M367"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -32438,20 +32421,6 @@
       <c r="I366"/>
       <c r="J366"/>
     </row>
-    <row r="367">
-      <c r="A367" s="1" t="n">
-        <v>46174</v>
-      </c>
-      <c r="B367"/>
-      <c r="C367"/>
-      <c r="D367"/>
-      <c r="E367"/>
-      <c r="F367"/>
-      <c r="G367"/>
-      <c r="H367"/>
-      <c r="I367"/>
-      <c r="J367"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -39773,16 +39742,6 @@
       <c r="E366"/>
       <c r="F366"/>
     </row>
-    <row r="367">
-      <c r="A367" s="1" t="n">
-        <v>46174</v>
-      </c>
-      <c r="B367"/>
-      <c r="C367"/>
-      <c r="D367"/>
-      <c r="E367"/>
-      <c r="F367"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -46008,15 +45967,6 @@
       <c r="D366"/>
       <c r="E366"/>
     </row>
-    <row r="367">
-      <c r="A367" s="1" t="n">
-        <v>46174</v>
-      </c>
-      <c r="B367"/>
-      <c r="C367"/>
-      <c r="D367"/>
-      <c r="E367"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -56756,19 +56706,6 @@
       </c>
       <c r="I378"/>
     </row>
-    <row r="379">
-      <c r="A379" s="1" t="n">
-        <v>46174</v>
-      </c>
-      <c r="B379"/>
-      <c r="C379"/>
-      <c r="D379"/>
-      <c r="E379"/>
-      <c r="F379"/>
-      <c r="G379"/>
-      <c r="H379"/>
-      <c r="I379"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -56812,14 +56749,14 @@
       </c>
       <c r="B2"/>
       <c r="C2" t="n">
-        <v>36.02323</v>
+        <v>36.08732</v>
       </c>
       <c r="D2"/>
       <c r="E2" t="n">
         <v>47.0480706394842</v>
       </c>
       <c r="F2" t="n">
-        <v>43.63031</v>
+        <v>47.0480706394842</v>
       </c>
       <c r="G2" t="n">
         <v>115.216482052098</v>
@@ -56832,14 +56769,14 @@
       </c>
       <c r="B3"/>
       <c r="C3" t="n">
-        <v>36.22936</v>
+        <v>36.29382</v>
       </c>
       <c r="D3"/>
       <c r="E3" t="n">
         <v>48.0427465497957</v>
       </c>
       <c r="F3" t="n">
-        <v>43.8588</v>
+        <v>48.0427465497957</v>
       </c>
       <c r="G3" t="n">
         <v>118.32197626037</v>
@@ -56852,14 +56789,14 @@
       </c>
       <c r="B4"/>
       <c r="C4" t="n">
-        <v>36.44757</v>
+        <v>36.51241</v>
       </c>
       <c r="D4"/>
       <c r="E4" t="n">
         <v>48.7654206853281</v>
       </c>
       <c r="F4" t="n">
-        <v>43.66354</v>
+        <v>48.7654206853281</v>
       </c>
       <c r="G4" t="n">
         <v>116.911395182597</v>
@@ -56872,14 +56809,14 @@
       </c>
       <c r="B5"/>
       <c r="C5" t="n">
-        <v>36.78331</v>
+        <v>36.84875</v>
       </c>
       <c r="D5"/>
       <c r="E5" t="n">
         <v>48.4339060488553</v>
       </c>
       <c r="F5" t="n">
-        <v>44.53219</v>
+        <v>48.4339060488553</v>
       </c>
       <c r="G5" t="n">
         <v>123.611765453881</v>
@@ -56892,14 +56829,14 @@
       </c>
       <c r="B6"/>
       <c r="C6" t="n">
-        <v>37.03361</v>
+        <v>37.0995</v>
       </c>
       <c r="D6"/>
       <c r="E6" t="n">
         <v>48.3551601391027</v>
       </c>
       <c r="F6" t="n">
-        <v>45.48883</v>
+        <v>48.3551601391027</v>
       </c>
       <c r="G6" t="n">
         <v>123.307642650783</v>
@@ -56912,14 +56849,14 @@
       </c>
       <c r="B7"/>
       <c r="C7" t="n">
-        <v>37.25403</v>
+        <v>37.32031</v>
       </c>
       <c r="D7"/>
       <c r="E7" t="n">
         <v>48.147140237467</v>
       </c>
       <c r="F7" t="n">
-        <v>44.36347</v>
+        <v>48.147140237467</v>
       </c>
       <c r="G7" t="n">
         <v>113.949502316894</v>
@@ -56932,14 +56869,14 @@
       </c>
       <c r="B8"/>
       <c r="C8" t="n">
-        <v>37.449</v>
+        <v>37.51563</v>
       </c>
       <c r="D8"/>
       <c r="E8" t="n">
         <v>48.8099504083692</v>
       </c>
       <c r="F8" t="n">
-        <v>45.74745</v>
+        <v>48.8099504083692</v>
       </c>
       <c r="G8" t="n">
         <v>105.846157193353</v>
@@ -56952,14 +56889,14 @@
       </c>
       <c r="B9"/>
       <c r="C9" t="n">
-        <v>37.61636</v>
+        <v>37.68328</v>
       </c>
       <c r="D9"/>
       <c r="E9" t="n">
         <v>49.9856919106415</v>
       </c>
       <c r="F9" t="n">
-        <v>46.12689</v>
+        <v>49.9856919106415</v>
       </c>
       <c r="G9" t="n">
         <v>111.546547736836</v>
@@ -56972,14 +56909,14 @@
       </c>
       <c r="B10"/>
       <c r="C10" t="n">
-        <v>37.77913</v>
+        <v>37.84634</v>
       </c>
       <c r="D10"/>
       <c r="E10" t="n">
         <v>49.7956557271464</v>
       </c>
       <c r="F10" t="n">
-        <v>45.65196</v>
+        <v>49.7956557271464</v>
       </c>
       <c r="G10" t="n">
         <v>111.913031900924</v>
@@ -56992,14 +56929,14 @@
       </c>
       <c r="B11"/>
       <c r="C11" t="n">
-        <v>37.93102</v>
+        <v>37.99851</v>
       </c>
       <c r="D11"/>
       <c r="E11" t="n">
         <v>50.8025853359446</v>
       </c>
       <c r="F11" t="n">
-        <v>45.96316</v>
+        <v>50.8025853359446</v>
       </c>
       <c r="G11" t="n">
         <v>105.068968039268</v>
@@ -57012,14 +56949,14 @@
       </c>
       <c r="B12"/>
       <c r="C12" t="n">
-        <v>38.0852</v>
+        <v>38.15296</v>
       </c>
       <c r="D12"/>
       <c r="E12" t="n">
         <v>51.2883683385226</v>
       </c>
       <c r="F12" t="n">
-        <v>45.92934</v>
+        <v>51.2883683385226</v>
       </c>
       <c r="G12" t="n">
         <v>108.811583895914</v>
@@ -57032,14 +56969,14 @@
       </c>
       <c r="B13"/>
       <c r="C13" t="n">
-        <v>38.245</v>
+        <v>38.31304</v>
       </c>
       <c r="D13"/>
       <c r="E13" t="n">
         <v>54.9932028979248</v>
       </c>
       <c r="F13" t="n">
-        <v>46.91861</v>
+        <v>54.9932028979248</v>
       </c>
       <c r="G13" t="n">
         <v>116.637323779457</v>
@@ -57052,14 +56989,14 @@
       </c>
       <c r="B14"/>
       <c r="C14" t="n">
-        <v>38.36861</v>
+        <v>38.43687</v>
       </c>
       <c r="D14"/>
       <c r="E14" t="n">
         <v>52.0648049915258</v>
       </c>
       <c r="F14" t="n">
-        <v>46.62268</v>
+        <v>52.0648049915258</v>
       </c>
       <c r="G14" t="n">
         <v>114.969270174948</v>
@@ -57072,7 +57009,7 @@
       </c>
       <c r="B15"/>
       <c r="C15" t="n">
-        <v>38.37893</v>
+        <v>38.44721</v>
       </c>
       <c r="D15" t="n">
         <v>22.66118</v>
@@ -57081,7 +57018,7 @@
         <v>51.9493552171652</v>
       </c>
       <c r="F15" t="n">
-        <v>46.82253</v>
+        <v>51.9493552171652</v>
       </c>
       <c r="G15" t="n">
         <v>114.76085528429</v>
@@ -57094,7 +57031,7 @@
       </c>
       <c r="B16"/>
       <c r="C16" t="n">
-        <v>38.32984</v>
+        <v>38.39803</v>
       </c>
       <c r="D16" t="n">
         <v>22.78054</v>
@@ -57103,7 +57040,7 @@
         <v>52.2386593510394</v>
       </c>
       <c r="F16" t="n">
-        <v>47.3226</v>
+        <v>52.2386593510394</v>
       </c>
       <c r="G16" t="n">
         <v>126.391821512333</v>
@@ -57116,7 +57053,7 @@
       </c>
       <c r="B17"/>
       <c r="C17" t="n">
-        <v>38.27404</v>
+        <v>38.34214</v>
       </c>
       <c r="D17" t="n">
         <v>22.83932</v>
@@ -57125,7 +57062,7 @@
         <v>52.3809505981755</v>
       </c>
       <c r="F17" t="n">
-        <v>47.3257</v>
+        <v>52.3809505981755</v>
       </c>
       <c r="G17" t="n">
         <v>139.858827475454</v>
@@ -57138,7 +57075,7 @@
       </c>
       <c r="B18"/>
       <c r="C18" t="n">
-        <v>38.25835</v>
+        <v>38.32642</v>
       </c>
       <c r="D18" t="n">
         <v>23.26217</v>
@@ -57147,7 +57084,7 @@
         <v>53.4134502698923</v>
       </c>
       <c r="F18" t="n">
-        <v>46.76416</v>
+        <v>53.4134502698923</v>
       </c>
       <c r="G18" t="n">
         <v>127.312352325635</v>
@@ -57160,7 +57097,7 @@
       </c>
       <c r="B19"/>
       <c r="C19" t="n">
-        <v>38.29493</v>
+        <v>38.36306</v>
       </c>
       <c r="D19" t="n">
         <v>22.98347</v>
@@ -57169,7 +57106,7 @@
         <v>52.743007476286</v>
       </c>
       <c r="F19" t="n">
-        <v>47.68579</v>
+        <v>52.743007476286</v>
       </c>
       <c r="G19" t="n">
         <v>122.065532900317</v>
@@ -57182,7 +57119,7 @@
       </c>
       <c r="B20"/>
       <c r="C20" t="n">
-        <v>38.37307</v>
+        <v>38.44134</v>
       </c>
       <c r="D20" t="n">
         <v>23.04468</v>
@@ -57191,7 +57128,7 @@
         <v>52.8913193800576</v>
       </c>
       <c r="F20" t="n">
-        <v>46.40966</v>
+        <v>52.8913193800576</v>
       </c>
       <c r="G20" t="n">
         <v>123.986450572393</v>
@@ -57204,7 +57141,7 @@
       </c>
       <c r="B21"/>
       <c r="C21" t="n">
-        <v>38.40751</v>
+        <v>38.47584</v>
       </c>
       <c r="D21" t="n">
         <v>22.60813</v>
@@ -57213,7 +57150,7 @@
         <v>51.8454246424202</v>
       </c>
       <c r="F21" t="n">
-        <v>47.45461</v>
+        <v>51.8454246424202</v>
       </c>
       <c r="G21" t="n">
         <v>125.694690338434</v>
@@ -57226,7 +57163,7 @@
       </c>
       <c r="B22"/>
       <c r="C22" t="n">
-        <v>38.40043</v>
+        <v>38.46875</v>
       </c>
       <c r="D22" t="n">
         <v>23.05225</v>
@@ -57235,7 +57172,7 @@
         <v>52.930398491864</v>
       </c>
       <c r="F22" t="n">
-        <v>48.11083</v>
+        <v>52.930398491864</v>
       </c>
       <c r="G22" t="n">
         <v>137.878248754946</v>
@@ -57248,7 +57185,7 @@
       </c>
       <c r="B23"/>
       <c r="C23" t="n">
-        <v>38.36188</v>
+        <v>38.43012</v>
       </c>
       <c r="D23" t="n">
         <v>22.96747</v>
@@ -57257,7 +57194,7 @@
         <v>52.72554752562</v>
       </c>
       <c r="F23" t="n">
-        <v>47.29437</v>
+        <v>52.72554752562</v>
       </c>
       <c r="G23" t="n">
         <v>144.60379645378</v>
@@ -57270,7 +57207,7 @@
       </c>
       <c r="B24"/>
       <c r="C24" t="n">
-        <v>38.3806</v>
+        <v>38.44888</v>
       </c>
       <c r="D24" t="n">
         <v>22.72123</v>
@@ -57279,7 +57216,7 @@
         <v>52.1329310311909</v>
       </c>
       <c r="F24" t="n">
-        <v>46.9677</v>
+        <v>52.1329310311909</v>
       </c>
       <c r="G24" t="n">
         <v>137.714101756615</v>
@@ -57292,7 +57229,7 @@
       </c>
       <c r="B25"/>
       <c r="C25" t="n">
-        <v>38.53757</v>
+        <v>38.60613</v>
       </c>
       <c r="D25" t="n">
         <v>22.52757</v>
@@ -57301,7 +57238,7 @@
         <v>51.6665542344544</v>
       </c>
       <c r="F25" t="n">
-        <v>47.06549</v>
+        <v>51.6665542344544</v>
       </c>
       <c r="G25" t="n">
         <v>146.877294818741</v>
@@ -57314,7 +57251,7 @@
       </c>
       <c r="B26"/>
       <c r="C26" t="n">
-        <v>38.63802</v>
+        <v>38.70676</v>
       </c>
       <c r="D26" t="n">
         <v>23.42988</v>
@@ -57323,7 +57260,7 @@
         <v>53.8950996961951</v>
       </c>
       <c r="F26" t="n">
-        <v>47.99719</v>
+        <v>53.8950996961951</v>
       </c>
       <c r="G26" t="n">
         <v>145.688095718119</v>
@@ -57336,7 +57273,7 @@
       </c>
       <c r="B27"/>
       <c r="C27" t="n">
-        <v>38.6707</v>
+        <v>38.7395</v>
       </c>
       <c r="D27" t="n">
         <v>23.40455</v>
@@ -57345,7 +57282,7 @@
         <v>53.8337033374164</v>
       </c>
       <c r="F27" t="n">
-        <v>47.52265</v>
+        <v>53.8337033374164</v>
       </c>
       <c r="G27" t="n">
         <v>129.398790476015</v>
@@ -57358,7 +57295,7 @@
       </c>
       <c r="B28"/>
       <c r="C28" t="n">
-        <v>38.733</v>
+        <v>38.80191</v>
       </c>
       <c r="D28" t="n">
         <v>23.57658</v>
@@ -57367,7 +57304,7 @@
         <v>54.2524995642211</v>
       </c>
       <c r="F28" t="n">
-        <v>48.52799</v>
+        <v>54.2524995642211</v>
       </c>
       <c r="G28" t="n">
         <v>122.250192685306</v>
@@ -57380,7 +57317,7 @@
       </c>
       <c r="B29"/>
       <c r="C29" t="n">
-        <v>38.80589</v>
+        <v>38.87493</v>
       </c>
       <c r="D29" t="n">
         <v>23.40508</v>
@@ -57389,7 +57326,7 @@
         <v>53.8380133936198</v>
       </c>
       <c r="F29" t="n">
-        <v>48.46553</v>
+        <v>53.8380133936198</v>
       </c>
       <c r="G29" t="n">
         <v>114.785160332972</v>
@@ -57402,7 +57339,7 @@
       </c>
       <c r="B30"/>
       <c r="C30" t="n">
-        <v>38.86964</v>
+        <v>38.93879</v>
       </c>
       <c r="D30" t="n">
         <v>23.85497</v>
@@ -57411,7 +57348,7 @@
         <v>54.9402305434009</v>
       </c>
       <c r="F30" t="n">
-        <v>48.88788</v>
+        <v>54.9402305434009</v>
       </c>
       <c r="G30" t="n">
         <v>121.077268347774</v>
@@ -57424,7 +57361,7 @@
       </c>
       <c r="B31"/>
       <c r="C31" t="n">
-        <v>38.92734</v>
+        <v>38.9966</v>
       </c>
       <c r="D31" t="n">
         <v>24.30336</v>
@@ -57433,7 +57370,7 @@
         <v>56.0398660522361</v>
       </c>
       <c r="F31" t="n">
-        <v>48.77424</v>
+        <v>56.0398660522361</v>
       </c>
       <c r="G31" t="n">
         <v>112.584313489258</v>
@@ -57446,7 +57383,7 @@
       </c>
       <c r="B32"/>
       <c r="C32" t="n">
-        <v>39.02091</v>
+        <v>39.09033</v>
       </c>
       <c r="D32" t="n">
         <v>24.07149</v>
@@ -57455,7 +57392,7 @@
         <v>55.4789823172276</v>
       </c>
       <c r="F32" t="n">
-        <v>48.79898</v>
+        <v>55.4789823172276</v>
       </c>
       <c r="G32" t="n">
         <v>116.806476142525</v>
@@ -57468,7 +57405,7 @@
       </c>
       <c r="B33"/>
       <c r="C33" t="n">
-        <v>39.08814</v>
+        <v>39.15768</v>
       </c>
       <c r="D33" t="n">
         <v>23.4835</v>
@@ -57477,7 +57414,7 @@
         <v>54.0684531225462</v>
       </c>
       <c r="F33" t="n">
-        <v>48.08708</v>
+        <v>54.0684531225462</v>
       </c>
       <c r="G33" t="n">
         <v>117.592873277475</v>
@@ -57490,7 +57427,7 @@
       </c>
       <c r="B34"/>
       <c r="C34" t="n">
-        <v>39.21112</v>
+        <v>39.28088</v>
       </c>
       <c r="D34" t="n">
         <v>23.72743</v>
@@ -57499,7 +57436,7 @@
         <v>54.663828245601</v>
       </c>
       <c r="F34" t="n">
-        <v>48.41684</v>
+        <v>54.663828245601</v>
       </c>
       <c r="G34" t="n">
         <v>116.055821639696</v>
@@ -57512,7 +57449,7 @@
       </c>
       <c r="B35"/>
       <c r="C35" t="n">
-        <v>39.29142</v>
+        <v>39.36132</v>
       </c>
       <c r="D35" t="n">
         <v>23.88441</v>
@@ -57521,7 +57458,7 @@
         <v>55.0464666147897</v>
       </c>
       <c r="F35" t="n">
-        <v>48.81774</v>
+        <v>55.0464666147897</v>
       </c>
       <c r="G35" t="n">
         <v>124.001814024335</v>
@@ -57534,7 +57471,7 @@
       </c>
       <c r="B36"/>
       <c r="C36" t="n">
-        <v>39.36352</v>
+        <v>39.43356</v>
       </c>
       <c r="D36" t="n">
         <v>24.28252</v>
@@ -57543,7 +57480,7 @@
         <v>56.0223773483257</v>
       </c>
       <c r="F36" t="n">
-        <v>49.79384</v>
+        <v>56.0223773483257</v>
       </c>
       <c r="G36" t="n">
         <v>118.116443336019</v>
@@ -57556,7 +57493,7 @@
       </c>
       <c r="B37"/>
       <c r="C37" t="n">
-        <v>39.48621</v>
+        <v>39.55646</v>
       </c>
       <c r="D37" t="n">
         <v>24.08909</v>
@@ -57565,7 +57502,7 @@
         <v>55.5538432023376</v>
       </c>
       <c r="F37" t="n">
-        <v>48.16092</v>
+        <v>55.5538432023376</v>
       </c>
       <c r="G37" t="n">
         <v>107.612117139915</v>
@@ -57578,7 +57515,7 @@
       </c>
       <c r="B38"/>
       <c r="C38" t="n">
-        <v>39.66579</v>
+        <v>39.73635</v>
       </c>
       <c r="D38" t="n">
         <v>24.32548</v>
@@ -57587,7 +57524,7 @@
         <v>56.1315846366565</v>
       </c>
       <c r="F38" t="n">
-        <v>47.93862</v>
+        <v>56.1315846366565</v>
       </c>
       <c r="G38" t="n">
         <v>99.0343748561887</v>
@@ -57600,7 +57537,7 @@
       </c>
       <c r="B39"/>
       <c r="C39" t="n">
-        <v>39.77705</v>
+        <v>39.84782</v>
       </c>
       <c r="D39" t="n">
         <v>24.89642</v>
@@ -57609,7 +57546,7 @@
         <v>57.5379352972906</v>
       </c>
       <c r="F39" t="n">
-        <v>50.93118</v>
+        <v>57.5379352972906</v>
       </c>
       <c r="G39" t="n">
         <v>95.6194936322363</v>
@@ -57622,7 +57559,7 @@
       </c>
       <c r="B40"/>
       <c r="C40" t="n">
-        <v>39.91931</v>
+        <v>39.99033</v>
       </c>
       <c r="D40" t="n">
         <v>24.58041</v>
@@ -57631,7 +57568,7 @@
         <v>56.7730784549298</v>
       </c>
       <c r="F40" t="n">
-        <v>50.11432</v>
+        <v>56.7730784549298</v>
       </c>
       <c r="G40" t="n">
         <v>89.9700502542306</v>
@@ -57644,7 +57581,7 @@
       </c>
       <c r="B41"/>
       <c r="C41" t="n">
-        <v>39.98907</v>
+        <v>40.06022</v>
       </c>
       <c r="D41" t="n">
         <v>24.88709</v>
@@ -57653,7 +57590,7 @@
         <v>57.5248181020272</v>
       </c>
       <c r="F41" t="n">
-        <v>49.16506</v>
+        <v>57.5248181020272</v>
       </c>
       <c r="G41" t="n">
         <v>93.1396009054267</v>
@@ -57666,7 +57603,7 @@
       </c>
       <c r="B42"/>
       <c r="C42" t="n">
-        <v>40.03981</v>
+        <v>40.11104</v>
       </c>
       <c r="D42" t="n">
         <v>24.6631</v>
@@ -57675,7 +57612,7 @@
         <v>56.9815238088347</v>
       </c>
       <c r="F42" t="n">
-        <v>49.32859</v>
+        <v>56.9815238088347</v>
       </c>
       <c r="G42" t="n">
         <v>89.1606210561612</v>
@@ -57688,7 +57625,7 @@
       </c>
       <c r="B43"/>
       <c r="C43" t="n">
-        <v>40.15182</v>
+        <v>40.22326</v>
       </c>
       <c r="D43" t="n">
         <v>24.45016</v>
@@ -57697,7 +57634,7 @@
         <v>56.4651819248757</v>
       </c>
       <c r="F43" t="n">
-        <v>50.90394</v>
+        <v>56.4651819248757</v>
       </c>
       <c r="G43" t="n">
         <v>81.6910873770982</v>
@@ -57710,7 +57647,7 @@
       </c>
       <c r="B44"/>
       <c r="C44" t="n">
-        <v>40.23759</v>
+        <v>40.30918</v>
       </c>
       <c r="D44" t="n">
         <v>24.62713</v>
@@ -57719,7 +57656,7 @@
         <v>56.8977386246237</v>
       </c>
       <c r="F44" t="n">
-        <v>49.85281</v>
+        <v>56.8977386246237</v>
       </c>
       <c r="G44" t="n">
         <v>84.3870202460052</v>
@@ -57732,7 +57669,7 @@
       </c>
       <c r="B45"/>
       <c r="C45" t="n">
-        <v>40.35657</v>
+        <v>40.42837</v>
       </c>
       <c r="D45" t="n">
         <v>25.11562</v>
@@ -57741,7 +57678,7 @@
         <v>58.1001548250512</v>
       </c>
       <c r="F45" t="n">
-        <v>50.04997</v>
+        <v>58.1001548250512</v>
       </c>
       <c r="G45" t="n">
         <v>80.8420468856442</v>
@@ -57754,7 +57691,7 @@
       </c>
       <c r="B46"/>
       <c r="C46" t="n">
-        <v>40.40232</v>
+        <v>40.4742</v>
       </c>
       <c r="D46" t="n">
         <v>24.89828</v>
@@ -57763,7 +57700,7 @@
         <v>57.5724679727907</v>
       </c>
       <c r="F46" t="n">
-        <v>50.24851</v>
+        <v>57.5724679727907</v>
       </c>
       <c r="G46" t="n">
         <v>92.2493322163269</v>
@@ -57776,7 +57713,7 @@
       </c>
       <c r="B47"/>
       <c r="C47" t="n">
-        <v>40.58204</v>
+        <v>40.65424</v>
       </c>
       <c r="D47" t="n">
         <v>25.49384</v>
@@ -57785,7 +57722,7 @@
         <v>59.0428508029851</v>
       </c>
       <c r="F47" t="n">
-        <v>49.92605</v>
+        <v>59.0428508029851</v>
       </c>
       <c r="G47" t="n">
         <v>93.9745806637975</v>
@@ -57798,7 +57735,7 @@
       </c>
       <c r="B48"/>
       <c r="C48" t="n">
-        <v>40.63844</v>
+        <v>40.71074</v>
       </c>
       <c r="D48" t="n">
         <v>25.24888</v>
@@ -57807,7 +57744,7 @@
         <v>58.4477449913473</v>
       </c>
       <c r="F48" t="n">
-        <v>50.08649</v>
+        <v>58.4477449913473</v>
       </c>
       <c r="G48" t="n">
         <v>84.0700606744408</v>
@@ -57820,7 +57757,7 @@
       </c>
       <c r="B49"/>
       <c r="C49" t="n">
-        <v>40.69361</v>
+        <v>40.76601</v>
       </c>
       <c r="D49" t="n">
         <v>25.12299</v>
@@ -57829,7 +57766,7 @@
         <v>58.1412928258319</v>
       </c>
       <c r="F49" t="n">
-        <v>49.76272</v>
+        <v>58.1412928258319</v>
       </c>
       <c r="G49" t="n">
         <v>72.4598168171145</v>
@@ -57842,7 +57779,7 @@
       </c>
       <c r="B50"/>
       <c r="C50" t="n">
-        <v>40.68948</v>
+        <v>40.76187</v>
       </c>
       <c r="D50" t="n">
         <v>24.75473</v>
@@ -57851,7 +57788,7 @@
         <v>57.2496749410041</v>
       </c>
       <c r="F50" t="n">
-        <v>48.65421</v>
+        <v>57.2496749410041</v>
       </c>
       <c r="G50" t="n">
         <v>78.4290580830351</v>
@@ -57864,7 +57801,7 @@
       </c>
       <c r="B51"/>
       <c r="C51" t="n">
-        <v>40.90153</v>
+        <v>40.9743</v>
       </c>
       <c r="D51" t="n">
         <v>25.45928</v>
@@ -57873,7 +57810,7 @@
         <v>58.9935998610504</v>
       </c>
       <c r="F51" t="n">
-        <v>49.47975</v>
+        <v>58.9935998610504</v>
       </c>
       <c r="G51" t="n">
         <v>75.6427530958432</v>
@@ -57886,7 +57823,7 @@
       </c>
       <c r="B52"/>
       <c r="C52" t="n">
-        <v>41.09179</v>
+        <v>41.16489</v>
       </c>
       <c r="D52" t="n">
         <v>25.78229</v>
@@ -57895,7 +57832,7 @@
         <v>59.7880207834673</v>
       </c>
       <c r="F52" t="n">
-        <v>48.18467</v>
+        <v>59.7880207834673</v>
       </c>
       <c r="G52" t="n">
         <v>91.7495849726348</v>
@@ -57908,7 +57845,7 @@
       </c>
       <c r="B53"/>
       <c r="C53" t="n">
-        <v>41.22239</v>
+        <v>41.29573</v>
       </c>
       <c r="D53" t="n">
         <v>25.48537</v>
@@ -57917,7 +57854,7 @@
         <v>59.0664547503893</v>
       </c>
       <c r="F53" t="n">
-        <v>49.09352</v>
+        <v>59.0664547503893</v>
       </c>
       <c r="G53" t="n">
         <v>108.722526437984</v>
@@ -57930,7 +57867,7 @@
       </c>
       <c r="B54"/>
       <c r="C54" t="n">
-        <v>41.31297</v>
+        <v>41.38647</v>
       </c>
       <c r="D54" t="n">
         <v>25.48295</v>
@@ -57939,7 +57876,7 @@
         <v>59.0605464664233</v>
       </c>
       <c r="F54" t="n">
-        <v>49.08853</v>
+        <v>59.0605464664233</v>
       </c>
       <c r="G54" t="n">
         <v>112.284310162226</v>
@@ -57952,7 +57889,7 @@
       </c>
       <c r="B55"/>
       <c r="C55" t="n">
-        <v>41.45271</v>
+        <v>41.52646</v>
       </c>
       <c r="D55" t="n">
         <v>25.92997</v>
@@ -57961,7 +57898,7 @@
         <v>60.1630174339458</v>
       </c>
       <c r="F55" t="n">
-        <v>49.75443</v>
+        <v>60.1630174339458</v>
       </c>
       <c r="G55" t="n">
         <v>112.475559432759</v>
@@ -57974,7 +57911,7 @@
       </c>
       <c r="B56"/>
       <c r="C56" t="n">
-        <v>41.68236</v>
+        <v>41.75652</v>
       </c>
       <c r="D56" t="n">
         <v>26.16485</v>
@@ -57983,7 +57920,7 @@
         <v>60.7403466030283</v>
       </c>
       <c r="F56" t="n">
-        <v>50.57748</v>
+        <v>60.7403466030283</v>
       </c>
       <c r="G56" t="n">
         <v>126.024221475454</v>
@@ -57996,7 +57933,7 @@
       </c>
       <c r="B57"/>
       <c r="C57" t="n">
-        <v>42.03085</v>
+        <v>42.10563</v>
       </c>
       <c r="D57" t="n">
         <v>26.89176</v>
@@ -58005,7 +57942,7 @@
         <v>62.5457930208471</v>
       </c>
       <c r="F57" t="n">
-        <v>50.93198</v>
+        <v>62.5457930208471</v>
       </c>
       <c r="G57" t="n">
         <v>136.194659089154</v>
@@ -58018,7 +57955,7 @@
       </c>
       <c r="B58"/>
       <c r="C58" t="n">
-        <v>42.48045</v>
+        <v>42.55602</v>
       </c>
       <c r="D58" t="n">
         <v>28.58989</v>
@@ -58027,7 +57964,7 @@
         <v>66.8516188995698</v>
       </c>
       <c r="F58" t="n">
-        <v>51.89052</v>
+        <v>66.8516188995698</v>
       </c>
       <c r="G58" t="n">
         <v>153.184707292391</v>
@@ -58040,7 +57977,7 @@
       </c>
       <c r="B59"/>
       <c r="C59" t="n">
-        <v>42.59836</v>
+        <v>42.67414</v>
       </c>
       <c r="D59" t="n">
         <v>27.5481</v>
@@ -58049,7 +57986,7 @@
         <v>64.3320141084303</v>
       </c>
       <c r="F59" t="n">
-        <v>51.73318</v>
+        <v>64.3320141084303</v>
       </c>
       <c r="G59" t="n">
         <v>145.705423416739</v>
@@ -58062,7 +57999,7 @@
       </c>
       <c r="B60"/>
       <c r="C60" t="n">
-        <v>42.83932</v>
+        <v>42.91554</v>
       </c>
       <c r="D60" t="n">
         <v>27.60331</v>
@@ -58071,7 +58008,7 @@
         <v>64.4680734742902</v>
       </c>
       <c r="F60" t="n">
-        <v>52.64203</v>
+        <v>64.4680734742902</v>
       </c>
       <c r="G60" t="n">
         <v>159.419006112617</v>
@@ -58084,7 +58021,7 @@
       </c>
       <c r="B61"/>
       <c r="C61" t="n">
-        <v>42.94221</v>
+        <v>43.01861</v>
       </c>
       <c r="D61" t="n">
         <v>27.84053</v>
@@ -58093,7 +58030,7 @@
         <v>65.0548739214473</v>
       </c>
       <c r="F61" t="n">
-        <v>53.40421</v>
+        <v>65.0548739214473</v>
       </c>
       <c r="G61" t="n">
         <v>165.117093222416</v>
@@ -58106,7 +58043,7 @@
       </c>
       <c r="B62"/>
       <c r="C62" t="n">
-        <v>42.95916</v>
+        <v>43.03559</v>
       </c>
       <c r="D62" t="n">
         <v>27.58366</v>
@@ -58115,13 +58052,13 @@
         <v>64.4251111367324</v>
       </c>
       <c r="F62" t="n">
-        <v>51.18501</v>
+        <v>64.4251111367324</v>
       </c>
       <c r="G62" t="n">
         <v>169.614593332276</v>
       </c>
       <c r="H62" t="n">
-        <v>99.521</v>
+        <v>99.509</v>
       </c>
     </row>
     <row r="63">
@@ -58130,7 +58067,7 @@
       </c>
       <c r="B63"/>
       <c r="C63" t="n">
-        <v>43.22936</v>
+        <v>43.30627</v>
       </c>
       <c r="D63" t="n">
         <v>27.56531</v>
@@ -58139,13 +58076,13 @@
         <v>64.3799265012473</v>
       </c>
       <c r="F63" t="n">
-        <v>53.87256</v>
+        <v>64.3799265012473</v>
       </c>
       <c r="G63" t="n">
         <v>181.293315730133</v>
       </c>
       <c r="H63" t="n">
-        <v>101.35716245</v>
+        <v>101.3300147</v>
       </c>
     </row>
     <row r="64">
@@ -58154,7 +58091,7 @@
       </c>
       <c r="B64"/>
       <c r="C64" t="n">
-        <v>43.68789</v>
+        <v>43.76562</v>
       </c>
       <c r="D64" t="n">
         <v>28.08266</v>
@@ -58163,13 +58100,13 @@
         <v>65.6665325493564</v>
       </c>
       <c r="F64" t="n">
-        <v>54.94863</v>
+        <v>65.6665325493564</v>
       </c>
       <c r="G64" t="n">
         <v>182.502327484173</v>
       </c>
       <c r="H64" t="n">
-        <v>103.136994222622</v>
+        <v>103.20461997195</v>
       </c>
     </row>
     <row r="65">
@@ -58178,7 +58115,7 @@
       </c>
       <c r="B65"/>
       <c r="C65" t="n">
-        <v>44.13621</v>
+        <v>44.21473</v>
       </c>
       <c r="D65" t="n">
         <v>28.78972</v>
@@ -58187,13 +58124,13 @@
         <v>67.4330222379973</v>
       </c>
       <c r="F65" t="n">
-        <v>55.48792</v>
+        <v>67.4330222379973</v>
       </c>
       <c r="G65" t="n">
         <v>157.977035361986</v>
       </c>
       <c r="H65" t="n">
-        <v>103.857921812238</v>
+        <v>103.896090925762</v>
       </c>
     </row>
     <row r="66">
@@ -58202,7 +58139,7 @@
       </c>
       <c r="B66"/>
       <c r="C66" t="n">
-        <v>44.48186</v>
+        <v>44.561</v>
       </c>
       <c r="D66" t="n">
         <v>28.88911</v>
@@ -58211,13 +58148,13 @@
         <v>67.6788956988001</v>
       </c>
       <c r="F66" t="n">
-        <v>56.75786</v>
+        <v>67.6788956988001</v>
       </c>
       <c r="G66" t="n">
         <v>179.885045607189</v>
       </c>
       <c r="H66" t="n">
-        <v>104.97958736781</v>
+        <v>104.96310377957</v>
       </c>
     </row>
     <row r="67">
@@ -58226,7 +58163,7 @@
       </c>
       <c r="B67"/>
       <c r="C67" t="n">
-        <v>44.62287</v>
+        <v>44.70226</v>
       </c>
       <c r="D67" t="n">
         <v>29.03227</v>
@@ -58235,13 +58172,13 @@
         <v>68.0334355619786</v>
       </c>
       <c r="F67" t="n">
-        <v>56.58775</v>
+        <v>68.0334355619786</v>
       </c>
       <c r="G67" t="n">
         <v>196.43783233916</v>
       </c>
       <c r="H67" t="n">
-        <v>106.199450173024</v>
+        <v>106.20586692832</v>
       </c>
     </row>
     <row r="68">
@@ -58250,7 +58187,7 @@
       </c>
       <c r="B68"/>
       <c r="C68" t="n">
-        <v>44.74617</v>
+        <v>44.82578</v>
       </c>
       <c r="D68" t="n">
         <v>29.44985</v>
@@ -58259,13 +58196,13 @@
         <v>69.0729803008243</v>
       </c>
       <c r="F68" t="n">
-        <v>57.20745</v>
+        <v>69.0729803008243</v>
       </c>
       <c r="G68" t="n">
         <v>182.029307743188</v>
       </c>
       <c r="H68" t="n">
-        <v>107.445169723554</v>
+        <v>107.489895859483</v>
       </c>
     </row>
     <row r="69">
@@ -58274,7 +58211,7 @@
       </c>
       <c r="B69"/>
       <c r="C69" t="n">
-        <v>44.86411</v>
+        <v>44.94393</v>
       </c>
       <c r="D69" t="n">
         <v>29.71028</v>
@@ -58283,13 +58220,13 @@
         <v>69.7200013572934</v>
       </c>
       <c r="F69" t="n">
-        <v>57.83334</v>
+        <v>69.7200013572934</v>
       </c>
       <c r="G69" t="n">
         <v>190.757887391991</v>
       </c>
       <c r="H69" t="n">
-        <v>108.549706068312</v>
+        <v>108.551896030575</v>
       </c>
     </row>
     <row r="70">
@@ -58298,7 +58235,7 @@
       </c>
       <c r="B70"/>
       <c r="C70" t="n">
-        <v>45.11744</v>
+        <v>45.1977</v>
       </c>
       <c r="D70" t="n">
         <v>30.11359</v>
@@ -58307,13 +58244,13 @@
         <v>70.7249965923022</v>
       </c>
       <c r="F70" t="n">
-        <v>56.35887</v>
+        <v>70.7249965923022</v>
       </c>
       <c r="G70" t="n">
         <v>207.428219170707</v>
       </c>
       <c r="H70" t="n">
-        <v>108.94374150134</v>
+        <v>108.92531455292</v>
       </c>
     </row>
     <row r="71">
@@ -58322,7 +58259,7 @@
       </c>
       <c r="B71"/>
       <c r="C71" t="n">
-        <v>45.30247</v>
+        <v>45.38307</v>
       </c>
       <c r="D71" t="n">
         <v>28.83503</v>
@@ -58331,13 +58268,13 @@
         <v>67.6288849284461</v>
       </c>
       <c r="F71" t="n">
-        <v>57.36519</v>
+        <v>67.6288849284461</v>
       </c>
       <c r="G71" t="n">
         <v>204.869973108076</v>
       </c>
       <c r="H71" t="n">
-        <v>109.32395515918</v>
+        <v>109.319624191602</v>
       </c>
     </row>
     <row r="72">
@@ -58346,7 +58283,7 @@
       </c>
       <c r="B72"/>
       <c r="C72" t="n">
-        <v>45.50074</v>
+        <v>45.58169</v>
       </c>
       <c r="D72" t="n">
         <v>29.2697</v>
@@ -58355,13 +58292,13 @@
         <v>68.7123108900657</v>
       </c>
       <c r="F72" t="n">
-        <v>56.26497</v>
+        <v>68.7123108900657</v>
       </c>
       <c r="G72" t="n">
         <v>213.197289826926</v>
       </c>
       <c r="H72" t="n">
-        <v>108.381582665708</v>
+        <v>108.408991722086</v>
       </c>
     </row>
     <row r="73">
@@ -58370,7 +58307,7 @@
       </c>
       <c r="B73"/>
       <c r="C73" t="n">
-        <v>45.59164</v>
+        <v>45.67275</v>
       </c>
       <c r="D73" t="n">
         <v>29.35063</v>
@@ -58379,13 +58316,13 @@
         <v>68.9129221019337</v>
       </c>
       <c r="F73" t="n">
-        <v>56.68871</v>
+        <v>68.9129221019337</v>
       </c>
       <c r="G73" t="n">
         <v>175.091643836291</v>
       </c>
       <c r="H73" t="n">
-        <v>107.995744231418</v>
+        <v>108.00137391321</v>
       </c>
     </row>
     <row r="74">
@@ -58394,7 +58331,7 @@
       </c>
       <c r="B74"/>
       <c r="C74" t="n">
-        <v>45.65695</v>
+        <v>45.73818</v>
       </c>
       <c r="D74" t="n">
         <v>30.28833</v>
@@ -58403,13 +58340,13 @@
         <v>71.2736632739779</v>
       </c>
       <c r="F74" t="n">
-        <v>56.49496</v>
+        <v>71.2736632739779</v>
       </c>
       <c r="G74" t="n">
         <v>184.956465203277</v>
       </c>
       <c r="H74" t="n">
-        <v>108.513043846286</v>
+        <v>108.47441993095</v>
       </c>
     </row>
     <row r="75">
@@ -58418,7 +58355,7 @@
       </c>
       <c r="B75"/>
       <c r="C75" t="n">
-        <v>45.41114</v>
+        <v>45.49193</v>
       </c>
       <c r="D75" t="n">
         <v>29.69948</v>
@@ -58427,13 +58364,13 @@
         <v>69.8276114333646</v>
       </c>
       <c r="F75" t="n">
-        <v>56.21239</v>
+        <v>69.8276114333646</v>
       </c>
       <c r="G75" t="n">
         <v>185.390357423826</v>
       </c>
       <c r="H75" t="n">
-        <v>107.098033754531</v>
+        <v>107.143438798398</v>
       </c>
     </row>
     <row r="76">
@@ -58442,7 +58379,7 @@
       </c>
       <c r="B76"/>
       <c r="C76" t="n">
-        <v>45.24699</v>
+        <v>45.32749</v>
       </c>
       <c r="D76" t="n">
         <v>29.93737</v>
@@ -58451,13 +58388,13 @@
         <v>70.4198048982248</v>
       </c>
       <c r="F76" t="n">
-        <v>55.32439</v>
+        <v>70.4198048982248</v>
       </c>
       <c r="G76" t="n">
         <v>172.0208728389</v>
       </c>
       <c r="H76" t="n">
-        <v>106.909541215123</v>
+        <v>106.934509092741</v>
       </c>
     </row>
     <row r="77">
@@ -58466,7 +58403,7 @@
       </c>
       <c r="B77"/>
       <c r="C77" t="n">
-        <v>45.0433</v>
+        <v>45.12344</v>
       </c>
       <c r="D77" t="n">
         <v>29.98058</v>
@@ -58475,13 +58412,13 @@
         <v>70.5270534261849</v>
       </c>
       <c r="F77" t="n">
-        <v>54.23884</v>
+        <v>70.5270534261849</v>
       </c>
       <c r="G77" t="n">
         <v>172.48792856317</v>
       </c>
       <c r="H77" t="n">
-        <v>107.253789937835</v>
+        <v>107.254243274928</v>
       </c>
     </row>
     <row r="78">
@@ -58490,7 +58427,7 @@
       </c>
       <c r="B78"/>
       <c r="C78" t="n">
-        <v>44.84677</v>
+        <v>44.92656</v>
       </c>
       <c r="D78" t="n">
         <v>29.4335</v>
@@ -58499,13 +58436,13 @@
         <v>69.1831495026874</v>
       </c>
       <c r="F78" t="n">
-        <v>53.2778</v>
+        <v>69.1831495026874</v>
       </c>
       <c r="G78" t="n">
         <v>177.383308425235</v>
       </c>
       <c r="H78" t="n">
-        <v>107.09076417713</v>
+        <v>107.10301479191</v>
       </c>
     </row>
     <row r="79">
@@ -58514,7 +58451,7 @@
       </c>
       <c r="B79"/>
       <c r="C79" t="n">
-        <v>44.6164</v>
+        <v>44.69578</v>
       </c>
       <c r="D79" t="n">
         <v>28.79836</v>
@@ -58523,13 +58460,13 @@
         <v>67.6269423000673</v>
       </c>
       <c r="F79" t="n">
-        <v>51.51437</v>
+        <v>67.6269423000673</v>
       </c>
       <c r="G79" t="n">
         <v>171.422493083739</v>
       </c>
       <c r="H79" t="n">
-        <v>105.459771838712</v>
+        <v>105.480404117813</v>
       </c>
     </row>
     <row r="80">
@@ -58538,7 +58475,7 @@
       </c>
       <c r="B80"/>
       <c r="C80" t="n">
-        <v>44.64804</v>
+        <v>44.72747</v>
       </c>
       <c r="D80" t="n">
         <v>29.38201</v>
@@ -58547,13 +58484,13 @@
         <v>69.087512178922</v>
       </c>
       <c r="F80" t="n">
-        <v>52.76884</v>
+        <v>69.087512178922</v>
       </c>
       <c r="G80" t="n">
         <v>164.88541255992</v>
       </c>
       <c r="H80" t="n">
-        <v>105.557849426522</v>
+        <v>105.624912271454</v>
       </c>
     </row>
     <row r="81">
@@ -58562,7 +58499,7 @@
       </c>
       <c r="B81"/>
       <c r="C81" t="n">
-        <v>44.70424</v>
+        <v>44.78377</v>
       </c>
       <c r="D81" t="n">
         <v>29.84576</v>
@@ -58571,13 +58508,13 @@
         <v>70.2468086678287</v>
       </c>
       <c r="F81" t="n">
-        <v>52.08439</v>
+        <v>70.2468086678287</v>
       </c>
       <c r="G81" t="n">
         <v>171.728399442184</v>
       </c>
       <c r="H81" t="n">
-        <v>105.917801693066</v>
+        <v>105.874187064415</v>
       </c>
     </row>
     <row r="82">
@@ -58586,7 +58523,7 @@
       </c>
       <c r="B82"/>
       <c r="C82" t="n">
-        <v>44.60431</v>
+        <v>44.68367</v>
       </c>
       <c r="D82" t="n">
         <v>29.13966</v>
@@ -58595,13 +58532,13 @@
         <v>68.5162864734976</v>
       </c>
       <c r="F82" t="n">
-        <v>52.39</v>
+        <v>68.5162864734976</v>
       </c>
       <c r="G82" t="n">
         <v>167.492275026035</v>
       </c>
       <c r="H82" t="n">
-        <v>104.834262581746</v>
+        <v>104.848266191761</v>
       </c>
     </row>
     <row r="83">
@@ -58610,7 +58547,7 @@
       </c>
       <c r="B83"/>
       <c r="C83" t="n">
-        <v>44.54336</v>
+        <v>44.6226</v>
       </c>
       <c r="D83" t="n">
         <v>29.2146</v>
@@ -58619,13 +58556,13 @@
         <v>68.7023214152762</v>
       </c>
       <c r="F83" t="n">
-        <v>51.92474</v>
+        <v>68.7023214152762</v>
       </c>
       <c r="G83" t="n">
         <v>141.338290928496</v>
       </c>
       <c r="H83" t="n">
-        <v>104.4222639298</v>
+        <v>104.428873126994</v>
       </c>
     </row>
     <row r="84">
@@ -58634,7 +58571,7 @@
       </c>
       <c r="B84"/>
       <c r="C84" t="n">
-        <v>44.55833</v>
+        <v>44.6376</v>
       </c>
       <c r="D84" t="n">
         <v>29.25461</v>
@@ -58643,13 +58580,13 @@
         <v>68.8015984471542</v>
       </c>
       <c r="F84" t="n">
-        <v>51.3203</v>
+        <v>68.8015984471542</v>
       </c>
       <c r="G84" t="n">
         <v>123.703177670584</v>
       </c>
       <c r="H84" t="n">
-        <v>104.990321045578</v>
+        <v>104.931176006735</v>
       </c>
     </row>
     <row r="85">
@@ -58658,7 +58595,7 @@
       </c>
       <c r="B85"/>
       <c r="C85" t="n">
-        <v>44.76627</v>
+        <v>44.84592</v>
       </c>
       <c r="D85" t="n">
         <v>28.83764</v>
@@ -58667,13 +58604,13 @@
         <v>67.775427332607</v>
       </c>
       <c r="F85" t="n">
-        <v>51.24548</v>
+        <v>67.775427332607</v>
       </c>
       <c r="G85" t="n">
         <v>123.334372485864</v>
       </c>
       <c r="H85" t="n">
-        <v>105.533121005384</v>
+        <v>105.623721768379</v>
       </c>
     </row>
     <row r="86">
@@ -58682,7 +58619,7 @@
       </c>
       <c r="B86"/>
       <c r="C86" t="n">
-        <v>45.24503</v>
+        <v>45.32553</v>
       </c>
       <c r="D86" t="n">
         <v>29.87316</v>
@@ -58691,13 +58628,13 @@
         <v>70.390501773446</v>
       </c>
       <c r="F86" t="n">
-        <v>50.8784</v>
+        <v>70.390501773446</v>
       </c>
       <c r="G86" t="n">
         <v>131.649747872205</v>
       </c>
       <c r="H86" t="n">
-        <v>106.809016438339</v>
+        <v>106.851069415328</v>
       </c>
     </row>
     <row r="87">
@@ -58706,7 +58643,7 @@
       </c>
       <c r="B87"/>
       <c r="C87" t="n">
-        <v>45.42115</v>
+        <v>45.50196</v>
       </c>
       <c r="D87" t="n">
         <v>29.52085</v>
@@ -58715,13 +58652,13 @@
         <v>70.4014470107206</v>
       </c>
       <c r="F87" t="n">
-        <v>51.29417</v>
+        <v>70.4014470107206</v>
       </c>
       <c r="G87" t="n">
         <v>141.097832665717</v>
       </c>
       <c r="H87" t="n">
-        <v>105.624504446038</v>
+        <v>105.653268927182</v>
       </c>
     </row>
     <row r="88">
@@ -58730,7 +58667,7 @@
       </c>
       <c r="B88"/>
       <c r="C88" t="n">
-        <v>45.42859</v>
+        <v>45.50942</v>
       </c>
       <c r="D88" t="n">
         <v>28.57354</v>
@@ -58739,13 +58676,13 @@
         <v>67.366873295787</v>
       </c>
       <c r="F88" t="n">
-        <v>52.0828</v>
+        <v>67.366873295787</v>
       </c>
       <c r="G88" t="n">
         <v>166.302249164013</v>
       </c>
       <c r="H88" t="n">
-        <v>105.066807062563</v>
+        <v>105.034140771268</v>
       </c>
     </row>
     <row r="89">
@@ -58756,7 +58693,7 @@
         <v>100</v>
       </c>
       <c r="C89" t="n">
-        <v>45.53598</v>
+        <v>45.61699</v>
       </c>
       <c r="D89" t="n">
         <v>29.17511</v>
@@ -58765,13 +58702,13 @@
         <v>68.5949669848519</v>
       </c>
       <c r="F89" t="n">
-        <v>52.45974</v>
+        <v>68.5949669848519</v>
       </c>
       <c r="G89" t="n">
         <v>180.100488544691</v>
       </c>
       <c r="H89" t="n">
-        <v>105.739234627763</v>
+        <v>105.775681805114</v>
       </c>
     </row>
     <row r="90">
@@ -58782,7 +58719,7 @@
         <v>97.8</v>
       </c>
       <c r="C90" t="n">
-        <v>45.60008</v>
+        <v>45.68121</v>
       </c>
       <c r="D90" t="n">
         <v>29.46036</v>
@@ -58791,13 +58728,13 @@
         <v>68.7876849814182</v>
       </c>
       <c r="F90" t="n">
-        <v>51.92006</v>
+        <v>68.7876849814182</v>
       </c>
       <c r="G90" t="n">
         <v>187.655302182983</v>
       </c>
       <c r="H90" t="n">
-        <v>105.504493526889</v>
+        <v>105.499607275602</v>
       </c>
     </row>
     <row r="91">
@@ -58808,7 +58745,7 @@
         <v>95.6</v>
       </c>
       <c r="C91" t="n">
-        <v>45.79526</v>
+        <v>45.87674</v>
       </c>
       <c r="D91" t="n">
         <v>29.8279</v>
@@ -58817,13 +58754,13 @@
         <v>69.3580401685875</v>
       </c>
       <c r="F91" t="n">
-        <v>51.95757</v>
+        <v>69.3580401685875</v>
       </c>
       <c r="G91" t="n">
         <v>176.409774913281</v>
       </c>
       <c r="H91" t="n">
-        <v>106.347474430169</v>
+        <v>106.350989106316</v>
       </c>
     </row>
     <row r="92">
@@ -58834,7 +58771,7 @@
         <v>94.6</v>
       </c>
       <c r="C92" t="n">
-        <v>45.99349</v>
+        <v>46.07531</v>
       </c>
       <c r="D92" t="n">
         <v>30.49605</v>
@@ -58843,13 +58780,13 @@
         <v>67.348811674053</v>
       </c>
       <c r="F92" t="n">
-        <v>51.32919</v>
+        <v>67.348811674053</v>
       </c>
       <c r="G92" t="n">
         <v>177.027742144788</v>
       </c>
       <c r="H92" t="n">
-        <v>105.826371805461</v>
+        <v>105.838377338824</v>
       </c>
     </row>
     <row r="93">
@@ -58860,7 +58797,7 @@
         <v>89.4</v>
       </c>
       <c r="C93" t="n">
-        <v>46.18412</v>
+        <v>46.26629</v>
       </c>
       <c r="D93" t="n">
         <v>29.99272</v>
@@ -58869,13 +58806,13 @@
         <v>67.9809519255659</v>
       </c>
       <c r="F93" t="n">
-        <v>51.41789</v>
+        <v>67.9809519255659</v>
       </c>
       <c r="G93" t="n">
         <v>185.256429056007</v>
       </c>
       <c r="H93" t="n">
-        <v>106.080355097795</v>
+        <v>106.119907422545</v>
       </c>
     </row>
     <row r="94">
@@ -58886,7 +58823,7 @@
         <v>99.6</v>
       </c>
       <c r="C94" t="n">
-        <v>46.26637</v>
+        <v>46.34869</v>
       </c>
       <c r="D94" t="n">
         <v>29.79457</v>
@@ -58895,13 +58832,13 @@
         <v>68.4094108092543</v>
       </c>
       <c r="F94" t="n">
-        <v>51.74475</v>
+        <v>68.4094108092543</v>
       </c>
       <c r="G94" t="n">
         <v>196.964374678061</v>
       </c>
       <c r="H94" t="n">
-        <v>105.867133584048</v>
+        <v>105.85248525584</v>
       </c>
     </row>
     <row r="95">
@@ -58912,7 +58849,7 @@
         <v>89.8</v>
       </c>
       <c r="C95" t="n">
-        <v>46.34809</v>
+        <v>46.43055</v>
       </c>
       <c r="D95" t="n">
         <v>30.2165</v>
@@ -58921,13 +58858,13 @@
         <v>67.6714224665581</v>
       </c>
       <c r="F95" t="n">
-        <v>51.22981</v>
+        <v>67.6714224665581</v>
       </c>
       <c r="G95" t="n">
         <v>191.17662977513</v>
       </c>
       <c r="H95" t="n">
-        <v>105.481777217802</v>
+        <v>105.491528281118</v>
       </c>
     </row>
     <row r="96">
@@ -58938,7 +58875,7 @@
         <v>91</v>
       </c>
       <c r="C96" t="n">
-        <v>46.35832</v>
+        <v>46.44079</v>
       </c>
       <c r="D96" t="n">
         <v>30.00421</v>
@@ -58947,13 +58884,13 @@
         <v>67.4704046182422</v>
       </c>
       <c r="F96" t="n">
-        <v>50.92849</v>
+        <v>67.4704046182422</v>
       </c>
       <c r="G96" t="n">
         <v>172.056507055475</v>
       </c>
       <c r="H96" t="n">
-        <v>105.250772125695</v>
+        <v>105.283709970404</v>
       </c>
     </row>
     <row r="97">
@@ -58964,7 +58901,7 @@
         <v>93</v>
       </c>
       <c r="C97" t="n">
-        <v>46.54187</v>
+        <v>46.62467</v>
       </c>
       <c r="D97" t="n">
         <v>29.50359</v>
@@ -58973,13 +58910,13 @@
         <v>69.7466083213932</v>
       </c>
       <c r="F97" t="n">
-        <v>51.8994</v>
+        <v>69.7466083213932</v>
       </c>
       <c r="G97" t="n">
         <v>193.177983688479</v>
       </c>
       <c r="H97" t="n">
-        <v>106.87900157048</v>
+        <v>106.874546828057</v>
       </c>
     </row>
     <row r="98">
@@ -58990,7 +58927,7 @@
         <v>95</v>
       </c>
       <c r="C98" t="n">
-        <v>46.60886</v>
+        <v>46.69178</v>
       </c>
       <c r="D98" t="n">
         <v>32.65577</v>
@@ -58999,13 +58936,13 @@
         <v>67.0285185497215</v>
       </c>
       <c r="F98" t="n">
-        <v>51.88104</v>
+        <v>67.0285185497215</v>
       </c>
       <c r="G98" t="n">
         <v>222.184557813375</v>
       </c>
       <c r="H98" t="n">
-        <v>107.408052628253</v>
+        <v>107.401438343919</v>
       </c>
     </row>
     <row r="99">
@@ -59016,7 +58953,7 @@
         <v>97</v>
       </c>
       <c r="C99" t="n">
-        <v>46.63329</v>
+        <v>46.71626</v>
       </c>
       <c r="D99" t="n">
         <v>32.67193</v>
@@ -59025,13 +58962,13 @@
         <v>66.1144029195023</v>
       </c>
       <c r="F99" t="n">
-        <v>51.63769</v>
+        <v>66.1144029195023</v>
       </c>
       <c r="G99" t="n">
         <v>242.14018488135</v>
       </c>
       <c r="H99" t="n">
-        <v>107.851647885608</v>
+        <v>107.849302341813</v>
       </c>
     </row>
     <row r="100">
@@ -59042,7 +58979,7 @@
         <v>102.2</v>
       </c>
       <c r="C100" t="n">
-        <v>46.5864</v>
+        <v>46.66928</v>
       </c>
       <c r="D100" t="n">
         <v>32.64498</v>
@@ -59051,13 +58988,13 @@
         <v>64.8226175155385</v>
       </c>
       <c r="F100" t="n">
-        <v>51.06438</v>
+        <v>64.8226175155385</v>
       </c>
       <c r="G100" t="n">
         <v>222.10383207341</v>
       </c>
       <c r="H100" t="n">
-        <v>106.745089978302</v>
+        <v>106.795614657934</v>
       </c>
     </row>
     <row r="101">
@@ -59068,7 +59005,7 @@
         <v>95.9</v>
       </c>
       <c r="C101" t="n">
-        <v>46.62428</v>
+        <v>46.70723</v>
       </c>
       <c r="D101" t="n">
         <v>33.35789</v>
@@ -59077,13 +59014,13 @@
         <v>66.3696624141498</v>
       </c>
       <c r="F101" t="n">
-        <v>51.60097</v>
+        <v>66.3696624141498</v>
       </c>
       <c r="G101" t="n">
         <v>180.705410996021</v>
       </c>
       <c r="H101" t="n">
-        <v>106.729078214805</v>
+        <v>106.794546701787</v>
       </c>
     </row>
     <row r="102">
@@ -59094,7 +59031,7 @@
         <v>98.1</v>
       </c>
       <c r="C102" t="n">
-        <v>46.68614</v>
+        <v>46.7692</v>
       </c>
       <c r="D102" t="n">
         <v>33.37851</v>
@@ -59103,13 +59040,13 @@
         <v>66.6113025617677</v>
       </c>
       <c r="F102" t="n">
-        <v>51.25476</v>
+        <v>66.6113025617677</v>
       </c>
       <c r="G102" t="n">
         <v>175.680558319211</v>
       </c>
       <c r="H102" t="n">
-        <v>106.608474356422</v>
+        <v>106.567074317313</v>
       </c>
     </row>
     <row r="103">
@@ -59120,7 +59057,7 @@
         <v>109.2</v>
       </c>
       <c r="C103" t="n">
-        <v>46.99202</v>
+        <v>47.07562</v>
       </c>
       <c r="D103" t="n">
         <v>34.09858</v>
@@ -59129,13 +59066,13 @@
         <v>67.995137662185</v>
       </c>
       <c r="F103" t="n">
-        <v>50.57589</v>
+        <v>67.995137662185</v>
       </c>
       <c r="G103" t="n">
         <v>188.48261783792</v>
       </c>
       <c r="H103" t="n">
-        <v>106.96667883026</v>
+        <v>106.983751577893</v>
       </c>
     </row>
     <row r="104">
@@ -59146,7 +59083,7 @@
         <v>109.5</v>
       </c>
       <c r="C104" t="n">
-        <v>47.35602</v>
+        <v>47.44027</v>
       </c>
       <c r="D104" t="n">
         <v>34.47328</v>
@@ -59155,13 +59092,13 @@
         <v>71.3067533838305</v>
       </c>
       <c r="F104" t="n">
-        <v>51.4119</v>
+        <v>71.3067533838305</v>
       </c>
       <c r="G104" t="n">
         <v>190.064902239597</v>
       </c>
       <c r="H104" t="n">
-        <v>108.100525625861</v>
+        <v>108.09210324424</v>
       </c>
     </row>
     <row r="105">
@@ -59172,7 +59109,7 @@
         <v>108.3</v>
       </c>
       <c r="C105" t="n">
-        <v>47.49024</v>
+        <v>47.57473</v>
       </c>
       <c r="D105" t="n">
         <v>34.79283</v>
@@ -59181,13 +59118,13 @@
         <v>68.4590001748442</v>
       </c>
       <c r="F105" t="n">
-        <v>50.8328</v>
+        <v>68.4590001748442</v>
       </c>
       <c r="G105" t="n">
         <v>198.358548584475</v>
       </c>
       <c r="H105" t="n">
-        <v>107.276799620592</v>
+        <v>107.261955891324</v>
       </c>
     </row>
     <row r="106">
@@ -59198,7 +59135,7 @@
         <v>103.2</v>
       </c>
       <c r="C106" t="n">
-        <v>47.63521</v>
+        <v>47.71995</v>
       </c>
       <c r="D106" t="n">
         <v>34.90994</v>
@@ -59207,13 +59144,13 @@
         <v>68.4216822935521</v>
       </c>
       <c r="F106" t="n">
-        <v>50.91572</v>
+        <v>68.4216822935521</v>
       </c>
       <c r="G106" t="n">
         <v>179.262321129805</v>
       </c>
       <c r="H106" t="n">
-        <v>107.182396036926</v>
+        <v>107.248011837059</v>
       </c>
     </row>
     <row r="107">
@@ -59224,7 +59161,7 @@
         <v>106.2</v>
       </c>
       <c r="C107" t="n">
-        <v>47.79915</v>
+        <v>47.88419</v>
       </c>
       <c r="D107" t="n">
         <v>35.18414</v>
@@ -59233,13 +59170,13 @@
         <v>69.527531781795</v>
       </c>
       <c r="F107" t="n">
-        <v>53.68349</v>
+        <v>69.527531781795</v>
       </c>
       <c r="G107" t="n">
         <v>191.370558162712</v>
       </c>
       <c r="H107" t="n">
-        <v>108.312098491155</v>
+        <v>108.277592750694</v>
       </c>
     </row>
     <row r="108">
@@ -59250,7 +59187,7 @@
         <v>101.8</v>
       </c>
       <c r="C108" t="n">
-        <v>47.81657</v>
+        <v>47.90164</v>
       </c>
       <c r="D108" t="n">
         <v>34.98182</v>
@@ -59259,13 +59196,13 @@
         <v>68.1168296034174</v>
       </c>
       <c r="F108" t="n">
-        <v>50.83241</v>
+        <v>68.1168296034174</v>
       </c>
       <c r="G108" t="n">
         <v>198.640067240011</v>
       </c>
       <c r="H108" t="n">
-        <v>107.608069850962</v>
+        <v>107.691810973913</v>
       </c>
     </row>
     <row r="109">
@@ -59276,7 +59213,7 @@
         <v>102.9</v>
       </c>
       <c r="C109" t="n">
-        <v>48.02122</v>
+        <v>48.10665</v>
       </c>
       <c r="D109" t="n">
         <v>35.31776</v>
@@ -59285,13 +59222,13 @@
         <v>71.0979126510547</v>
       </c>
       <c r="F109" t="n">
-        <v>52.16401</v>
+        <v>71.0979126510547</v>
       </c>
       <c r="G109" t="n">
         <v>200.957419356457</v>
       </c>
       <c r="H109" t="n">
-        <v>108.768084843956</v>
+        <v>108.768729083652</v>
       </c>
     </row>
     <row r="110">
@@ -59302,7 +59239,7 @@
         <v>103.2</v>
       </c>
       <c r="C110" t="n">
-        <v>47.89918</v>
+        <v>47.9844</v>
       </c>
       <c r="D110" t="n">
         <v>32.60874</v>
@@ -59311,13 +59248,13 @@
         <v>70.5507049560547</v>
       </c>
       <c r="F110" t="n">
-        <v>56.88224</v>
+        <v>70.5507049560547</v>
       </c>
       <c r="G110" t="n">
         <v>216.534758535397</v>
       </c>
       <c r="H110" t="n">
-        <v>109.621914309981</v>
+        <v>109.647580414648</v>
       </c>
     </row>
     <row r="111">
@@ -59328,7 +59265,7 @@
         <v>107.2</v>
       </c>
       <c r="C111" t="n">
-        <v>47.87555</v>
+        <v>47.96073</v>
       </c>
       <c r="D111" t="n">
         <v>32.60874</v>
@@ -59337,13 +59274,13 @@
         <v>71.7154235839844</v>
       </c>
       <c r="F111" t="n">
-        <v>56.11052</v>
+        <v>71.7154235839844</v>
       </c>
       <c r="G111" t="n">
         <v>220.44593124421</v>
       </c>
       <c r="H111" t="n">
-        <v>109.643838692843</v>
+        <v>109.656352221081</v>
       </c>
     </row>
     <row r="112">
@@ -59354,7 +59291,7 @@
         <v>109.4</v>
       </c>
       <c r="C112" t="n">
-        <v>47.9406</v>
+        <v>48.02589</v>
       </c>
       <c r="D112" t="n">
         <v>32.66702</v>
@@ -59363,13 +59300,13 @@
         <v>72.7019653320312</v>
       </c>
       <c r="F112" t="n">
-        <v>57.26664</v>
+        <v>72.7019653320312</v>
       </c>
       <c r="G112" t="n">
         <v>235.814564606971</v>
       </c>
       <c r="H112" t="n">
-        <v>110.147103912443</v>
+        <v>110.160771441298</v>
       </c>
     </row>
     <row r="113">
@@ -59380,7 +59317,7 @@
         <v>115.2</v>
       </c>
       <c r="C113" t="n">
-        <v>48.17218</v>
+        <v>48.25788</v>
       </c>
       <c r="D113" t="n">
         <v>33.18785</v>
@@ -59389,13 +59326,13 @@
         <v>73.8026885986328</v>
       </c>
       <c r="F113" t="n">
-        <v>56.34501</v>
+        <v>73.8026885986328</v>
       </c>
       <c r="G113" t="n">
         <v>235.8327683193</v>
       </c>
       <c r="H113" t="n">
-        <v>110.714361497592</v>
+        <v>110.677425459358</v>
       </c>
     </row>
     <row r="114">
@@ -59406,7 +59343,7 @@
         <v>116.1</v>
       </c>
       <c r="C114" t="n">
-        <v>48.34617</v>
+        <v>48.43218</v>
       </c>
       <c r="D114" t="n">
         <v>33.18785</v>
@@ -59415,13 +59352,13 @@
         <v>73.0529632568359</v>
       </c>
       <c r="F114" t="n">
-        <v>56.35681</v>
+        <v>73.0529632568359</v>
       </c>
       <c r="G114" t="n">
         <v>259.871104532309</v>
       </c>
       <c r="H114" t="n">
-        <v>111.348754788973</v>
+        <v>111.37912033677</v>
       </c>
     </row>
     <row r="115">
@@ -59432,7 +59369,7 @@
         <v>115.1</v>
       </c>
       <c r="C115" t="n">
-        <v>48.42433</v>
+        <v>48.51048</v>
       </c>
       <c r="D115" t="n">
         <v>33.93756</v>
@@ -59441,13 +59378,13 @@
         <v>74.6876220703125</v>
       </c>
       <c r="F115" t="n">
-        <v>57.36809</v>
+        <v>74.6876220703125</v>
       </c>
       <c r="G115" t="n">
         <v>241.144156052488</v>
       </c>
       <c r="H115" t="n">
-        <v>111.515777921157</v>
+        <v>111.576261379766</v>
       </c>
     </row>
     <row r="116">
@@ -59458,7 +59395,7 @@
         <v>117.9</v>
       </c>
       <c r="C116" t="n">
-        <v>48.33776</v>
+        <v>48.42375</v>
       </c>
       <c r="D116" t="n">
         <v>34.51573</v>
@@ -59467,13 +59404,13 @@
         <v>74.9036331176758</v>
       </c>
       <c r="F116" t="n">
-        <v>56.51735</v>
+        <v>74.9036331176758</v>
       </c>
       <c r="G116" t="n">
         <v>257.658953805693</v>
       </c>
       <c r="H116" t="n">
-        <v>111.591608650143</v>
+        <v>111.548367314421</v>
       </c>
     </row>
     <row r="117">
@@ -59484,7 +59421,7 @@
         <v>114.3</v>
       </c>
       <c r="C117" t="n">
-        <v>48.62723</v>
+        <v>48.71374</v>
       </c>
       <c r="D117" t="n">
         <v>34.95026</v>
@@ -59493,13 +59430,13 @@
         <v>75.0103302001953</v>
       </c>
       <c r="F117" t="n">
-        <v>57.71768</v>
+        <v>75.0103302001953</v>
       </c>
       <c r="G117" t="n">
         <v>285.862384690571</v>
       </c>
       <c r="H117" t="n">
-        <v>113.124877352996</v>
+        <v>113.232747660869</v>
       </c>
     </row>
     <row r="118">
@@ -59510,7 +59447,7 @@
         <v>116.8</v>
       </c>
       <c r="C118" t="n">
-        <v>49.00367</v>
+        <v>49.09085</v>
       </c>
       <c r="D118" t="n">
         <v>34.83347</v>
@@ -59519,13 +59456,13 @@
         <v>76.31689453125</v>
       </c>
       <c r="F118" t="n">
-        <v>57.33051</v>
+        <v>76.31689453125</v>
       </c>
       <c r="G118" t="n">
         <v>290.650216840126</v>
       </c>
       <c r="H118" t="n">
-        <v>113.578508111181</v>
+        <v>113.563387284039</v>
       </c>
     </row>
     <row r="119">
@@ -59536,7 +59473,7 @@
         <v>116.5</v>
       </c>
       <c r="C119" t="n">
-        <v>49.48015</v>
+        <v>49.56818</v>
       </c>
       <c r="D119" t="n">
         <v>34.57013</v>
@@ -59545,13 +59482,13 @@
         <v>75.3541717529297</v>
       </c>
       <c r="F119" t="n">
-        <v>60.22621</v>
+        <v>75.3541717529297</v>
       </c>
       <c r="G119" t="n">
         <v>334.28449137043</v>
       </c>
       <c r="H119" t="n">
-        <v>113.704580255185</v>
+        <v>113.723511660109</v>
       </c>
     </row>
     <row r="120">
@@ -59562,7 +59499,7 @@
         <v>114.6</v>
       </c>
       <c r="C120" t="n">
-        <v>49.78936</v>
+        <v>49.87794</v>
       </c>
       <c r="D120" t="n">
         <v>34.71557</v>
@@ -59571,13 +59508,13 @@
         <v>75.5981674194336</v>
       </c>
       <c r="F120" t="n">
-        <v>58.06295</v>
+        <v>75.5981674194336</v>
       </c>
       <c r="G120" t="n">
         <v>300.688294639131</v>
       </c>
       <c r="H120" t="n">
-        <v>113.689798659752</v>
+        <v>113.655277553113</v>
       </c>
     </row>
     <row r="121">
@@ -59588,7 +59525,7 @@
         <v>116.9</v>
       </c>
       <c r="C121" t="n">
-        <v>49.99203</v>
+        <v>50.08097</v>
       </c>
       <c r="D121" t="n">
         <v>35.26501</v>
@@ -59597,13 +59534,13 @@
         <v>77.8755111694336</v>
       </c>
       <c r="F121" t="n">
-        <v>56.8571</v>
+        <v>77.8755111694336</v>
       </c>
       <c r="G121" t="n">
         <v>263.57283939781</v>
       </c>
       <c r="H121" t="n">
-        <v>114.899458117491</v>
+        <v>114.96344979775</v>
       </c>
     </row>
     <row r="122">
@@ -59614,7 +59551,7 @@
         <v>118.6</v>
       </c>
       <c r="C122" t="n">
-        <v>50.03424</v>
+        <v>50.12325</v>
       </c>
       <c r="D122" t="n">
         <v>36.10024</v>
@@ -59623,13 +59560,13 @@
         <v>75.8688507080078</v>
       </c>
       <c r="F122" t="n">
-        <v>59.81848</v>
+        <v>75.8688507080078</v>
       </c>
       <c r="G122" t="n">
         <v>290.255969163301</v>
       </c>
       <c r="H122" t="n">
-        <v>115.491190326796</v>
+        <v>115.533668508747</v>
       </c>
     </row>
     <row r="123">
@@ -59640,7 +59577,7 @@
         <v>122</v>
       </c>
       <c r="C123" t="n">
-        <v>49.93408</v>
+        <v>50.02292</v>
       </c>
       <c r="D123" t="n">
         <v>35.86639</v>
@@ -59649,13 +59586,13 @@
         <v>77.4675140380859</v>
       </c>
       <c r="F123" t="n">
-        <v>59.64289</v>
+        <v>77.4675140380859</v>
       </c>
       <c r="G123" t="n">
         <v>297.218310985335</v>
       </c>
       <c r="H123" t="n">
-        <v>114.850214220483</v>
+        <v>114.839311161009</v>
       </c>
     </row>
     <row r="124">
@@ -59666,7 +59603,7 @@
         <v>122.2</v>
       </c>
       <c r="C124" t="n">
-        <v>50.08426</v>
+        <v>50.17337</v>
       </c>
       <c r="D124" t="n">
         <v>36.95681</v>
@@ -59675,13 +59612,13 @@
         <v>76.7981872558594</v>
       </c>
       <c r="F124" t="n">
-        <v>58.92749</v>
+        <v>76.7981872558594</v>
       </c>
       <c r="G124" t="n">
         <v>331.994921930565</v>
       </c>
       <c r="H124" t="n">
-        <v>116.013646890536</v>
+        <v>116.024452852191</v>
       </c>
     </row>
     <row r="125">
@@ -59692,7 +59629,7 @@
         <v>121.9</v>
       </c>
       <c r="C125" t="n">
-        <v>50.30921</v>
+        <v>50.39872</v>
       </c>
       <c r="D125" t="n">
         <v>36.54683</v>
@@ -59701,13 +59638,13 @@
         <v>77.6030197143555</v>
       </c>
       <c r="F125" t="n">
-        <v>60.43551</v>
+        <v>77.6030197143555</v>
       </c>
       <c r="G125" t="n">
         <v>325.499553080885</v>
       </c>
       <c r="H125" t="n">
-        <v>116.131980810365</v>
+        <v>116.069702388803</v>
       </c>
     </row>
     <row r="126">
@@ -59718,7 +59655,7 @@
         <v>122.3</v>
       </c>
       <c r="C126" t="n">
-        <v>50.59314</v>
+        <v>50.68315</v>
       </c>
       <c r="D126" t="n">
         <v>37.35325</v>
@@ -59727,13 +59664,13 @@
         <v>79.2743377685547</v>
       </c>
       <c r="F126" t="n">
-        <v>60.06196</v>
+        <v>79.2743377685547</v>
       </c>
       <c r="G126" t="n">
         <v>305.419628678167</v>
       </c>
       <c r="H126" t="n">
-        <v>117.064520616272</v>
+        <v>117.082990890657</v>
       </c>
     </row>
     <row r="127">
@@ -59744,7 +59681,7 @@
         <v>118.6</v>
       </c>
       <c r="C127" t="n">
-        <v>50.48446</v>
+        <v>50.57427</v>
       </c>
       <c r="D127" t="n">
         <v>37.23661</v>
@@ -59753,13 +59690,13 @@
         <v>78.7332000732422</v>
       </c>
       <c r="F127" t="n">
-        <v>59.63336</v>
+        <v>78.7332000732422</v>
       </c>
       <c r="G127" t="n">
         <v>353.804791825462</v>
       </c>
       <c r="H127" t="n">
-        <v>116.569337694065</v>
+        <v>116.655637973906</v>
       </c>
     </row>
     <row r="128">
@@ -59770,7 +59707,7 @@
         <v>120.4</v>
       </c>
       <c r="C128" t="n">
-        <v>50.37478</v>
+        <v>50.46441</v>
       </c>
       <c r="D128" t="n">
         <v>37.26571</v>
@@ -59779,13 +59716,13 @@
         <v>82.041015625</v>
       </c>
       <c r="F128" t="n">
-        <v>59.74251</v>
+        <v>82.041015625</v>
       </c>
       <c r="G128" t="n">
         <v>372.587592154422</v>
       </c>
       <c r="H128" t="n">
-        <v>117.315381455307</v>
+        <v>117.328741005016</v>
       </c>
     </row>
     <row r="129">
@@ -59796,7 +59733,7 @@
         <v>121.2</v>
       </c>
       <c r="C129" t="n">
-        <v>50.23104</v>
+        <v>50.3204</v>
       </c>
       <c r="D129" t="n">
         <v>37.46896</v>
@@ -59805,13 +59742,13 @@
         <v>80.9652252197266</v>
       </c>
       <c r="F129" t="n">
-        <v>59.98371</v>
+        <v>80.9652252197266</v>
       </c>
       <c r="G129" t="n">
         <v>405.0141394805</v>
       </c>
       <c r="H129" t="n">
-        <v>118.176476355189</v>
+        <v>118.145349042411</v>
       </c>
     </row>
     <row r="130">
@@ -59822,22 +59759,22 @@
         <v>118.4</v>
       </c>
       <c r="C130" t="n">
-        <v>50.44948</v>
+        <v>50.53924</v>
       </c>
       <c r="D130" t="n">
-        <v>36.91168</v>
+        <v>36.88212</v>
       </c>
       <c r="E130" t="n">
         <v>79.8137512207031</v>
       </c>
       <c r="F130" t="n">
-        <v>60.35159</v>
+        <v>79.8137512207031</v>
       </c>
       <c r="G130" t="n">
         <v>410.999401501032</v>
       </c>
       <c r="H130" t="n">
-        <v>118.434101073643</v>
+        <v>118.497422182557</v>
       </c>
     </row>
     <row r="131">
@@ -59848,22 +59785,22 @@
         <v>123.7</v>
       </c>
       <c r="C131" t="n">
-        <v>51.1394</v>
+        <v>51.23038</v>
       </c>
       <c r="D131" t="n">
-        <v>38.53474</v>
+        <v>38.53298</v>
       </c>
       <c r="E131" t="n">
         <v>82.3772125244141</v>
       </c>
       <c r="F131" t="n">
-        <v>60.42048</v>
+        <v>82.3772125244141</v>
       </c>
       <c r="G131" t="n">
         <v>394.564206501934</v>
       </c>
       <c r="H131" t="n">
-        <v>119.154180408171</v>
+        <v>119.123088571681</v>
       </c>
     </row>
     <row r="132">
@@ -59874,22 +59811,22 @@
         <v>124.3</v>
       </c>
       <c r="C132" t="n">
-        <v>51.73611</v>
+        <v>51.82815</v>
       </c>
       <c r="D132" t="n">
-        <v>38.38905</v>
+        <v>38.3873</v>
       </c>
       <c r="E132" t="n">
         <v>81.8722534179688</v>
       </c>
       <c r="F132" t="n">
-        <v>61.76796</v>
+        <v>81.8722534179688</v>
       </c>
       <c r="G132" t="n">
         <v>375.909668573678</v>
       </c>
       <c r="H132" t="n">
-        <v>120.343339128645</v>
+        <v>120.388175772312</v>
       </c>
     </row>
     <row r="133">
@@ -59900,22 +59837,22 @@
         <v>118.2</v>
       </c>
       <c r="C133" t="n">
-        <v>52.30219</v>
+        <v>52.39525</v>
       </c>
       <c r="D133" t="n">
-        <v>38.85158</v>
+        <v>38.8498</v>
       </c>
       <c r="E133" t="n">
         <v>84.3476867675781</v>
       </c>
       <c r="F133" t="n">
-        <v>61.5364</v>
+        <v>84.3476867675781</v>
       </c>
       <c r="G133" t="n">
         <v>376.486015931608</v>
       </c>
       <c r="H133" t="n">
-        <v>121.034109895243</v>
+        <v>121.068368965426</v>
       </c>
     </row>
     <row r="134">
@@ -59926,22 +59863,22 @@
         <v>121.3</v>
       </c>
       <c r="C134" t="n">
-        <v>52.62573</v>
+        <v>52.71936</v>
       </c>
       <c r="D134" t="n">
-        <v>38.47168</v>
+        <v>38.46992</v>
       </c>
       <c r="E134" t="n">
         <v>85.1487045288086</v>
       </c>
       <c r="F134" t="n">
-        <v>61.37386</v>
+        <v>85.1487045288086</v>
       </c>
       <c r="G134" t="n">
         <v>416.822971947014</v>
       </c>
       <c r="H134" t="n">
-        <v>121.639280444719</v>
+        <v>121.657971922287</v>
       </c>
     </row>
     <row r="135">
@@ -59952,22 +59889,22 @@
         <v>123.8</v>
       </c>
       <c r="C135" t="n">
-        <v>52.86034</v>
+        <v>52.95438</v>
       </c>
       <c r="D135" t="n">
-        <v>39.47622</v>
+        <v>39.47441</v>
       </c>
       <c r="E135" t="n">
         <v>84.3313751220703</v>
       </c>
       <c r="F135" t="n">
-        <v>62.58162</v>
+        <v>84.3313751220703</v>
       </c>
       <c r="G135" t="n">
         <v>397.135123643281</v>
       </c>
       <c r="H135" t="n">
-        <v>121.709831227377</v>
+        <v>121.79422885084</v>
       </c>
     </row>
     <row r="136">
@@ -59978,22 +59915,22 @@
         <v>124.5</v>
       </c>
       <c r="C136" t="n">
-        <v>53.09491</v>
+        <v>53.18937</v>
       </c>
       <c r="D136" t="n">
-        <v>39.70809</v>
+        <v>39.70628</v>
       </c>
       <c r="E136" t="n">
         <v>85.3585891723633</v>
       </c>
       <c r="F136" t="n">
-        <v>62.10193</v>
+        <v>85.3585891723633</v>
       </c>
       <c r="G136" t="n">
         <v>401.555039297703</v>
       </c>
       <c r="H136" t="n">
-        <v>122.351242037945</v>
+        <v>122.296021073706</v>
       </c>
     </row>
     <row r="137">
@@ -60004,22 +59941,22 @@
         <v>127.5</v>
       </c>
       <c r="C137" t="n">
-        <v>53.41112</v>
+        <v>53.50614</v>
       </c>
       <c r="D137" t="n">
-        <v>40.34251</v>
+        <v>40.28341</v>
       </c>
       <c r="E137" t="n">
         <v>85.438362121582</v>
       </c>
       <c r="F137" t="n">
-        <v>62.04065</v>
+        <v>85.438362121582</v>
       </c>
       <c r="G137" t="n">
         <v>430.731723439813</v>
       </c>
       <c r="H137" t="n">
-        <v>124.054371327114</v>
+        <v>123.984929124734</v>
       </c>
     </row>
     <row r="138">
@@ -60030,22 +59967,22 @@
         <v>127.2</v>
       </c>
       <c r="C138" t="n">
-        <v>53.64078</v>
+        <v>53.73622</v>
       </c>
       <c r="D138" t="n">
-        <v>39.84536</v>
+        <v>39.84507</v>
       </c>
       <c r="E138" t="n">
         <v>84.9697418212891</v>
       </c>
       <c r="F138" t="n">
-        <v>63.46946</v>
+        <v>84.9697418212891</v>
       </c>
       <c r="G138" t="n">
         <v>429.272952936529</v>
       </c>
       <c r="H138" t="n">
-        <v>124.233009621825</v>
+        <v>124.280013256051</v>
       </c>
     </row>
     <row r="139">
@@ -60056,22 +59993,22 @@
         <v>127.9</v>
       </c>
       <c r="C139" t="n">
-        <v>53.72796</v>
+        <v>53.82355</v>
       </c>
       <c r="D139" t="n">
-        <v>40.65092</v>
+        <v>40.65063</v>
       </c>
       <c r="E139" t="n">
         <v>85.9269638061523</v>
       </c>
       <c r="F139" t="n">
-        <v>65.00281</v>
+        <v>85.9269638061523</v>
       </c>
       <c r="G139" t="n">
         <v>429.349191914501</v>
       </c>
       <c r="H139" t="n">
-        <v>124.255371563557</v>
+        <v>124.325996860955</v>
       </c>
     </row>
     <row r="140">
@@ -60082,22 +60019,22 @@
         <v>129</v>
       </c>
       <c r="C140" t="n">
-        <v>53.46659</v>
+        <v>53.56171</v>
       </c>
       <c r="D140" t="n">
-        <v>39.35187</v>
+        <v>39.35159</v>
       </c>
       <c r="E140" t="n">
         <v>84.5964660644531</v>
       </c>
       <c r="F140" t="n">
-        <v>63.967</v>
+        <v>84.5964660644531</v>
       </c>
       <c r="G140" t="n">
         <v>445.882103839945</v>
       </c>
       <c r="H140" t="n">
-        <v>121.629855562419</v>
+        <v>121.63060924901</v>
       </c>
     </row>
     <row r="141">
@@ -60108,22 +60045,22 @@
         <v>130.1</v>
       </c>
       <c r="C141" t="n">
-        <v>53.69491</v>
+        <v>53.79044</v>
       </c>
       <c r="D141" t="n">
-        <v>40.80582</v>
+        <v>40.80552</v>
       </c>
       <c r="E141" t="n">
         <v>86.8485641479492</v>
       </c>
       <c r="F141" t="n">
-        <v>65.76544</v>
+        <v>86.8485641479492</v>
       </c>
       <c r="G141" t="n">
         <v>432.403184852728</v>
       </c>
       <c r="H141" t="n">
-        <v>123.484710859746</v>
+        <v>123.50128801926</v>
       </c>
     </row>
     <row r="142">
@@ -60134,22 +60071,22 @@
         <v>126</v>
       </c>
       <c r="C142" t="n">
-        <v>54.04778</v>
+        <v>54.14394</v>
       </c>
       <c r="D142" t="n">
-        <v>42.28775</v>
+        <v>42.23144</v>
       </c>
       <c r="E142" t="n">
         <v>88.8986968994141</v>
       </c>
       <c r="F142" t="n">
-        <v>66.10149</v>
+        <v>88.8986968994141</v>
       </c>
       <c r="G142" t="n">
         <v>378.637513812833</v>
       </c>
       <c r="H142" t="n">
-        <v>125.098656030682</v>
+        <v>125.119154892312</v>
       </c>
     </row>
     <row r="143">
@@ -60160,22 +60097,22 @@
         <v>130.2</v>
       </c>
       <c r="C143" t="n">
-        <v>54.32493</v>
+        <v>54.42158</v>
       </c>
       <c r="D143" t="n">
-        <v>41.82112</v>
+        <v>41.85268</v>
       </c>
       <c r="E143" t="n">
         <v>88.6025543212891</v>
       </c>
       <c r="F143" t="n">
-        <v>66.84948</v>
+        <v>88.6025543212891</v>
       </c>
       <c r="G143" t="n">
         <v>345.445684152086</v>
       </c>
       <c r="H143" t="n">
-        <v>124.704595264186</v>
+        <v>124.790091514945</v>
       </c>
     </row>
     <row r="144">
@@ -60186,22 +60123,22 @@
         <v>127.6</v>
       </c>
       <c r="C144" t="n">
-        <v>54.60644</v>
+        <v>54.70359</v>
       </c>
       <c r="D144" t="n">
-        <v>42.42578</v>
+        <v>42.42877</v>
       </c>
       <c r="E144" t="n">
         <v>89.8053665161133</v>
       </c>
       <c r="F144" t="n">
-        <v>68.88267</v>
+        <v>89.8053665161133</v>
       </c>
       <c r="G144" t="n">
         <v>349.505101730711</v>
       </c>
       <c r="H144" t="n">
-        <v>125.703479072252</v>
+        <v>125.70480288575</v>
       </c>
     </row>
     <row r="145">
@@ -60212,22 +60149,22 @@
         <v>128.3</v>
       </c>
       <c r="C145" t="n">
-        <v>54.8427</v>
+        <v>54.94027</v>
       </c>
       <c r="D145" t="n">
-        <v>42.8011</v>
+        <v>42.77537</v>
       </c>
       <c r="E145" t="n">
         <v>89.4126586914062</v>
       </c>
       <c r="F145" t="n">
-        <v>67.73643</v>
+        <v>89.4126586914062</v>
       </c>
       <c r="G145" t="n">
         <v>358.058455757405</v>
       </c>
       <c r="H145" t="n">
-        <v>126.306855771799</v>
+        <v>126.257904018447</v>
       </c>
     </row>
     <row r="146">
@@ -60238,22 +60175,22 @@
         <v>128.2</v>
       </c>
       <c r="C146" t="n">
-        <v>55.16294</v>
+        <v>55.26108</v>
       </c>
       <c r="D146" t="n">
-        <v>43.1189</v>
+        <v>43.12196</v>
       </c>
       <c r="E146" t="n">
         <v>90.7935943603516</v>
       </c>
       <c r="F146" t="n">
-        <v>67.32718</v>
+        <v>90.7935943603516</v>
       </c>
       <c r="G146" t="n">
         <v>317.414292518911</v>
       </c>
       <c r="H146" t="n">
-        <v>126.962388353254</v>
+        <v>127.055853971843</v>
       </c>
     </row>
     <row r="147">
@@ -60264,22 +60201,22 @@
         <v>132.7</v>
       </c>
       <c r="C147" t="n">
-        <v>55.49058</v>
+        <v>55.58931</v>
       </c>
       <c r="D147" t="n">
-        <v>43.72358</v>
+        <v>43.72669</v>
       </c>
       <c r="E147" t="n">
         <v>94.4965972900391</v>
       </c>
       <c r="F147" t="n">
-        <v>67.707</v>
+        <v>94.4965972900391</v>
       </c>
       <c r="G147" t="n">
         <v>345.416243887031</v>
       </c>
       <c r="H147" t="n">
-        <v>128.470701526891</v>
+        <v>128.450927248454</v>
       </c>
     </row>
     <row r="148">
@@ -60290,22 +60227,22 @@
         <v>136.4</v>
       </c>
       <c r="C148" t="n">
-        <v>55.78232</v>
+        <v>55.88156</v>
       </c>
       <c r="D148" t="n">
-        <v>43.92607</v>
+        <v>43.90032</v>
       </c>
       <c r="E148" t="n">
         <v>91.892463684082</v>
       </c>
       <c r="F148" t="n">
-        <v>69.11852</v>
+        <v>91.892463684082</v>
       </c>
       <c r="G148" t="n">
         <v>349.988051673129</v>
       </c>
       <c r="H148" t="n">
-        <v>128.988438454044</v>
+        <v>128.954454883268</v>
       </c>
     </row>
     <row r="149">
@@ -60316,22 +60253,22 @@
         <v>131.1</v>
       </c>
       <c r="C149" t="n">
-        <v>55.97106</v>
+        <v>56.07064</v>
       </c>
       <c r="D149" t="n">
-        <v>43.92607</v>
+        <v>43.92931</v>
       </c>
       <c r="E149" t="n">
         <v>91.4909439086914</v>
       </c>
       <c r="F149" t="n">
-        <v>68.00978</v>
+        <v>91.4909439086914</v>
       </c>
       <c r="G149" t="n">
         <v>357.106734215402</v>
       </c>
       <c r="H149" t="n">
-        <v>128.601473138682</v>
+        <v>128.595961498693</v>
       </c>
     </row>
     <row r="150">
@@ -60342,22 +60279,22 @@
         <v>132.2</v>
       </c>
       <c r="C150" t="n">
-        <v>56.408</v>
+        <v>56.50835</v>
       </c>
       <c r="D150" t="n">
-        <v>44.98596</v>
+        <v>44.98928</v>
       </c>
       <c r="E150" t="n">
         <v>92.7977676391602</v>
       </c>
       <c r="F150" t="n">
-        <v>69.61723</v>
+        <v>92.7977676391602</v>
       </c>
       <c r="G150" t="n">
         <v>348.251172199536</v>
       </c>
       <c r="H150" t="n">
-        <v>131.002462642181</v>
+        <v>131.057288201778</v>
       </c>
     </row>
     <row r="151">
@@ -60368,22 +60305,22 @@
         <v>137.2</v>
       </c>
       <c r="C151" t="n">
-        <v>56.45565</v>
+        <v>56.5561</v>
       </c>
       <c r="D151" t="n">
-        <v>44.04872</v>
+        <v>44.05197</v>
       </c>
       <c r="E151" t="n">
         <v>92.9095230102539</v>
       </c>
       <c r="F151" t="n">
-        <v>67.71196</v>
+        <v>92.9095230102539</v>
       </c>
       <c r="G151" t="n">
         <v>384.507954586591</v>
       </c>
       <c r="H151" t="n">
-        <v>130.279329048397</v>
+        <v>130.269633899685</v>
       </c>
     </row>
     <row r="152">
@@ -60394,22 +60331,22 @@
         <v>133.8</v>
       </c>
       <c r="C152" t="n">
-        <v>56.8139</v>
+        <v>56.91497</v>
       </c>
       <c r="D152" t="n">
-        <v>44.45257</v>
+        <v>44.48456</v>
       </c>
       <c r="E152" t="n">
         <v>94.2794723510742</v>
       </c>
       <c r="F152" t="n">
-        <v>69.48866</v>
+        <v>94.2794723510742</v>
       </c>
       <c r="G152" t="n">
         <v>424.839914731363</v>
       </c>
       <c r="H152" t="n">
-        <v>132.41591004479</v>
+        <v>132.443834089471</v>
       </c>
     </row>
     <row r="153">
@@ -60420,22 +60357,22 @@
         <v>132.4</v>
       </c>
       <c r="C153" t="n">
-        <v>56.93381</v>
+        <v>57.0351</v>
       </c>
       <c r="D153" t="n">
-        <v>45.99049</v>
+        <v>45.99459</v>
       </c>
       <c r="E153" t="n">
         <v>94.6048202514648</v>
       </c>
       <c r="F153" t="n">
-        <v>68.88441</v>
+        <v>94.6048202514648</v>
       </c>
       <c r="G153" t="n">
         <v>408.999097033915</v>
       </c>
       <c r="H153" t="n">
-        <v>132.920414662061</v>
+        <v>132.944471782329</v>
       </c>
     </row>
     <row r="154">
@@ -60446,22 +60383,22 @@
         <v>139.2</v>
       </c>
       <c r="C154" t="n">
-        <v>56.9945</v>
+        <v>57.0959</v>
       </c>
       <c r="D154" t="n">
-        <v>45.08381</v>
+        <v>45.05828</v>
       </c>
       <c r="E154" t="n">
         <v>92.3840713500977</v>
       </c>
       <c r="F154" t="n">
-        <v>70.74751</v>
+        <v>92.3840713500977</v>
       </c>
       <c r="G154" t="n">
         <v>439.205388503335</v>
       </c>
       <c r="H154" t="n">
-        <v>132.522982622221</v>
+        <v>132.507084470165</v>
       </c>
     </row>
     <row r="155">
@@ -60472,22 +60409,22 @@
         <v>129.7</v>
       </c>
       <c r="C155" t="n">
-        <v>57.24163</v>
+        <v>57.34347</v>
       </c>
       <c r="D155" t="n">
-        <v>45.08381</v>
+        <v>45.05828</v>
       </c>
       <c r="E155" t="n">
         <v>93.9198455810547</v>
       </c>
       <c r="F155" t="n">
-        <v>70.35421</v>
+        <v>93.9198455810547</v>
       </c>
       <c r="G155" t="n">
         <v>462.626076574791</v>
       </c>
       <c r="H155" t="n">
-        <v>134.000613878459</v>
+        <v>134.025615658193</v>
       </c>
     </row>
     <row r="156">
@@ -60498,22 +60435,22 @@
         <v>129.5</v>
       </c>
       <c r="C156" t="n">
-        <v>57.63296</v>
+        <v>57.7355</v>
       </c>
       <c r="D156" t="n">
-        <v>46.39647</v>
+        <v>46.39914</v>
       </c>
       <c r="E156" t="n">
         <v>95.9850769042969</v>
       </c>
       <c r="F156" t="n">
-        <v>71.33716</v>
+        <v>95.9850769042969</v>
       </c>
       <c r="G156" t="n">
         <v>496.261591523384</v>
       </c>
       <c r="H156" t="n">
-        <v>135.039118636017</v>
+        <v>135.005342908655</v>
       </c>
     </row>
     <row r="157">
@@ -60524,22 +60461,22 @@
         <v>127</v>
       </c>
       <c r="C157" t="n">
-        <v>57.92947</v>
+        <v>58.03253</v>
       </c>
       <c r="D157" t="n">
-        <v>46.54096</v>
+        <v>46.54364</v>
       </c>
       <c r="E157" t="n">
         <v>97.1216659545898</v>
       </c>
       <c r="F157" t="n">
-        <v>71.50031</v>
+        <v>97.1216659545898</v>
       </c>
       <c r="G157" t="n">
         <v>476.17742913272</v>
       </c>
       <c r="H157" t="n">
-        <v>135.396972300403</v>
+        <v>135.444110273108</v>
       </c>
     </row>
     <row r="158">
@@ -60550,22 +60487,22 @@
         <v>132.4</v>
       </c>
       <c r="C158" t="n">
-        <v>58.16224</v>
+        <v>58.26572</v>
       </c>
       <c r="D158" t="n">
-        <v>46.22149</v>
+        <v>46.22415</v>
       </c>
       <c r="E158" t="n">
         <v>95.6308441162109</v>
       </c>
       <c r="F158" t="n">
-        <v>73.36443</v>
+        <v>95.6308441162109</v>
       </c>
       <c r="G158" t="n">
         <v>463.885267349189</v>
       </c>
       <c r="H158" t="n">
-        <v>135.061187809098</v>
+        <v>135.055385676624</v>
       </c>
     </row>
     <row r="159">
@@ -60576,22 +60513,22 @@
         <v>133.4</v>
       </c>
       <c r="C159" t="n">
-        <v>58.33597</v>
+        <v>58.43976</v>
       </c>
       <c r="D159" t="n">
-        <v>46.93945</v>
+        <v>46.94216</v>
       </c>
       <c r="E159" t="n">
         <v>95.0773010253906</v>
       </c>
       <c r="F159" t="n">
-        <v>73.22492</v>
+        <v>95.0773010253906</v>
       </c>
       <c r="G159" t="n">
         <v>458.754109474569</v>
       </c>
       <c r="H159" t="n">
-        <v>134.65600424567</v>
+        <v>134.688035027584</v>
       </c>
     </row>
     <row r="160">
@@ -60602,22 +60539,22 @@
         <v>127.7</v>
       </c>
       <c r="C160" t="n">
-        <v>58.62014</v>
+        <v>58.72443</v>
       </c>
       <c r="D160" t="n">
-        <v>46.79453</v>
+        <v>46.82625</v>
       </c>
       <c r="E160" t="n">
         <v>96.7915496826172</v>
       </c>
       <c r="F160" t="n">
-        <v>76.08191</v>
+        <v>96.7915496826172</v>
       </c>
       <c r="G160" t="n">
         <v>492.017809420976</v>
       </c>
       <c r="H160" t="n">
-        <v>135.875987644136</v>
+        <v>135.886758539329</v>
       </c>
     </row>
     <row r="161">
@@ -60628,22 +60565,22 @@
         <v>123.2</v>
       </c>
       <c r="C161" t="n">
-        <v>58.76839</v>
+        <v>58.87294</v>
       </c>
       <c r="D161" t="n">
-        <v>46.79453</v>
+        <v>46.76834</v>
       </c>
       <c r="E161" t="n">
         <v>96.0263595581055</v>
       </c>
       <c r="F161" t="n">
-        <v>75.70811</v>
+        <v>96.0263595581055</v>
       </c>
       <c r="G161" t="n">
         <v>519.001394057854</v>
       </c>
       <c r="H161" t="n">
-        <v>136.257799169416</v>
+        <v>136.242781846702</v>
       </c>
     </row>
     <row r="162">
@@ -60654,22 +60591,22 @@
         <v>127.6</v>
       </c>
       <c r="C162" t="n">
-        <v>58.57363</v>
+        <v>58.67783</v>
       </c>
       <c r="D162" t="n">
-        <v>44.8143</v>
+        <v>44.81814</v>
       </c>
       <c r="E162" t="n">
         <v>91.5295867919922</v>
       </c>
       <c r="F162" t="n">
-        <v>72.65603</v>
+        <v>91.5295867919922</v>
       </c>
       <c r="G162" t="n">
         <v>551.2433264353</v>
       </c>
       <c r="H162" t="n">
-        <v>134.299774595352</v>
+        <v>134.294510066294</v>
       </c>
     </row>
     <row r="163">
@@ -60680,22 +60617,22 @@
         <v>128.2</v>
       </c>
       <c r="C163" t="n">
-        <v>58.83836</v>
+        <v>58.94304</v>
       </c>
       <c r="D163" t="n">
-        <v>47.39829</v>
+        <v>47.40236</v>
       </c>
       <c r="E163" t="n">
         <v>93.3627395629883</v>
       </c>
       <c r="F163" t="n">
-        <v>75.67067</v>
+        <v>93.3627395629883</v>
       </c>
       <c r="G163" t="n">
         <v>585.099231212815</v>
       </c>
       <c r="H163" t="n">
-        <v>136.012096721442</v>
+        <v>136.069883489371</v>
       </c>
     </row>
     <row r="164">
@@ -60706,22 +60643,22 @@
         <v>124.3</v>
       </c>
       <c r="C164" t="n">
-        <v>59.09723</v>
+        <v>59.20237</v>
       </c>
       <c r="D164" t="n">
-        <v>49.12721</v>
+        <v>49.15925</v>
       </c>
       <c r="E164" t="n">
         <v>97.3191986083984</v>
       </c>
       <c r="F164" t="n">
-        <v>75.2054</v>
+        <v>97.3191986083984</v>
       </c>
       <c r="G164" t="n">
         <v>577.795473692407</v>
       </c>
       <c r="H164" t="n">
-        <v>136.617350551853</v>
+        <v>136.629130710512</v>
       </c>
     </row>
     <row r="165">
@@ -60732,22 +60669,22 @@
         <v>127.8</v>
       </c>
       <c r="C165" t="n">
-        <v>58.83774</v>
+        <v>58.94242</v>
       </c>
       <c r="D165" t="n">
-        <v>47.33523</v>
+        <v>47.33724</v>
       </c>
       <c r="E165" t="n">
         <v>91.8904037475586</v>
       </c>
       <c r="F165" t="n">
-        <v>75.86769</v>
+        <v>91.8904037475586</v>
       </c>
       <c r="G165" t="n">
         <v>529.062783378813</v>
       </c>
       <c r="H165" t="n">
-        <v>135.260740260873</v>
+        <v>135.260106820793</v>
       </c>
     </row>
     <row r="166">
@@ -60758,22 +60695,22 @@
         <v>129.2</v>
       </c>
       <c r="C166" t="n">
-        <v>58.65124</v>
+        <v>58.75559</v>
       </c>
       <c r="D166" t="n">
-        <v>48.4182</v>
+        <v>48.39207</v>
       </c>
       <c r="E166" t="n">
         <v>92.642951965332</v>
       </c>
       <c r="F166" t="n">
-        <v>71.12096</v>
+        <v>92.642951965332</v>
       </c>
       <c r="G166" t="n">
         <v>470.408608477343</v>
       </c>
       <c r="H166" t="n">
-        <v>135.536672171005</v>
+        <v>135.561736859003</v>
       </c>
     </row>
     <row r="167">
@@ -60784,22 +60721,22 @@
         <v>121.4</v>
       </c>
       <c r="C167" t="n">
-        <v>58.2806</v>
+        <v>58.38429</v>
       </c>
       <c r="D167" t="n">
-        <v>47.8675</v>
+        <v>47.87048</v>
       </c>
       <c r="E167" t="n">
         <v>91.8343505859375</v>
       </c>
       <c r="F167" t="n">
-        <v>73.23555</v>
+        <v>91.8343505859375</v>
       </c>
       <c r="G167" t="n">
         <v>359.612034906274</v>
       </c>
       <c r="H167" t="n">
-        <v>135.162590955813</v>
+        <v>135.129294918423</v>
       </c>
     </row>
     <row r="168">
@@ -60810,22 +60747,22 @@
         <v>121.8</v>
       </c>
       <c r="C168" t="n">
-        <v>57.93406</v>
+        <v>58.03713</v>
       </c>
       <c r="D168" t="n">
-        <v>47.63639</v>
+        <v>47.63936</v>
       </c>
       <c r="E168" t="n">
         <v>91.4482650756836</v>
       </c>
       <c r="F168" t="n">
-        <v>72.34477</v>
+        <v>91.4482650756836</v>
       </c>
       <c r="G168" t="n">
         <v>285.445972817485</v>
       </c>
       <c r="H168" t="n">
-        <v>135.269369402668</v>
+        <v>135.348204376191</v>
       </c>
     </row>
     <row r="169">
@@ -60836,22 +60773,22 @@
         <v>113.4</v>
       </c>
       <c r="C169" t="n">
-        <v>57.32905</v>
+        <v>57.43105</v>
       </c>
       <c r="D169" t="n">
-        <v>47.20214</v>
+        <v>47.17599</v>
       </c>
       <c r="E169" t="n">
         <v>88.056640625</v>
       </c>
       <c r="F169" t="n">
-        <v>72.9495</v>
+        <v>88.056640625</v>
       </c>
       <c r="G169" t="n">
         <v>203.933772464511</v>
       </c>
       <c r="H169" t="n">
-        <v>134.552441744834</v>
+        <v>134.537468631977</v>
       </c>
     </row>
     <row r="170">
@@ -60862,22 +60799,22 @@
         <v>121.3</v>
       </c>
       <c r="C170" t="n">
-        <v>56.7744</v>
+        <v>56.8754</v>
       </c>
       <c r="D170" t="n">
-        <v>47.63243</v>
+        <v>47.63485</v>
       </c>
       <c r="E170" t="n">
         <v>87.1845169067383</v>
       </c>
       <c r="F170" t="n">
-        <v>70.24229</v>
+        <v>87.1845169067383</v>
       </c>
       <c r="G170" t="n">
         <v>210.284710466966</v>
       </c>
       <c r="H170" t="n">
-        <v>135.272297308169</v>
+        <v>135.286842332257</v>
       </c>
     </row>
     <row r="171">
@@ -60888,22 +60825,22 @@
         <v>111.3</v>
       </c>
       <c r="C171" t="n">
-        <v>56.35504</v>
+        <v>56.4553</v>
       </c>
       <c r="D171" t="n">
-        <v>47.57477</v>
+        <v>47.57718</v>
       </c>
       <c r="E171" t="n">
         <v>87.3976287841797</v>
       </c>
       <c r="F171" t="n">
-        <v>70.0477</v>
+        <v>87.3976287841797</v>
       </c>
       <c r="G171" t="n">
         <v>206.821495823248</v>
       </c>
       <c r="H171" t="n">
-        <v>135.496849321701</v>
+        <v>135.501948411566</v>
       </c>
     </row>
     <row r="172">
@@ -60914,22 +60851,22 @@
         <v>107.3</v>
       </c>
       <c r="C172" t="n">
-        <v>56.29226</v>
+        <v>56.39241</v>
       </c>
       <c r="D172" t="n">
-        <v>47.19868</v>
+        <v>47.17202</v>
       </c>
       <c r="E172" t="n">
         <v>89.5705718994141</v>
       </c>
       <c r="F172" t="n">
-        <v>66.44216</v>
+        <v>89.5705718994141</v>
       </c>
       <c r="G172" t="n">
         <v>255.845447860765</v>
       </c>
       <c r="H172" t="n">
-        <v>135.754293335412</v>
+        <v>135.762112152516</v>
       </c>
     </row>
     <row r="173">
@@ -60940,22 +60877,22 @@
         <v>115.47</v>
       </c>
       <c r="C173" t="n">
-        <v>56.67331</v>
+        <v>56.77413</v>
       </c>
       <c r="D173" t="n">
-        <v>49.61389</v>
+        <v>49.45022</v>
       </c>
       <c r="E173" t="n">
         <v>89.4139938354492</v>
       </c>
       <c r="F173" t="n">
-        <v>67.19307</v>
+        <v>89.4139938354492</v>
       </c>
       <c r="G173" t="n">
         <v>264.693635340251</v>
       </c>
       <c r="H173" t="n">
-        <v>136.213142846885</v>
+        <v>136.249498135143</v>
       </c>
     </row>
     <row r="174">
@@ -60966,22 +60903,22 @@
         <v>118.13</v>
       </c>
       <c r="C174" t="n">
-        <v>57.22921</v>
+        <v>57.33103</v>
       </c>
       <c r="D174" t="n">
-        <v>49.67141</v>
+        <v>49.67995</v>
       </c>
       <c r="E174" t="n">
         <v>89.8660736083984</v>
       </c>
       <c r="F174" t="n">
-        <v>66.94417</v>
+        <v>89.8660736083984</v>
       </c>
       <c r="G174" t="n">
         <v>305.69232782834</v>
       </c>
       <c r="H174" t="n">
-        <v>136.567297018287</v>
+        <v>136.635084214866</v>
       </c>
     </row>
     <row r="175">
@@ -60992,22 +60929,22 @@
         <v>121.1</v>
       </c>
       <c r="C175" t="n">
-        <v>57.74975</v>
+        <v>57.85249</v>
       </c>
       <c r="D175" t="n">
-        <v>49.23785</v>
+        <v>49.27534</v>
       </c>
       <c r="E175" t="n">
         <v>91.5934143066406</v>
       </c>
       <c r="F175" t="n">
-        <v>68.65957</v>
+        <v>91.5934143066406</v>
       </c>
       <c r="G175" t="n">
         <v>344.580653943245</v>
       </c>
       <c r="H175" t="n">
-        <v>137.33753657347</v>
+        <v>137.26087290057</v>
       </c>
     </row>
     <row r="176">
@@ -61018,22 +60955,22 @@
         <v>125.2</v>
       </c>
       <c r="C176" t="n">
-        <v>57.97413</v>
+        <v>58.07727</v>
       </c>
       <c r="D176" t="n">
-        <v>49.38153</v>
+        <v>49.39034</v>
       </c>
       <c r="E176" t="n">
         <v>88.1884689331055</v>
       </c>
       <c r="F176" t="n">
-        <v>65.03807</v>
+        <v>88.1884689331055</v>
       </c>
       <c r="G176" t="n">
         <v>309.998290043929</v>
       </c>
       <c r="H176" t="n">
-        <v>136.42012182916</v>
+        <v>136.522409404365</v>
       </c>
     </row>
     <row r="177">
@@ -61044,22 +60981,22 @@
         <v>133.61</v>
       </c>
       <c r="C177" t="n">
-        <v>58.54197</v>
+        <v>58.64612</v>
       </c>
       <c r="D177" t="n">
-        <v>49.32394</v>
+        <v>49.33274</v>
       </c>
       <c r="E177" t="n">
         <v>92.2564315795898</v>
       </c>
       <c r="F177" t="n">
-        <v>69.955</v>
+        <v>92.2564315795898</v>
       </c>
       <c r="G177" t="n">
         <v>336.375066493063</v>
       </c>
       <c r="H177" t="n">
-        <v>138.630127802792</v>
+        <v>138.544306287643</v>
       </c>
     </row>
     <row r="178">
@@ -61070,22 +61007,22 @@
         <v>133.78</v>
       </c>
       <c r="C178" t="n">
-        <v>58.80878</v>
+        <v>58.91341</v>
       </c>
       <c r="D178" t="n">
-        <v>49.58226</v>
+        <v>49.61973</v>
       </c>
       <c r="E178" t="n">
         <v>91.1535415649414</v>
       </c>
       <c r="F178" t="n">
-        <v>70.44533</v>
+        <v>91.1535415649414</v>
       </c>
       <c r="G178" t="n">
         <v>323.874381991398</v>
       </c>
       <c r="H178" t="n">
-        <v>138.097788112029</v>
+        <v>138.120360710403</v>
       </c>
     </row>
     <row r="179">
@@ -61096,22 +61033,22 @@
         <v>133.08</v>
       </c>
       <c r="C179" t="n">
-        <v>59.12885</v>
+        <v>59.23404</v>
       </c>
       <c r="D179" t="n">
-        <v>51.55678</v>
+        <v>51.53927</v>
       </c>
       <c r="E179" t="n">
         <v>92.2140197753906</v>
       </c>
       <c r="F179" t="n">
-        <v>72.21234</v>
+        <v>92.2140197753906</v>
       </c>
       <c r="G179" t="n">
         <v>348.917878694058</v>
       </c>
       <c r="H179" t="n">
-        <v>139.575434444828</v>
+        <v>139.536094407685</v>
       </c>
     </row>
     <row r="180">
@@ -61122,22 +61059,22 @@
         <v>132.71</v>
       </c>
       <c r="C180" t="n">
-        <v>59.21958</v>
+        <v>59.32494</v>
       </c>
       <c r="D180" t="n">
-        <v>50.6576</v>
+        <v>50.66915</v>
       </c>
       <c r="E180" t="n">
         <v>92.7438201904297</v>
       </c>
       <c r="F180" t="n">
-        <v>71.80368</v>
+        <v>92.7438201904297</v>
       </c>
       <c r="G180" t="n">
         <v>363.450051915994</v>
       </c>
       <c r="H180" t="n">
-        <v>139.065984109104</v>
+        <v>139.071439213307</v>
       </c>
     </row>
     <row r="181">
@@ -61148,22 +61085,22 @@
         <v>133.4</v>
       </c>
       <c r="C181" t="n">
-        <v>59.3358</v>
+        <v>59.44137</v>
       </c>
       <c r="D181" t="n">
-        <v>50.62884</v>
+        <v>50.64038</v>
       </c>
       <c r="E181" t="n">
         <v>94.0013046264648</v>
       </c>
       <c r="F181" t="n">
-        <v>69.53547</v>
+        <v>94.0013046264648</v>
       </c>
       <c r="G181" t="n">
         <v>348.027280885619</v>
       </c>
       <c r="H181" t="n">
-        <v>139.096578625608</v>
+        <v>139.178524221502</v>
       </c>
     </row>
     <row r="182">
@@ -61174,22 +61111,22 @@
         <v>133.8</v>
       </c>
       <c r="C182" t="n">
-        <v>59.79333</v>
+        <v>59.8997</v>
       </c>
       <c r="D182" t="n">
-        <v>52.15801</v>
+        <v>52.142</v>
       </c>
       <c r="E182" t="n">
         <v>96.2896499633789</v>
       </c>
       <c r="F182" t="n">
-        <v>73.81049</v>
+        <v>96.2896499633789</v>
       </c>
       <c r="G182" t="n">
         <v>361.003104964462</v>
       </c>
       <c r="H182" t="n">
-        <v>140.835285858429</v>
+        <v>140.806912954893</v>
       </c>
     </row>
     <row r="183">
@@ -61200,22 +61137,22 @@
         <v>134.9</v>
       </c>
       <c r="C183" t="n">
-        <v>60.09029</v>
+        <v>60.1972</v>
       </c>
       <c r="D183" t="n">
-        <v>50.28563</v>
+        <v>50.29892</v>
       </c>
       <c r="E183" t="n">
         <v>95.7192459106445</v>
       </c>
       <c r="F183" t="n">
-        <v>73.54281</v>
+        <v>95.7192459106445</v>
       </c>
       <c r="G183" t="n">
         <v>356.31614243135</v>
       </c>
       <c r="H183" t="n">
-        <v>140.82401903556</v>
+        <v>140.866051858334</v>
       </c>
     </row>
     <row r="184">
@@ -61226,22 +61163,22 @@
         <v>135</v>
       </c>
       <c r="C184" t="n">
-        <v>60.60714</v>
+        <v>60.71496</v>
       </c>
       <c r="D184" t="n">
-        <v>53.83341</v>
+        <v>53.8744</v>
       </c>
       <c r="E184" t="n">
         <v>96.9096527099609</v>
       </c>
       <c r="F184" t="n">
-        <v>75.10474</v>
+        <v>96.9096527099609</v>
       </c>
       <c r="G184" t="n">
         <v>378.150517662722</v>
       </c>
       <c r="H184" t="n">
-        <v>142.832169547007</v>
+        <v>142.873393097315</v>
       </c>
     </row>
     <row r="185">
@@ -61252,22 +61189,22 @@
         <v>138.93</v>
       </c>
       <c r="C185" t="n">
-        <v>60.71264</v>
+        <v>60.82066</v>
       </c>
       <c r="D185" t="n">
-        <v>51.96785</v>
+        <v>51.8599</v>
       </c>
       <c r="E185" t="n">
         <v>95.6520462036133</v>
       </c>
       <c r="F185" t="n">
-        <v>77.40863</v>
+        <v>95.6520462036133</v>
       </c>
       <c r="G185" t="n">
         <v>385.923182777376</v>
       </c>
       <c r="H185" t="n">
-        <v>142.953576891122</v>
+        <v>142.896252840211</v>
       </c>
     </row>
     <row r="186">
@@ -61278,22 +61215,22 @@
         <v>135</v>
       </c>
       <c r="C186" t="n">
-        <v>60.95204</v>
+        <v>61.06048</v>
       </c>
       <c r="D186" t="n">
-        <v>51.68074</v>
+        <v>51.65906</v>
       </c>
       <c r="E186" t="n">
         <v>94.3085556030273</v>
       </c>
       <c r="F186" t="n">
-        <v>78.05057</v>
+        <v>94.3085556030273</v>
       </c>
       <c r="G186" t="n">
         <v>342.949516351264</v>
       </c>
       <c r="H186" t="n">
-        <v>143.421035087556</v>
+        <v>143.480698514328</v>
       </c>
     </row>
     <row r="187">
@@ -61304,22 +61241,22 @@
         <v>134.72</v>
       </c>
       <c r="C187" t="n">
-        <v>61.26441</v>
+        <v>61.37341</v>
       </c>
       <c r="D187" t="n">
-        <v>52.75746</v>
+        <v>52.79198</v>
       </c>
       <c r="E187" t="n">
         <v>97.4155883789062</v>
       </c>
       <c r="F187" t="n">
-        <v>78.42361</v>
+        <v>97.4155883789062</v>
       </c>
       <c r="G187" t="n">
         <v>355.531724207281</v>
       </c>
       <c r="H187" t="n">
-        <v>144.985758580361</v>
+        <v>145.044638128134</v>
       </c>
     </row>
     <row r="188">
@@ -61330,22 +61267,22 @@
         <v>134</v>
       </c>
       <c r="C188" t="n">
-        <v>61.55724</v>
+        <v>61.66675</v>
       </c>
       <c r="D188" t="n">
-        <v>53.18511</v>
+        <v>53.21967</v>
       </c>
       <c r="E188" t="n">
         <v>97.0624771118164</v>
       </c>
       <c r="F188" t="n">
-        <v>79.13474</v>
+        <v>97.0624771118164</v>
       </c>
       <c r="G188" t="n">
         <v>358.677522489883</v>
       </c>
       <c r="H188" t="n">
-        <v>144.910365985899</v>
+        <v>144.901043936387</v>
       </c>
     </row>
     <row r="189">
@@ -61356,22 +61293,22 @@
         <v>136.1</v>
       </c>
       <c r="C189" t="n">
-        <v>61.79277</v>
+        <v>61.9027</v>
       </c>
       <c r="D189" t="n">
-        <v>54.14956</v>
+        <v>54.15612</v>
       </c>
       <c r="E189" t="n">
         <v>96.817253112793</v>
       </c>
       <c r="F189" t="n">
-        <v>74.25173</v>
+        <v>96.817253112793</v>
       </c>
       <c r="G189" t="n">
         <v>352.39440177229</v>
       </c>
       <c r="H189" t="n">
-        <v>145.150917193436</v>
+        <v>145.228520295683</v>
       </c>
     </row>
     <row r="190">
@@ -61382,22 +61319,22 @@
         <v>137.02</v>
       </c>
       <c r="C190" t="n">
-        <v>61.97898</v>
+        <v>62.08925</v>
       </c>
       <c r="D190" t="n">
-        <v>54.37804</v>
+        <v>54.38462</v>
       </c>
       <c r="E190" t="n">
         <v>98.8926086425781</v>
       </c>
       <c r="F190" t="n">
-        <v>71.9428</v>
+        <v>98.8926086425781</v>
       </c>
       <c r="G190" t="n">
         <v>340.338325099792</v>
       </c>
       <c r="H190" t="n">
-        <v>145.878123288575</v>
+        <v>145.873334925796</v>
       </c>
     </row>
     <row r="191">
@@ -61408,22 +61345,22 @@
         <v>136.4</v>
       </c>
       <c r="C191" t="n">
-        <v>62.21691</v>
+        <v>62.3276</v>
       </c>
       <c r="D191" t="n">
-        <v>53.94703</v>
+        <v>53.95357</v>
       </c>
       <c r="E191" t="n">
         <v>98.626594543457</v>
       </c>
       <c r="F191" t="n">
-        <v>72.93655</v>
+        <v>98.626594543457</v>
       </c>
       <c r="G191" t="n">
         <v>356.897756264822</v>
       </c>
       <c r="H191" t="n">
-        <v>146.359521095427</v>
+        <v>146.379515397988</v>
       </c>
     </row>
     <row r="192">
@@ -61434,22 +61371,22 @@
         <v>130.6</v>
       </c>
       <c r="C192" t="n">
-        <v>62.41373</v>
+        <v>62.52477</v>
       </c>
       <c r="D192" t="n">
-        <v>54.08994</v>
+        <v>54.06794</v>
       </c>
       <c r="E192" t="n">
         <v>99.345573425293</v>
       </c>
       <c r="F192" t="n">
-        <v>72.68291</v>
+        <v>99.345573425293</v>
       </c>
       <c r="G192" t="n">
         <v>370.192789445644</v>
       </c>
       <c r="H192" t="n">
-        <v>147.872878543554</v>
+        <v>147.910645129051</v>
       </c>
     </row>
     <row r="193">
@@ -61460,22 +61397,22 @@
         <v>135</v>
       </c>
       <c r="C193" t="n">
-        <v>62.6488</v>
+        <v>62.76026</v>
       </c>
       <c r="D193" t="n">
-        <v>53.77421</v>
+        <v>53.78095</v>
       </c>
       <c r="E193" t="n">
         <v>100.264602661133</v>
       </c>
       <c r="F193" t="n">
-        <v>73.46729</v>
+        <v>100.264602661133</v>
       </c>
       <c r="G193" t="n">
         <v>385.928935037614</v>
       </c>
       <c r="H193" t="n">
-        <v>148.625551495341</v>
+        <v>148.638365503086</v>
       </c>
     </row>
     <row r="194">
@@ -61486,22 +61423,22 @@
         <v>131.8</v>
       </c>
       <c r="C194" t="n">
-        <v>63.10729</v>
+        <v>63.21956</v>
       </c>
       <c r="D194" t="n">
-        <v>54.03116</v>
+        <v>54.00944</v>
       </c>
       <c r="E194" t="n">
-        <v>100.408935546875</v>
+        <v>100.381248474121</v>
       </c>
       <c r="F194" t="n">
-        <v>76.27325</v>
+        <v>100.381248474121</v>
       </c>
       <c r="G194" t="n">
         <v>383.140800985249</v>
       </c>
       <c r="H194" t="n">
-        <v>150.113293265809</v>
+        <v>150.139612994667</v>
       </c>
     </row>
     <row r="195">
@@ -61512,22 +61449,22 @@
         <v>129.2</v>
       </c>
       <c r="C195" t="n">
-        <v>63.22859</v>
+        <v>63.34108</v>
       </c>
       <c r="D195" t="n">
-        <v>54.11695</v>
+        <v>54.12381</v>
       </c>
       <c r="E195" t="n">
-        <v>99.2799530029297</v>
+        <v>99.1624984741211</v>
       </c>
       <c r="F195" t="n">
-        <v>74.42883</v>
+        <v>99.1624984741211</v>
       </c>
       <c r="G195" t="n">
         <v>387.142139366241</v>
       </c>
       <c r="H195" t="n">
-        <v>149.581892207648</v>
+        <v>149.678684382774</v>
       </c>
     </row>
     <row r="196">
@@ -61538,22 +61475,22 @@
         <v>131.6</v>
       </c>
       <c r="C196" t="n">
-        <v>63.50078</v>
+        <v>63.61376</v>
       </c>
       <c r="D196" t="n">
-        <v>54.34541</v>
+        <v>54.40927</v>
       </c>
       <c r="E196" t="n">
-        <v>100.930046081543</v>
+        <v>100.17716217041</v>
       </c>
       <c r="F196" t="n">
-        <v>76.11222</v>
+        <v>100.17716217041</v>
       </c>
       <c r="G196" t="n">
         <v>437.144781455405</v>
       </c>
       <c r="H196" t="n">
-        <v>150.842867558959</v>
+        <v>150.792293794582</v>
       </c>
     </row>
     <row r="197">
@@ -61564,22 +61501,22 @@
         <v>133.6</v>
       </c>
       <c r="C197" t="n">
-        <v>63.59293</v>
+        <v>63.70607</v>
       </c>
       <c r="D197" t="n">
-        <v>54.34541</v>
+        <v>54.32334</v>
       </c>
       <c r="E197" t="n">
-        <v>99.6178970336914</v>
+        <v>99.2576217651367</v>
       </c>
       <c r="F197" t="n">
-        <v>75.73089</v>
+        <v>99.2576217651367</v>
       </c>
       <c r="G197" t="n">
         <v>446.056239584272</v>
       </c>
       <c r="H197" t="n">
-        <v>150.856443417039</v>
+        <v>150.820944330403</v>
       </c>
     </row>
     <row r="198">
@@ -61590,22 +61527,22 @@
         <v>131.8</v>
       </c>
       <c r="C198" t="n">
-        <v>63.73535</v>
+        <v>63.84875</v>
       </c>
       <c r="D198" t="n">
-        <v>54.45976</v>
+        <v>54.4377</v>
       </c>
       <c r="E198" t="n">
-        <v>99.7612152099609</v>
+        <v>99.6928482055664</v>
       </c>
       <c r="F198" t="n">
-        <v>75.55484</v>
+        <v>99.6928482055664</v>
       </c>
       <c r="G198" t="n">
         <v>413.009292743841</v>
       </c>
       <c r="H198" t="n">
-        <v>151.167207690478</v>
+        <v>151.229669089538</v>
       </c>
     </row>
     <row r="199">
@@ -61616,22 +61553,22 @@
         <v>133.9</v>
       </c>
       <c r="C199" t="n">
-        <v>63.94772</v>
+        <v>64.06149</v>
       </c>
       <c r="D199" t="n">
-        <v>55.67663</v>
+        <v>55.6827</v>
       </c>
       <c r="E199" t="n">
-        <v>101.372833251953</v>
+        <v>101.605499267578</v>
       </c>
       <c r="F199" t="n">
-        <v>74.47744</v>
+        <v>101.605499267578</v>
       </c>
       <c r="G199" t="n">
         <v>387.341541075231</v>
       </c>
       <c r="H199" t="n">
-        <v>152.45061728377</v>
+        <v>152.498486013199</v>
       </c>
     </row>
     <row r="200">
@@ -61642,22 +61579,22 @@
         <v>132.78</v>
       </c>
       <c r="C200" t="n">
-        <v>64.12216</v>
+        <v>64.23624</v>
       </c>
       <c r="D200" t="n">
-        <v>56.55658</v>
+        <v>56.5909</v>
       </c>
       <c r="E200" t="n">
-        <v>100.899238586426</v>
+        <v>101.092422485352</v>
       </c>
       <c r="F200" t="n">
-        <v>75.2242</v>
+        <v>101.092422485352</v>
       </c>
       <c r="G200" t="n">
         <v>392.405196955101</v>
       </c>
       <c r="H200" t="n">
-        <v>154.484308518336</v>
+        <v>154.451991619028</v>
       </c>
     </row>
     <row r="201">
@@ -61668,22 +61605,22 @@
         <v>132.68</v>
       </c>
       <c r="C201" t="n">
-        <v>64.1571</v>
+        <v>64.27124</v>
       </c>
       <c r="D201" t="n">
-        <v>54.66585</v>
+        <v>54.6704</v>
       </c>
       <c r="E201" t="n">
-        <v>98.768196105957</v>
+        <v>98.8581695556641</v>
       </c>
       <c r="F201" t="n">
-        <v>72.18655</v>
+        <v>98.8581695556641</v>
       </c>
       <c r="G201" t="n">
         <v>358.96215617611</v>
       </c>
       <c r="H201" t="n">
-        <v>153.951337653947</v>
+        <v>153.984002084423</v>
       </c>
     </row>
     <row r="202">
@@ -61694,22 +61631,22 @@
         <v>130.89</v>
       </c>
       <c r="C202" t="n">
-        <v>64.38107</v>
+        <v>64.49561</v>
       </c>
       <c r="D202" t="n">
-        <v>55.2064</v>
+        <v>55.15434</v>
       </c>
       <c r="E202" t="n">
-        <v>100.408538818359</v>
+        <v>100.510284423828</v>
       </c>
       <c r="F202" t="n">
-        <v>74.25872</v>
+        <v>100.510284423828</v>
       </c>
       <c r="G202" t="n">
         <v>370.050554281521</v>
       </c>
       <c r="H202" t="n">
-        <v>155.062866311809</v>
+        <v>155.138882100056</v>
       </c>
     </row>
     <row r="203">
@@ -61720,22 +61657,22 @@
         <v>135.12</v>
       </c>
       <c r="C203" t="n">
-        <v>64.47234</v>
+        <v>64.58704</v>
       </c>
       <c r="D203" t="n">
-        <v>55.4631</v>
+        <v>55.43952</v>
       </c>
       <c r="E203" t="n">
-        <v>100.125999450684</v>
+        <v>100.619422912598</v>
       </c>
       <c r="F203" t="n">
-        <v>74.08023</v>
+        <v>100.619422912598</v>
       </c>
       <c r="G203" t="n">
         <v>371.711908290207</v>
       </c>
       <c r="H203" t="n">
-        <v>155.43656781962</v>
+        <v>155.512766805917</v>
       </c>
     </row>
     <row r="204">
@@ -61746,22 +61683,22 @@
         <v>131.73</v>
       </c>
       <c r="C204" t="n">
-        <v>64.78421</v>
+        <v>64.89946</v>
       </c>
       <c r="D204" t="n">
-        <v>56.70698</v>
+        <v>56.71145</v>
       </c>
       <c r="E204" t="n">
-        <v>100.988090515137</v>
+        <v>101.200942993164</v>
       </c>
       <c r="F204" t="n">
-        <v>72.52217</v>
+        <v>101.200942993164</v>
       </c>
       <c r="G204" t="n">
         <v>425.569324215302</v>
       </c>
       <c r="H204" t="n">
-        <v>155.741223492547</v>
+        <v>155.761587232806</v>
       </c>
     </row>
     <row r="205">
@@ -61772,22 +61709,22 @@
         <v>131.59</v>
       </c>
       <c r="C205" t="n">
-        <v>64.96223</v>
+        <v>65.07781</v>
       </c>
       <c r="D205" t="n">
-        <v>56.76411</v>
+        <v>56.74003</v>
       </c>
       <c r="E205" t="n">
-        <v>101.444747924805</v>
+        <v>101.476356506348</v>
       </c>
       <c r="F205" t="n">
-        <v>73.9518</v>
+        <v>101.476356506348</v>
       </c>
       <c r="G205" t="n">
         <v>437.326337080964</v>
       </c>
       <c r="H205" t="n">
-        <v>155.177440263504</v>
+        <v>155.158789890215</v>
       </c>
     </row>
     <row r="206">
@@ -61798,22 +61735,22 @@
         <v>130.04</v>
       </c>
       <c r="C206" t="n">
-        <v>65.14023</v>
+        <v>65.25612</v>
       </c>
       <c r="D206" t="n">
-        <v>57.02077</v>
+        <v>57.02516</v>
       </c>
       <c r="E206" t="n">
-        <v>100.063819885254</v>
+        <v>100.217239379883</v>
       </c>
       <c r="F206" t="n">
-        <v>75.6903</v>
+        <v>100.217239379883</v>
       </c>
       <c r="G206" t="n">
         <v>449.048375295697</v>
       </c>
       <c r="H206" t="n">
-        <v>154.857774736561</v>
+        <v>154.843817546738</v>
       </c>
     </row>
     <row r="207">
@@ -61824,22 +61761,22 @@
         <v>130.58</v>
       </c>
       <c r="C207" t="n">
-        <v>65.07281</v>
+        <v>65.18858</v>
       </c>
       <c r="D207" t="n">
-        <v>57.36272</v>
+        <v>57.36714</v>
       </c>
       <c r="E207" t="n">
-        <v>99.9487838745117</v>
+        <v>99.8771591186523</v>
       </c>
       <c r="F207" t="n">
-        <v>72.35416</v>
+        <v>99.8771591186523</v>
       </c>
       <c r="G207" t="n">
         <v>449.505386792615</v>
       </c>
       <c r="H207" t="n">
-        <v>153.965793954078</v>
+        <v>153.97204685395</v>
       </c>
     </row>
     <row r="208">
@@ -61850,22 +61787,22 @@
         <v>130.34</v>
       </c>
       <c r="C208" t="n">
-        <v>65.32604</v>
+        <v>65.44226</v>
       </c>
       <c r="D208" t="n">
-        <v>56.58579</v>
+        <v>56.56116</v>
       </c>
       <c r="E208" t="n">
-        <v>100.746879577637</v>
+        <v>101.083480834961</v>
       </c>
       <c r="F208" t="n">
-        <v>76.43601</v>
+        <v>101.083480834961</v>
       </c>
       <c r="G208" t="n">
         <v>467.889355408494</v>
       </c>
       <c r="H208" t="n">
-        <v>154.018142324023</v>
+        <v>154.102923093776</v>
       </c>
     </row>
     <row r="209">
@@ -61876,22 +61813,22 @@
         <v>130.82</v>
       </c>
       <c r="C209" t="n">
-        <v>65.7753</v>
+        <v>65.89232</v>
       </c>
       <c r="D209" t="n">
-        <v>58.3582</v>
+        <v>58.30598</v>
       </c>
       <c r="E209" t="n">
-        <v>103.919555664062</v>
+        <v>103.547325134277</v>
       </c>
       <c r="F209" t="n">
-        <v>79.29119</v>
+        <v>103.547325134277</v>
       </c>
       <c r="G209" t="n">
         <v>450.065887618886</v>
       </c>
       <c r="H209" t="n">
-        <v>156.20828030787</v>
+        <v>156.187935643235</v>
       </c>
     </row>
     <row r="210">
@@ -61902,22 +61839,22 @@
         <v>128.46</v>
       </c>
       <c r="C210" t="n">
-        <v>65.89872</v>
+        <v>66.01596</v>
       </c>
       <c r="D210" t="n">
-        <v>58.3582</v>
+        <v>58.36308</v>
       </c>
       <c r="E210" t="n">
-        <v>102.240783691406</v>
+        <v>102.208679199219</v>
       </c>
       <c r="F210" t="n">
-        <v>78.69578</v>
+        <v>102.208679199219</v>
       </c>
       <c r="G210" t="n">
         <v>418.020657323971</v>
       </c>
       <c r="H210" t="n">
-        <v>155.817759607101</v>
+        <v>155.786532648632</v>
       </c>
     </row>
     <row r="211">
@@ -61928,22 +61865,22 @@
         <v>129.92</v>
       </c>
       <c r="C211" t="n">
-        <v>66.01023</v>
+        <v>66.12766</v>
       </c>
       <c r="D211" t="n">
-        <v>58.32963</v>
+        <v>58.33451</v>
       </c>
       <c r="E211" t="n">
-        <v>101.49845123291</v>
+        <v>101.703422546387</v>
       </c>
       <c r="F211" t="n">
-        <v>77.23929</v>
+        <v>101.703422546387</v>
       </c>
       <c r="G211" t="n">
         <v>382.526208884689</v>
       </c>
       <c r="H211" t="n">
-        <v>154.761315196965</v>
+        <v>154.893875816555</v>
       </c>
     </row>
     <row r="212">
@@ -61954,22 +61891,22 @@
         <v>129</v>
       </c>
       <c r="C212" t="n">
-        <v>66.42142</v>
+        <v>66.53959</v>
       </c>
       <c r="D212" t="n">
-        <v>58.52924</v>
+        <v>58.53413</v>
       </c>
       <c r="E212" t="n">
-        <v>105.580459594727</v>
+        <v>105.754432678223</v>
       </c>
       <c r="F212" t="n">
-        <v>80.6637</v>
+        <v>105.754432678223</v>
       </c>
       <c r="G212" t="n">
         <v>405.586054176021</v>
       </c>
       <c r="H212" t="n">
-        <v>157.669280309516</v>
+        <v>157.799684926874</v>
       </c>
     </row>
     <row r="213">
@@ -61980,22 +61917,22 @@
         <v>125.6</v>
       </c>
       <c r="C213" t="n">
-        <v>66.54962</v>
+        <v>66.66802</v>
       </c>
       <c r="D213" t="n">
-        <v>59.54864</v>
+        <v>59.52554</v>
       </c>
       <c r="E213" t="n">
-        <v>105.412628173828</v>
+        <v>105.496231079102</v>
       </c>
       <c r="F213" t="n">
-        <v>81.14625</v>
+        <v>105.496231079102</v>
       </c>
       <c r="G213" t="n">
         <v>430.858967545744</v>
       </c>
       <c r="H213" t="n">
-        <v>157.921551158011</v>
+        <v>157.82966686701</v>
       </c>
     </row>
     <row r="214">
@@ -62006,22 +61943,22 @@
         <v>124.6</v>
       </c>
       <c r="C214" t="n">
-        <v>66.51469</v>
+        <v>66.63302</v>
       </c>
       <c r="D214" t="n">
-        <v>58.42424</v>
+        <v>58.40103</v>
       </c>
       <c r="E214" t="n">
-        <v>100.704711914062</v>
+        <v>100.505714416504</v>
       </c>
       <c r="F214" t="n">
-        <v>80.36641</v>
+        <v>100.505714416504</v>
       </c>
       <c r="G214" t="n">
         <v>435.427555525409</v>
       </c>
       <c r="H214" t="n">
-        <v>156.593430912772</v>
+        <v>156.641209475501</v>
       </c>
     </row>
     <row r="215">
@@ -62032,22 +61969,22 @@
         <v>123.5</v>
       </c>
       <c r="C215" t="n">
-        <v>66.6077</v>
+        <v>66.7262</v>
       </c>
       <c r="D215" t="n">
-        <v>58.68067</v>
+        <v>58.68591</v>
       </c>
       <c r="E215" t="n">
-        <v>103.368240356445</v>
+        <v>102.995468139648</v>
       </c>
       <c r="F215" t="n">
-        <v>79.43369</v>
+        <v>102.995468139648</v>
       </c>
       <c r="G215" t="n">
         <v>408.707731777219</v>
       </c>
       <c r="H215" t="n">
-        <v>157.449996979865</v>
+        <v>157.494904067143</v>
       </c>
     </row>
     <row r="216">
@@ -62058,22 +61995,22 @@
         <v>126.56</v>
       </c>
       <c r="C216" t="n">
-        <v>66.59474</v>
+        <v>66.71322</v>
       </c>
       <c r="D216" t="n">
-        <v>59.22072</v>
+        <v>59.22601</v>
       </c>
       <c r="E216" t="n">
-        <v>102.702919006348</v>
+        <v>102.848419189453</v>
       </c>
       <c r="F216" t="n">
-        <v>78.89589</v>
+        <v>102.848419189453</v>
       </c>
       <c r="G216" t="n">
         <v>418.738691000236</v>
       </c>
       <c r="H216" t="n">
-        <v>156.906794490284</v>
+        <v>156.937372106745</v>
       </c>
     </row>
     <row r="217">
@@ -62084,22 +62021,22 @@
         <v>126.68</v>
       </c>
       <c r="C217" t="n">
-        <v>66.82254</v>
+        <v>66.94142</v>
       </c>
       <c r="D217" t="n">
-        <v>60.79853</v>
+        <v>60.80396</v>
       </c>
       <c r="E217" t="n">
-        <v>104.465019226074</v>
+        <v>104.57006072998</v>
       </c>
       <c r="F217" t="n">
-        <v>74.53812</v>
+        <v>104.57006072998</v>
       </c>
       <c r="G217" t="n">
         <v>411.141879592497</v>
       </c>
       <c r="H217" t="n">
-        <v>158.061628497733</v>
+        <v>158.075168054519</v>
       </c>
     </row>
     <row r="218">
@@ -62110,22 +62047,22 @@
         <v>123.52</v>
       </c>
       <c r="C218" t="n">
-        <v>67.02911</v>
+        <v>67.14836</v>
       </c>
       <c r="D218" t="n">
-        <v>59.93613</v>
+        <v>59.94148</v>
       </c>
       <c r="E218" t="n">
-        <v>102.629348754883</v>
+        <v>102.69718170166</v>
       </c>
       <c r="F218" t="n">
-        <v>76.15361</v>
+        <v>102.69718170166</v>
       </c>
       <c r="G218" t="n">
         <v>412.363224733081</v>
       </c>
       <c r="H218" t="n">
-        <v>158.202303347096</v>
+        <v>158.190562927199</v>
       </c>
     </row>
     <row r="219">
@@ -62136,22 +62073,22 @@
         <v>125.7</v>
       </c>
       <c r="C219" t="n">
-        <v>67.47216</v>
+        <v>67.5922</v>
       </c>
       <c r="D219" t="n">
-        <v>60.75815</v>
+        <v>60.76358</v>
       </c>
       <c r="E219" t="n">
-        <v>106.569496154785</v>
+        <v>106.433670043945</v>
       </c>
       <c r="F219" t="n">
-        <v>78.02142</v>
+        <v>106.433670043945</v>
       </c>
       <c r="G219" t="n">
         <v>430.719432270171</v>
       </c>
       <c r="H219" t="n">
-        <v>160.943949264101</v>
+        <v>160.88138440259</v>
       </c>
     </row>
     <row r="220">
@@ -62162,22 +62099,22 @@
         <v>126.61</v>
       </c>
       <c r="C220" t="n">
-        <v>67.54476</v>
+        <v>67.66493</v>
       </c>
       <c r="D220" t="n">
-        <v>60.41472</v>
+        <v>60.36269</v>
       </c>
       <c r="E220" t="n">
-        <v>104.878189086914</v>
+        <v>105.783615112305</v>
       </c>
       <c r="F220" t="n">
-        <v>76.45459</v>
+        <v>105.783615112305</v>
       </c>
       <c r="G220" t="n">
         <v>452.362298444493</v>
       </c>
       <c r="H220" t="n">
-        <v>159.973457250038</v>
+        <v>160.136503592806</v>
       </c>
     </row>
     <row r="221">
@@ -62188,22 +62125,22 @@
         <v>122.41</v>
       </c>
       <c r="C221" t="n">
-        <v>67.72707</v>
+        <v>67.84756</v>
       </c>
       <c r="D221" t="n">
-        <v>60.35762</v>
+        <v>60.33414</v>
       </c>
       <c r="E221" t="n">
-        <v>105.419578552246</v>
+        <v>105.972724914551</v>
       </c>
       <c r="F221" t="n">
-        <v>77.12138</v>
+        <v>105.972724914551</v>
       </c>
       <c r="G221" t="n">
         <v>448.731665832311</v>
       </c>
       <c r="H221" t="n">
-        <v>160.659743381641</v>
+        <v>160.873131509333</v>
       </c>
     </row>
     <row r="222">
@@ -62214,22 +62151,22 @@
         <v>113.77</v>
       </c>
       <c r="C222" t="n">
-        <v>67.94479</v>
+        <v>68.06567</v>
       </c>
       <c r="D222" t="n">
-        <v>62.32293</v>
+        <v>62.32722</v>
       </c>
       <c r="E222" t="n">
-        <v>108.531898498535</v>
+        <v>108.46216583252</v>
       </c>
       <c r="F222" t="n">
-        <v>76.17813</v>
+        <v>108.46216583252</v>
       </c>
       <c r="G222" t="n">
         <v>431.856740480751</v>
       </c>
       <c r="H222" t="n">
-        <v>162.778845396845</v>
+        <v>162.652388343826</v>
       </c>
     </row>
     <row r="223">
@@ -62240,22 +62177,22 @@
         <v>118.95</v>
       </c>
       <c r="C223" t="n">
-        <v>68.04692</v>
+        <v>68.16799</v>
       </c>
       <c r="D223" t="n">
-        <v>61.0842</v>
+        <v>61.08841</v>
       </c>
       <c r="E223" t="n">
-        <v>105.622421264648</v>
+        <v>105.825477600098</v>
       </c>
       <c r="F223" t="n">
-        <v>76.46107</v>
+        <v>105.825477600098</v>
       </c>
       <c r="G223" t="n">
         <v>400.0356189913</v>
       </c>
       <c r="H223" t="n">
-        <v>163.462516547512</v>
+        <v>163.470529857196</v>
       </c>
     </row>
     <row r="224">
@@ -62266,22 +62203,22 @@
         <v>120.34</v>
       </c>
       <c r="C224" t="n">
-        <v>68.2123</v>
+        <v>68.33366</v>
       </c>
       <c r="D224" t="n">
-        <v>62.43793</v>
+        <v>62.44223</v>
       </c>
       <c r="E224" t="n">
-        <v>106.060180664062</v>
+        <v>106.196563720703</v>
       </c>
       <c r="F224" t="n">
-        <v>77.23493</v>
+        <v>106.196563720703</v>
       </c>
       <c r="G224" t="n">
         <v>390.086200121441</v>
       </c>
       <c r="H224" t="n">
-        <v>163.462516547512</v>
+        <v>163.472164562494</v>
       </c>
     </row>
     <row r="225">
@@ -62292,22 +62229,22 @@
         <v>123.06</v>
       </c>
       <c r="C225" t="n">
-        <v>68.27642</v>
+        <v>68.39789</v>
       </c>
       <c r="D225" t="n">
-        <v>63.17484</v>
+        <v>63.151</v>
       </c>
       <c r="E225" t="n">
-        <v>107.475784301758</v>
+        <v>107.576789855957</v>
       </c>
       <c r="F225" t="n">
-        <v>73.05058</v>
+        <v>107.576789855957</v>
       </c>
       <c r="G225" t="n">
         <v>410.628833999784</v>
       </c>
       <c r="H225" t="n">
-        <v>163.818864833585</v>
+        <v>163.745163077314</v>
       </c>
     </row>
     <row r="226">
@@ -62318,22 +62255,22 @@
         <v>124.39</v>
       </c>
       <c r="C226" t="n">
-        <v>68.41539</v>
+        <v>68.53711</v>
       </c>
       <c r="D226" t="n">
-        <v>62.0531</v>
+        <v>62.0872</v>
       </c>
       <c r="E226" t="n">
-        <v>107.242248535156</v>
+        <v>108.343757629395</v>
       </c>
       <c r="F226" t="n">
-        <v>75.64643</v>
+        <v>108.343757629395</v>
       </c>
       <c r="G226" t="n">
         <v>430.117401872391</v>
       </c>
       <c r="H226" t="n">
-        <v>163.94172898221</v>
+        <v>164.108677339345</v>
       </c>
     </row>
     <row r="227">
@@ -62344,22 +62281,22 @@
         <v>126.02</v>
       </c>
       <c r="C227" t="n">
-        <v>68.66568</v>
+        <v>68.78784</v>
       </c>
       <c r="D227" t="n">
-        <v>63.71245</v>
+        <v>63.71894</v>
       </c>
       <c r="E227" t="n">
-        <v>107.652740478516</v>
+        <v>107.888885498047</v>
       </c>
       <c r="F227" t="n">
-        <v>77.16476</v>
+        <v>107.888885498047</v>
       </c>
       <c r="G227" t="n">
         <v>402.894613479197</v>
       </c>
       <c r="H227" t="n">
-        <v>165.454911140716</v>
+        <v>165.472420448035</v>
       </c>
     </row>
     <row r="228">
@@ -62370,22 +62307,22 @@
         <v>123.93</v>
       </c>
       <c r="C228" t="n">
-        <v>68.80056</v>
+        <v>68.92296</v>
       </c>
       <c r="D228" t="n">
-        <v>63.0537</v>
+        <v>63.03132</v>
       </c>
       <c r="E228" t="n">
-        <v>108.612739562988</v>
+        <v>108.636413574219</v>
       </c>
       <c r="F228" t="n">
-        <v>77.86269</v>
+        <v>108.636413574219</v>
       </c>
       <c r="G228" t="n">
         <v>377.528382629917</v>
       </c>
       <c r="H228" t="n">
-        <v>165.757693628104</v>
+        <v>165.775234977455</v>
       </c>
     </row>
     <row r="229">
@@ -62396,22 +62333,22 @@
         <v>120.8</v>
       </c>
       <c r="C229" t="n">
-        <v>68.87124</v>
+        <v>68.99377</v>
       </c>
       <c r="D229" t="n">
-        <v>62.79674</v>
+        <v>62.80294</v>
       </c>
       <c r="E229" t="n">
-        <v>105.711875915527</v>
+        <v>105.931678771973</v>
       </c>
       <c r="F229" t="n">
-        <v>77.94138</v>
+        <v>105.931678771973</v>
       </c>
       <c r="G229" t="n">
         <v>388.775963719798</v>
       </c>
       <c r="H229" t="n">
-        <v>164.662035273222</v>
+        <v>164.732508749447</v>
       </c>
     </row>
     <row r="230">
@@ -62422,22 +62359,22 @@
         <v>121.5</v>
       </c>
       <c r="C230" t="n">
-        <v>69.32378</v>
+        <v>69.44712</v>
       </c>
       <c r="D230" t="n">
-        <v>64.78778</v>
+        <v>64.79419</v>
       </c>
       <c r="E230" t="n">
-        <v>109.925979614258</v>
+        <v>110.126724243164</v>
       </c>
       <c r="F230" t="n">
-        <v>78.12507</v>
+        <v>110.126724243164</v>
       </c>
       <c r="G230" t="n">
         <v>377.756271741022</v>
       </c>
       <c r="H230" t="n">
-        <v>167.718162647893</v>
+        <v>167.926672094099</v>
       </c>
     </row>
     <row r="231">
@@ -62448,22 +62385,22 @@
         <v>121.1</v>
       </c>
       <c r="C231" t="n">
-        <v>69.70436</v>
+        <v>69.82837</v>
       </c>
       <c r="D231" t="n">
-        <v>64.55956</v>
+        <v>64.56594</v>
       </c>
       <c r="E231" t="n">
-        <v>109.68236541748</v>
+        <v>109.54354095459</v>
       </c>
       <c r="F231" t="n">
-        <v>81.17655</v>
+        <v>109.54354095459</v>
       </c>
       <c r="G231" t="n">
         <v>406.211349515929</v>
       </c>
       <c r="H231" t="n">
-        <v>167.746674735543</v>
+        <v>167.820878290679</v>
       </c>
     </row>
     <row r="232">
@@ -62474,22 +62411,22 @@
         <v>126.24</v>
       </c>
       <c r="C232" t="n">
-        <v>69.89929</v>
+        <v>70.02364</v>
       </c>
       <c r="D232" t="n">
-        <v>63.84365</v>
+        <v>63.87876</v>
       </c>
       <c r="E232" t="n">
-        <v>109.949111938477</v>
+        <v>109.191749572754</v>
       </c>
       <c r="F232" t="n">
-        <v>75.45274</v>
+        <v>109.191749572754</v>
       </c>
       <c r="G232" t="n">
         <v>400.511455824967</v>
       </c>
       <c r="H232" t="n">
-        <v>167.199820575905</v>
+        <v>167.015338074884</v>
       </c>
     </row>
     <row r="233">
@@ -62500,22 +62437,22 @@
         <v>126.56</v>
       </c>
       <c r="C233" t="n">
-        <v>69.96622</v>
+        <v>70.0907</v>
       </c>
       <c r="D233" t="n">
-        <v>64.32592</v>
+        <v>64.3328</v>
       </c>
       <c r="E233" t="n">
-        <v>108.349159240723</v>
+        <v>108.53564453125</v>
       </c>
       <c r="F233" t="n">
-        <v>73.90757</v>
+        <v>108.53564453125</v>
       </c>
       <c r="G233" t="n">
         <v>404.660573204323</v>
       </c>
       <c r="H233" t="n">
-        <v>167.462324294209</v>
+        <v>167.508033322205</v>
       </c>
     </row>
     <row r="234">
@@ -62526,22 +62463,22 @@
         <v>127.49</v>
       </c>
       <c r="C234" t="n">
-        <v>70.05615</v>
+        <v>70.18079</v>
       </c>
       <c r="D234" t="n">
-        <v>64.49655</v>
+        <v>64.50345</v>
       </c>
       <c r="E234" t="n">
-        <v>108.340553283691</v>
+        <v>108.311882019043</v>
       </c>
       <c r="F234" t="n">
-        <v>75.86228</v>
+        <v>108.311882019043</v>
       </c>
       <c r="G234" t="n">
         <v>403.477851186579</v>
       </c>
       <c r="H234" t="n">
-        <v>168.356573105941</v>
+        <v>168.363999372482</v>
       </c>
     </row>
     <row r="235">
@@ -62552,22 +62489,22 @@
         <v>123.25</v>
       </c>
       <c r="C235" t="n">
-        <v>70.21637</v>
+        <v>70.34129</v>
       </c>
       <c r="D235" t="n">
-        <v>66.23829</v>
+        <v>66.24537</v>
       </c>
       <c r="E235" t="n">
-        <v>109.670867919922</v>
+        <v>109.798309326172</v>
       </c>
       <c r="F235" t="n">
-        <v>76.12608</v>
+        <v>109.798309326172</v>
       </c>
       <c r="G235" t="n">
         <v>415.117781462886</v>
       </c>
       <c r="H235" t="n">
-        <v>169.327990532762</v>
+        <v>169.369132448735</v>
       </c>
     </row>
     <row r="236">
@@ -62578,22 +62515,22 @@
         <v>130.39</v>
       </c>
       <c r="C236" t="n">
-        <v>70.12844</v>
+        <v>70.2532</v>
       </c>
       <c r="D236" t="n">
-        <v>62.52083</v>
+        <v>62.55762</v>
       </c>
       <c r="E236" t="n">
-        <v>105.371765136719</v>
+        <v>105.489685058594</v>
       </c>
       <c r="F236" t="n">
-        <v>75.95308</v>
+        <v>105.489685058594</v>
       </c>
       <c r="G236" t="n">
         <v>402.300409612435</v>
       </c>
       <c r="H236" t="n">
-        <v>167.666882945635</v>
+        <v>167.782143677691</v>
       </c>
     </row>
     <row r="237">
@@ -62604,22 +62541,22 @@
         <v>135.58</v>
       </c>
       <c r="C237" t="n">
-        <v>70.30666</v>
+        <v>70.43175</v>
       </c>
       <c r="D237" t="n">
-        <v>65.2728</v>
+        <v>65.28278</v>
       </c>
       <c r="E237" t="n">
-        <v>107.960708618164</v>
+        <v>108.050605773926</v>
       </c>
       <c r="F237" t="n">
-        <v>77.37172</v>
+        <v>108.050605773926</v>
       </c>
       <c r="G237" t="n">
         <v>383.885385541075</v>
       </c>
       <c r="H237" t="n">
-        <v>168.750011009464</v>
+        <v>168.708301110791</v>
       </c>
     </row>
     <row r="238">
@@ -62630,22 +62567,22 @@
         <v>128.57</v>
       </c>
       <c r="C238" t="n">
-        <v>70.98249</v>
+        <v>71.10877</v>
       </c>
       <c r="D238" t="n">
-        <v>67.28565</v>
+        <v>67.2684</v>
       </c>
       <c r="E238" t="n">
-        <v>112.247917175293</v>
+        <v>112.677597045898</v>
       </c>
       <c r="F238" t="n">
-        <v>80.65749</v>
+        <v>112.677597045898</v>
       </c>
       <c r="G238" t="n">
         <v>385.262451679141</v>
       </c>
       <c r="H238" t="n">
-        <v>172.184073733507</v>
+        <v>172.205624192818</v>
       </c>
     </row>
     <row r="239">
@@ -62656,22 +62593,22 @@
         <v>126.16</v>
       </c>
       <c r="C239" t="n">
-        <v>71.38647</v>
+        <v>71.51347</v>
       </c>
       <c r="D239" t="n">
-        <v>68.04755</v>
+        <v>68.08652</v>
       </c>
       <c r="E239" t="n">
-        <v>110.610580444336</v>
+        <v>110.840049743652</v>
       </c>
       <c r="F239" t="n">
-        <v>79.83919</v>
+        <v>110.840049743652</v>
       </c>
       <c r="G239" t="n">
         <v>358.237642938385</v>
       </c>
       <c r="H239" t="n">
-        <v>171.763944593597</v>
+        <v>171.826771819594</v>
       </c>
     </row>
     <row r="240">
@@ -62682,22 +62619,22 @@
         <v>121.13</v>
       </c>
       <c r="C240" t="n">
-        <v>71.6928</v>
+        <v>71.82035</v>
       </c>
       <c r="D240" t="n">
-        <v>66.84516</v>
+        <v>66.82616</v>
       </c>
       <c r="E240" t="n">
-        <v>110.672058105469</v>
+        <v>110.745597839355</v>
       </c>
       <c r="F240" t="n">
-        <v>78.89811</v>
+        <v>110.745597839355</v>
       </c>
       <c r="G240" t="n">
         <v>331.078844148881</v>
       </c>
       <c r="H240" t="n">
-        <v>172.011284673812</v>
+        <v>171.988288985104</v>
       </c>
     </row>
     <row r="241">
@@ -62708,22 +62645,22 @@
         <v>121.21</v>
       </c>
       <c r="C241" t="n">
-        <v>71.93579</v>
+        <v>72.06377</v>
       </c>
       <c r="D241" t="n">
-        <v>67.80292</v>
+        <v>67.81202</v>
       </c>
       <c r="E241" t="n">
-        <v>112.560676574707</v>
+        <v>112.637153625488</v>
       </c>
       <c r="F241" t="n">
-        <v>78.55788</v>
+        <v>112.637153625488</v>
       </c>
       <c r="G241" t="n">
         <v>265.574269459142</v>
       </c>
       <c r="H241" t="n">
-        <v>172.050847269287</v>
+        <v>172.105241021614</v>
       </c>
     </row>
     <row r="242">
@@ -62734,22 +62671,22 @@
         <v>124.6</v>
       </c>
       <c r="C242" t="n">
-        <v>72.2032</v>
+        <v>72.33166</v>
       </c>
       <c r="D242" t="n">
-        <v>67.77455</v>
+        <v>67.78364</v>
       </c>
       <c r="E242" t="n">
-        <v>111.987724304199</v>
+        <v>111.93620300293</v>
       </c>
       <c r="F242" t="n">
-        <v>78.8484</v>
+        <v>111.93620300293</v>
       </c>
       <c r="G242" t="n">
         <v>214.053808539293</v>
       </c>
       <c r="H242" t="n">
-        <v>171.192313541413</v>
+        <v>171.129404305022</v>
       </c>
     </row>
     <row r="243">
@@ -62760,22 +62697,22 @@
         <v>131.87</v>
       </c>
       <c r="C243" t="n">
-        <v>72.54347</v>
+        <v>72.67253</v>
       </c>
       <c r="D243" t="n">
-        <v>67.97285</v>
+        <v>67.98196</v>
       </c>
       <c r="E243" t="n">
-        <v>112.685745239258</v>
+        <v>112.580673217773</v>
       </c>
       <c r="F243" t="n">
-        <v>79.96585</v>
+        <v>112.580673217773</v>
       </c>
       <c r="G243" t="n">
         <v>228.273466880429</v>
       </c>
       <c r="H243" t="n">
-        <v>171.957543182943</v>
+        <v>171.766005689036</v>
       </c>
     </row>
     <row r="244">
@@ -62786,22 +62723,22 @@
         <v>130.1</v>
       </c>
       <c r="C244" t="n">
-        <v>72.6834</v>
+        <v>72.81271</v>
       </c>
       <c r="D244" t="n">
-        <v>69.65404</v>
+        <v>69.58029</v>
       </c>
       <c r="E244" t="n">
-        <v>111.933746337891</v>
+        <v>113.257949829102</v>
       </c>
       <c r="F244" t="n">
-        <v>79.28621</v>
+        <v>113.257949829102</v>
       </c>
       <c r="G244" t="n">
         <v>218.599498134684</v>
       </c>
       <c r="H244" t="n">
-        <v>172.270505911536</v>
+        <v>172.617965077254</v>
       </c>
     </row>
     <row r="245">
@@ -62812,22 +62749,22 @@
         <v>131.9</v>
       </c>
       <c r="C245" t="n">
-        <v>72.75795</v>
+        <v>72.88739</v>
       </c>
       <c r="D245" t="n">
-        <v>68.91273</v>
+        <v>68.89617</v>
       </c>
       <c r="E245" t="n">
-        <v>113.605979919434</v>
+        <v>113.270439147949</v>
       </c>
       <c r="F245" t="n">
-        <v>77.80846</v>
+        <v>113.270439147949</v>
       </c>
       <c r="G245" t="n">
         <v>245.85432422616</v>
       </c>
       <c r="H245" t="n">
-        <v>171.820879891107</v>
+        <v>171.723804018154</v>
       </c>
     </row>
     <row r="246">
@@ -62838,22 +62775,22 @@
         <v>129.37</v>
       </c>
       <c r="C246" t="n">
-        <v>72.93086</v>
+        <v>73.06061</v>
       </c>
       <c r="D246" t="n">
-        <v>70.67659</v>
+        <v>70.66032</v>
       </c>
       <c r="E246" t="n">
-        <v>113.217803955078</v>
+        <v>113.209785461426</v>
       </c>
       <c r="F246" t="n">
-        <v>77.33625</v>
+        <v>113.209785461426</v>
       </c>
       <c r="G246" t="n">
         <v>261.796480895744</v>
       </c>
       <c r="H246" t="n">
-        <v>172.396479838742</v>
+        <v>172.481105993874</v>
       </c>
     </row>
     <row r="247">
@@ -62864,22 +62801,22 @@
         <v>130.49</v>
       </c>
       <c r="C247" t="n">
-        <v>73.28109</v>
+        <v>73.41146</v>
       </c>
       <c r="D247" t="n">
-        <v>70.5347</v>
+        <v>70.5184</v>
       </c>
       <c r="E247" t="n">
-        <v>115.105247497559</v>
+        <v>115.204376220703</v>
       </c>
       <c r="F247" t="n">
-        <v>79.9666</v>
+        <v>115.204376220703</v>
       </c>
       <c r="G247" t="n">
         <v>260.955205132106</v>
       </c>
       <c r="H247" t="n">
-        <v>173.268806026726</v>
+        <v>173.362484445503</v>
       </c>
     </row>
     <row r="248">
@@ -62890,22 +62827,22 @@
         <v>128.61</v>
       </c>
       <c r="C248" t="n">
-        <v>73.55558</v>
+        <v>73.68645</v>
       </c>
       <c r="D248" t="n">
-        <v>70.47797</v>
+        <v>70.49005</v>
       </c>
       <c r="E248" t="n">
-        <v>114.232711791992</v>
+        <v>114.295265197754</v>
       </c>
       <c r="F248" t="n">
-        <v>77.0411</v>
+        <v>114.295265197754</v>
       </c>
       <c r="G248" t="n">
         <v>219.550740676</v>
       </c>
       <c r="H248" t="n">
-        <v>172.345283290604</v>
+        <v>172.526877270475</v>
       </c>
     </row>
     <row r="249">
@@ -62916,22 +62853,22 @@
         <v>130.11</v>
       </c>
       <c r="C249" t="n">
-        <v>74.01906</v>
+        <v>74.15075</v>
       </c>
       <c r="D249" t="n">
-        <v>71.8814</v>
+        <v>71.89372</v>
       </c>
       <c r="E249" t="n">
-        <v>117.515815734863</v>
+        <v>117.606475830078</v>
       </c>
       <c r="F249" t="n">
-        <v>79.41278</v>
+        <v>117.606475830078</v>
       </c>
       <c r="G249" t="n">
         <v>188.002196063462</v>
       </c>
       <c r="H249" t="n">
-        <v>173.439675839499</v>
+        <v>173.506829933372</v>
       </c>
     </row>
     <row r="250">
@@ -62942,22 +62879,22 @@
         <v>131.45</v>
       </c>
       <c r="C250" t="n">
-        <v>74.23643</v>
+        <v>74.3685</v>
       </c>
       <c r="D250" t="n">
-        <v>72.97842</v>
+        <v>72.99092</v>
       </c>
       <c r="E250" t="n">
-        <v>116.435737609863</v>
+        <v>115.865539550781</v>
       </c>
       <c r="F250" t="n">
-        <v>78.00915</v>
+        <v>115.865539550781</v>
       </c>
       <c r="G250" t="n">
         <v>203.805071622606</v>
       </c>
       <c r="H250" t="n">
-        <v>172.263754837307</v>
+        <v>172.099689542612</v>
       </c>
     </row>
     <row r="251">
@@ -62968,22 +62905,22 @@
         <v>129.48</v>
       </c>
       <c r="C251" t="n">
-        <v>74.44462</v>
+        <v>74.57707</v>
       </c>
       <c r="D251" t="n">
-        <v>72.29505</v>
+        <v>72.30743</v>
       </c>
       <c r="E251" t="n">
-        <v>116.760543823242</v>
+        <v>116.908325195312</v>
       </c>
       <c r="F251" t="n">
-        <v>76.86587</v>
+        <v>116.908325195312</v>
       </c>
       <c r="G251" t="n">
         <v>204.290568769436</v>
       </c>
       <c r="H251" t="n">
-        <v>173.276665715751</v>
+        <v>173.335365313528</v>
       </c>
     </row>
     <row r="252">
@@ -62994,22 +62931,22 @@
         <v>128.25</v>
       </c>
       <c r="C252" t="n">
-        <v>74.84954</v>
+        <v>74.9827</v>
       </c>
       <c r="D252" t="n">
-        <v>73.97575</v>
+        <v>73.98842</v>
       </c>
       <c r="E252" t="n">
-        <v>118.41820526123</v>
+        <v>118.594581604004</v>
       </c>
       <c r="F252" t="n">
-        <v>83.50523</v>
+        <v>118.594581604004</v>
       </c>
       <c r="G252" t="n">
         <v>189.363800208266</v>
       </c>
       <c r="H252" t="n">
-        <v>174.654215208191</v>
+        <v>174.659647504523</v>
       </c>
     </row>
     <row r="253">
@@ -63020,22 +62957,22 @@
         <v>133.8</v>
       </c>
       <c r="C253" t="n">
-        <v>75.10689</v>
+        <v>75.24051</v>
       </c>
       <c r="D253" t="n">
-        <v>74.17381</v>
+        <v>74.18651</v>
       </c>
       <c r="E253" t="n">
-        <v>118.233589172363</v>
+        <v>118.224243164062</v>
       </c>
       <c r="F253" t="n">
-        <v>80.29373</v>
+        <v>118.224243164062</v>
       </c>
       <c r="G253" t="n">
         <v>165.973889681544</v>
       </c>
       <c r="H253" t="n">
-        <v>173.471806171231</v>
+        <v>173.491174462718</v>
       </c>
     </row>
     <row r="254">
@@ -63046,22 +62983,22 @@
         <v>128.76</v>
       </c>
       <c r="C254" t="n">
-        <v>75.37032</v>
+        <v>75.50441</v>
       </c>
       <c r="D254" t="n">
-        <v>74.7383</v>
+        <v>74.72298</v>
       </c>
       <c r="E254" t="n">
-        <v>119.101867675781</v>
+        <v>119.294158935547</v>
       </c>
       <c r="F254" t="n">
-        <v>78.84842</v>
+        <v>119.294158935547</v>
       </c>
       <c r="G254" t="n">
         <v>144.156151219199</v>
       </c>
       <c r="H254" t="n">
-        <v>173.395478576516</v>
+        <v>173.572715314716</v>
       </c>
     </row>
     <row r="255">
@@ -63072,22 +63009,22 @@
         <v>128.59</v>
       </c>
       <c r="C255" t="n">
-        <v>75.54076</v>
+        <v>75.67515</v>
       </c>
       <c r="D255" t="n">
-        <v>74.76662</v>
+        <v>74.77963</v>
       </c>
       <c r="E255" t="n">
-        <v>117.90803527832</v>
+        <v>117.741134643555</v>
       </c>
       <c r="F255" t="n">
-        <v>78.42628</v>
+        <v>117.741134643555</v>
       </c>
       <c r="G255" t="n">
         <v>137.371719645762</v>
       </c>
       <c r="H255" t="n">
-        <v>173.019210388005</v>
+        <v>173.194326795329</v>
       </c>
     </row>
     <row r="256">
@@ -63098,22 +63035,22 @@
         <v>131.1</v>
       </c>
       <c r="C256" t="n">
-        <v>75.97382</v>
+        <v>76.10898</v>
       </c>
       <c r="D256" t="n">
-        <v>76.36433</v>
+        <v>76.40534</v>
       </c>
       <c r="E256" t="n">
-        <v>120.860054016113</v>
+        <v>119.516311645508</v>
       </c>
       <c r="F256" t="n">
-        <v>80.33792</v>
+        <v>119.516311645508</v>
       </c>
       <c r="G256" t="n">
         <v>168.6791503943</v>
       </c>
       <c r="H256" t="n">
-        <v>175.744262951616</v>
+        <v>175.475296079224</v>
       </c>
     </row>
     <row r="257">
@@ -63124,22 +63061,22 @@
         <v>134.62</v>
       </c>
       <c r="C257" t="n">
-        <v>76.14914</v>
+        <v>76.28461</v>
       </c>
       <c r="D257" t="n">
-        <v>76.50582</v>
+        <v>76.49028</v>
       </c>
       <c r="E257" t="n">
-        <v>120.563079833984</v>
+        <v>120.460731506348</v>
       </c>
       <c r="F257" t="n">
-        <v>79.28191</v>
+        <v>120.460731506348</v>
       </c>
       <c r="G257" t="n">
         <v>178.146131692989</v>
       </c>
       <c r="H257" t="n">
-        <v>178.014878828951</v>
+        <v>178.054782931588</v>
       </c>
     </row>
     <row r="258">
@@ -63150,22 +63087,22 @@
         <v>132.86</v>
       </c>
       <c r="C258" t="n">
-        <v>76.49069</v>
+        <v>76.62677</v>
       </c>
       <c r="D258" t="n">
-        <v>76.02277</v>
+        <v>76.03565</v>
       </c>
       <c r="E258" t="n">
-        <v>121.082023620605</v>
+        <v>121.05362701416</v>
       </c>
       <c r="F258" t="n">
-        <v>80.64913</v>
+        <v>121.05362701416</v>
       </c>
       <c r="G258" t="n">
         <v>205.452748651121</v>
       </c>
       <c r="H258" t="n">
-        <v>179.430097115641</v>
+        <v>179.493465577676</v>
       </c>
     </row>
     <row r="259">
@@ -63176,22 +63113,22 @@
         <v>131.93</v>
       </c>
       <c r="C259" t="n">
-        <v>76.86809</v>
+        <v>77.00484</v>
       </c>
       <c r="D259" t="n">
-        <v>77.64809</v>
+        <v>77.63351</v>
       </c>
       <c r="E259" t="n">
-        <v>122.871055603027</v>
+        <v>122.956680297852</v>
       </c>
       <c r="F259" t="n">
-        <v>80.26793</v>
+        <v>122.956680297852</v>
       </c>
       <c r="G259" t="n">
         <v>216.218715144388</v>
       </c>
       <c r="H259" t="n">
-        <v>180.404402542979</v>
+        <v>180.390932905564</v>
       </c>
     </row>
     <row r="260">
@@ -63202,22 +63139,22 @@
         <v>132.14</v>
       </c>
       <c r="C260" t="n">
-        <v>77.09424</v>
+        <v>77.23139</v>
       </c>
       <c r="D260" t="n">
-        <v>78.2405</v>
+        <v>78.25413</v>
       </c>
       <c r="E260" t="n">
-        <v>122.469635009766</v>
+        <v>122.507736206055</v>
       </c>
       <c r="F260" t="n">
-        <v>78.86736</v>
+        <v>122.507736206055</v>
       </c>
       <c r="G260" t="n">
         <v>197.255765098037</v>
       </c>
       <c r="H260" t="n">
-        <v>180.777839656243</v>
+        <v>180.728263950097</v>
       </c>
     </row>
     <row r="261">
@@ -63228,22 +63165,22 @@
         <v>133.56</v>
       </c>
       <c r="C261" t="n">
-        <v>77.03358</v>
+        <v>77.17063</v>
       </c>
       <c r="D261" t="n">
-        <v>77.27174</v>
+        <v>77.25652</v>
       </c>
       <c r="E261" t="n">
-        <v>120.157470703125</v>
+        <v>120.225364685059</v>
       </c>
       <c r="F261" t="n">
-        <v>78.70687</v>
+        <v>120.225364685059</v>
       </c>
       <c r="G261" t="n">
         <v>194.98793606818</v>
       </c>
       <c r="H261" t="n">
-        <v>179.465392540339</v>
+        <v>179.472202515644</v>
       </c>
     </row>
     <row r="262">
@@ -63254,22 +63191,22 @@
         <v>130.52</v>
       </c>
       <c r="C262" t="n">
-        <v>77.35715</v>
+        <v>77.49477</v>
       </c>
       <c r="D262" t="n">
-        <v>77.75161</v>
+        <v>77.76461</v>
       </c>
       <c r="E262" t="n">
-        <v>124.120864868164</v>
+        <v>124.578727722168</v>
       </c>
       <c r="F262" t="n">
-        <v>78.56338</v>
+        <v>124.578727722168</v>
       </c>
       <c r="G262" t="n">
         <v>195.486524011256</v>
       </c>
       <c r="H262" t="n">
-        <v>182.449902018285</v>
+        <v>182.589634673341</v>
       </c>
     </row>
     <row r="263">
@@ -63280,22 +63217,22 @@
         <v>135.22</v>
       </c>
       <c r="C263" t="n">
-        <v>77.34246</v>
+        <v>77.48006</v>
       </c>
       <c r="D263" t="n">
-        <v>77.41109</v>
+        <v>77.33866</v>
       </c>
       <c r="E263" t="n">
-        <v>121.687660217285</v>
+        <v>120.796920776367</v>
       </c>
       <c r="F263" t="n">
-        <v>76.84389</v>
+        <v>120.796920776367</v>
       </c>
       <c r="G263" t="n">
         <v>218.294763441937</v>
       </c>
       <c r="H263" t="n">
-        <v>181.256679659085</v>
+        <v>181.190998071743</v>
       </c>
     </row>
     <row r="264">
@@ -63306,22 +63243,22 @@
         <v>136.13</v>
       </c>
       <c r="C264" t="n">
-        <v>77.7005</v>
+        <v>77.83873</v>
       </c>
       <c r="D264" t="n">
-        <v>79.50605</v>
+        <v>79.48902</v>
       </c>
       <c r="E264" t="n">
-        <v>122.574668884277</v>
+        <v>122.69465637207</v>
       </c>
       <c r="F264" t="n">
-        <v>79.91753</v>
+        <v>122.69465637207</v>
       </c>
       <c r="G264" t="n">
         <v>202.385831758158</v>
       </c>
       <c r="H264" t="n">
-        <v>183.613016494653</v>
+        <v>183.751226874497</v>
       </c>
     </row>
     <row r="265">
@@ -63332,22 +63269,22 @@
         <v>134.3</v>
       </c>
       <c r="C265" t="n">
-        <v>77.97327</v>
+        <v>78.11199</v>
       </c>
       <c r="D265" t="n">
-        <v>79.90132</v>
+        <v>79.91252</v>
       </c>
       <c r="E265" t="n">
-        <v>123.868675231934</v>
+        <v>123.656898498535</v>
       </c>
       <c r="F265" t="n">
-        <v>80.33326</v>
+        <v>123.656898498535</v>
       </c>
       <c r="G265" t="n">
         <v>229.242106865053</v>
       </c>
       <c r="H265" t="n">
-        <v>185.193924566672</v>
+        <v>185.202861566806</v>
       </c>
     </row>
     <row r="266">
@@ -63358,22 +63295,22 @@
         <v>133.18</v>
       </c>
       <c r="C266" t="n">
-        <v>78.15143</v>
+        <v>78.29047</v>
       </c>
       <c r="D266" t="n">
-        <v>80.66189</v>
+        <v>80.67319</v>
       </c>
       <c r="E266" t="n">
-        <v>123.802291870117</v>
+        <v>123.970306396484</v>
       </c>
       <c r="F266" t="n">
-        <v>80.17805</v>
+        <v>123.970306396484</v>
       </c>
       <c r="G266" t="n">
         <v>231.461737600006</v>
       </c>
       <c r="H266" t="n">
-        <v>183.692001838436</v>
+        <v>183.876809077987</v>
       </c>
     </row>
     <row r="267">
@@ -63384,22 +63321,22 @@
         <v>135.66</v>
       </c>
       <c r="C267" t="n">
-        <v>78.25837</v>
+        <v>78.3976</v>
       </c>
       <c r="D267" t="n">
-        <v>81.28216</v>
+        <v>81.29355</v>
       </c>
       <c r="E267" t="n">
-        <v>125.135795593262</v>
+        <v>125.092735290527</v>
       </c>
       <c r="F267" t="n">
-        <v>77.52192</v>
+        <v>125.092735290527</v>
       </c>
       <c r="G267" t="n">
         <v>230.190593617189</v>
       </c>
       <c r="H267" t="n">
-        <v>183.486266796377</v>
+        <v>183.547669589738</v>
       </c>
     </row>
     <row r="268">
@@ -63410,22 +63347,22 @@
         <v>136.9</v>
       </c>
       <c r="C268" t="n">
-        <v>78.81699</v>
+        <v>78.95721</v>
       </c>
       <c r="D268" t="n">
-        <v>81.81811</v>
+        <v>81.82958</v>
       </c>
       <c r="E268" t="n">
-        <v>126.058395385742</v>
+        <v>125.943244934082</v>
       </c>
       <c r="F268" t="n">
-        <v>81.56898</v>
+        <v>125.943244934082</v>
       </c>
       <c r="G268" t="n">
         <v>207.201157827684</v>
       </c>
       <c r="H268" t="n">
-        <v>184.834890857331</v>
+        <v>184.674652281019</v>
       </c>
     </row>
     <row r="269">
@@ -63436,22 +63373,22 @@
         <v>136.32</v>
       </c>
       <c r="C269" t="n">
-        <v>79.20584</v>
+        <v>79.34675</v>
       </c>
       <c r="D269" t="n">
-        <v>83.24888</v>
+        <v>83.28835</v>
       </c>
       <c r="E269" t="n">
-        <v>127.201683044434</v>
+        <v>127.864952087402</v>
       </c>
       <c r="F269" t="n">
-        <v>82.13345</v>
+        <v>127.864952087402</v>
       </c>
       <c r="G269" t="n">
         <v>214.073338717763</v>
       </c>
       <c r="H269" t="n">
-        <v>185.332096713737</v>
+        <v>185.446592327553</v>
       </c>
     </row>
     <row r="270">
@@ -63462,22 +63399,22 @@
         <v>138.87</v>
       </c>
       <c r="C270" t="n">
-        <v>79.42587</v>
+        <v>79.56718</v>
       </c>
       <c r="D270" t="n">
-        <v>81.30212</v>
+        <v>81.28338</v>
       </c>
       <c r="E270" t="n">
-        <v>126.010887145996</v>
+        <v>125.99161529541</v>
       </c>
       <c r="F270" t="n">
-        <v>80.65018</v>
+        <v>125.99161529541</v>
       </c>
       <c r="G270" t="n">
         <v>199.532840082304</v>
       </c>
       <c r="H270" t="n">
-        <v>185.545228624958</v>
+        <v>185.530043294101</v>
       </c>
     </row>
     <row r="271">
@@ -63488,22 +63425,22 @@
         <v>137.15</v>
       </c>
       <c r="C271" t="n">
-        <v>79.67389</v>
+        <v>79.81563</v>
       </c>
       <c r="D271" t="n">
-        <v>84.13756</v>
+        <v>84.14645</v>
       </c>
       <c r="E271" t="n">
-        <v>127.445404052734</v>
+        <v>127.462821960449</v>
       </c>
       <c r="F271" t="n">
-        <v>80.89652</v>
+        <v>127.462821960449</v>
       </c>
       <c r="G271" t="n">
         <v>183.844590233937</v>
       </c>
       <c r="H271" t="n">
-        <v>187.038867715389</v>
+        <v>187.027270743484</v>
       </c>
     </row>
     <row r="272">
@@ -63514,22 +63451,22 @@
         <v>138.48</v>
       </c>
       <c r="C272" t="n">
-        <v>79.74121</v>
+        <v>79.88307</v>
       </c>
       <c r="D272" t="n">
-        <v>84.13756</v>
+        <v>84.11817</v>
       </c>
       <c r="E272" t="n">
-        <v>128.280487060547</v>
+        <v>128.269912719727</v>
       </c>
       <c r="F272" t="n">
-        <v>80.87112</v>
+        <v>128.269912719727</v>
       </c>
       <c r="G272" t="n">
         <v>190.845533844781</v>
       </c>
       <c r="H272" t="n">
-        <v>188.718476747473</v>
+        <v>188.693683725809</v>
       </c>
     </row>
     <row r="273">
@@ -63540,22 +63477,22 @@
         <v>138.29</v>
       </c>
       <c r="C273" t="n">
-        <v>80.06981</v>
+        <v>80.21226</v>
       </c>
       <c r="D273" t="n">
-        <v>84.86944</v>
+        <v>84.87816</v>
       </c>
       <c r="E273" t="n">
-        <v>129.878997802734</v>
+        <v>129.961502075195</v>
       </c>
       <c r="F273" t="n">
-        <v>78.45729</v>
+        <v>129.961502075195</v>
       </c>
       <c r="G273" t="n">
         <v>198.916073447423</v>
       </c>
       <c r="H273" t="n">
-        <v>189.31860150353</v>
+        <v>189.288068829545</v>
       </c>
     </row>
     <row r="274">
@@ -63566,22 +63503,22 @@
         <v>137.53</v>
       </c>
       <c r="C274" t="n">
-        <v>80.18381</v>
+        <v>80.32647</v>
       </c>
       <c r="D274" t="n">
-        <v>85.1235</v>
+        <v>85.10404</v>
       </c>
       <c r="E274" t="n">
-        <v>127.949020385742</v>
+        <v>128.561813354492</v>
       </c>
       <c r="F274" t="n">
-        <v>80.08157</v>
+        <v>128.561813354492</v>
       </c>
       <c r="G274" t="n">
         <v>202.451578171905</v>
       </c>
       <c r="H274" t="n">
-        <v>189.172826180372</v>
+        <v>189.314569159181</v>
       </c>
     </row>
     <row r="275">
@@ -63592,22 +63529,22 @@
         <v>137.9</v>
       </c>
       <c r="C275" t="n">
-        <v>80.64302</v>
+        <v>80.7865</v>
       </c>
       <c r="D275" t="n">
-        <v>86.80307</v>
+        <v>86.83921</v>
       </c>
       <c r="E275" t="n">
-        <v>131.762954711914</v>
+        <v>132.224578857422</v>
       </c>
       <c r="F275" t="n">
-        <v>81.06001</v>
+        <v>132.224578857422</v>
       </c>
       <c r="G275" t="n">
         <v>207.4869264585</v>
       </c>
       <c r="H275" t="n">
-        <v>191.580996257648</v>
+        <v>191.686680710745</v>
       </c>
     </row>
     <row r="276">
@@ -63618,22 +63555,22 @@
         <v>139.35</v>
       </c>
       <c r="C276" t="n">
-        <v>81.0022</v>
+        <v>81.14631</v>
       </c>
       <c r="D276" t="n">
-        <v>86.7748</v>
+        <v>86.78265</v>
       </c>
       <c r="E276" t="n">
-        <v>132.141555786133</v>
+        <v>132.14111328125</v>
       </c>
       <c r="F276" t="n">
-        <v>82.31078</v>
+        <v>132.14111328125</v>
       </c>
       <c r="G276" t="n">
         <v>228.841264085355</v>
       </c>
       <c r="H276" t="n">
-        <v>192.163402486271</v>
+        <v>192.188899814208</v>
       </c>
     </row>
     <row r="277">
@@ -63644,22 +63581,22 @@
         <v>139.04</v>
       </c>
       <c r="C277" t="n">
-        <v>81.20701</v>
+        <v>81.35149</v>
       </c>
       <c r="D277" t="n">
-        <v>86.66166</v>
+        <v>86.66951</v>
       </c>
       <c r="E277" t="n">
-        <v>131.537521362305</v>
+        <v>131.623779296875</v>
       </c>
       <c r="F277" t="n">
-        <v>82.189</v>
+        <v>131.623779296875</v>
       </c>
       <c r="G277" t="n">
         <v>232.715085350116</v>
       </c>
       <c r="H277" t="n">
-        <v>190.956616318658</v>
+        <v>190.912765519441</v>
       </c>
     </row>
     <row r="278">
@@ -63670,22 +63607,22 @@
         <v>138.02</v>
       </c>
       <c r="C278" t="n">
-        <v>81.53863</v>
+        <v>81.68369</v>
       </c>
       <c r="D278" t="n">
-        <v>87.84074</v>
+        <v>87.8487</v>
       </c>
       <c r="E278" t="n">
-        <v>131.911148071289</v>
+        <v>131.909164428711</v>
       </c>
       <c r="F278" t="n">
-        <v>84.60503</v>
+        <v>131.909164428711</v>
       </c>
       <c r="G278" t="n">
         <v>251.491022169089</v>
       </c>
       <c r="H278" t="n">
-        <v>192.877639878823</v>
+        <v>192.66916296222</v>
       </c>
     </row>
     <row r="279">
@@ -63696,22 +63633,22 @@
         <v>139.83</v>
       </c>
       <c r="C279" t="n">
-        <v>81.85458</v>
+        <v>82.00021</v>
       </c>
       <c r="D279" t="n">
-        <v>89.6312</v>
+        <v>89.61161</v>
       </c>
       <c r="E279" t="n">
-        <v>131.852401733398</v>
+        <v>131.858520507812</v>
       </c>
       <c r="F279" t="n">
-        <v>82.28834</v>
+        <v>131.858520507812</v>
       </c>
       <c r="G279" t="n">
         <v>249.451194578235</v>
       </c>
       <c r="H279" t="n">
-        <v>193.396480730097</v>
+        <v>193.366625332143</v>
       </c>
     </row>
     <row r="280">
@@ -63722,22 +63659,22 @@
         <v>142.74</v>
       </c>
       <c r="C280" t="n">
-        <v>82.06091</v>
+        <v>82.20691</v>
       </c>
       <c r="D280" t="n">
-        <v>89.23472</v>
+        <v>89.1299</v>
       </c>
       <c r="E280" t="n">
-        <v>133.40657043457</v>
+        <v>135.133071899414</v>
       </c>
       <c r="F280" t="n">
-        <v>81.75806</v>
+        <v>135.133071899414</v>
       </c>
       <c r="G280" t="n">
         <v>250.400200578255</v>
       </c>
       <c r="H280" t="n">
-        <v>194.398274500279</v>
+        <v>194.727926374482</v>
       </c>
     </row>
     <row r="281">
@@ -63748,22 +63685,22 @@
         <v>141.91</v>
       </c>
       <c r="C281" t="n">
-        <v>82.22445</v>
+        <v>82.37074</v>
       </c>
       <c r="D281" t="n">
-        <v>86.97404</v>
+        <v>86.92694</v>
       </c>
       <c r="E281" t="n">
-        <v>131.150955200195</v>
+        <v>131.149261474609</v>
       </c>
       <c r="F281" t="n">
-        <v>82.58226</v>
+        <v>131.149261474609</v>
       </c>
       <c r="G281" t="n">
         <v>268.243959473448</v>
       </c>
       <c r="H281" t="n">
-        <v>194.019197865004</v>
+        <v>194.042484073644</v>
       </c>
     </row>
     <row r="282">
@@ -63774,22 +63711,22 @@
         <v>143.1</v>
       </c>
       <c r="C282" t="n">
-        <v>82.44612</v>
+        <v>82.5928</v>
       </c>
       <c r="D282" t="n">
-        <v>90.02705</v>
+        <v>90.03477</v>
       </c>
       <c r="E282" t="n">
-        <v>134.15217590332</v>
+        <v>134.188430786133</v>
       </c>
       <c r="F282" t="n">
-        <v>82.26266</v>
+        <v>134.188430786133</v>
       </c>
       <c r="G282" t="n">
         <v>286.105095441019</v>
       </c>
       <c r="H282" t="n">
-        <v>195.511205496586</v>
+        <v>195.472577181266</v>
       </c>
     </row>
     <row r="283">
@@ -63800,22 +63737,22 @@
         <v>143.35</v>
       </c>
       <c r="C283" t="n">
-        <v>82.45529</v>
+        <v>82.60198</v>
       </c>
       <c r="D283" t="n">
-        <v>88.63302</v>
+        <v>88.61194</v>
       </c>
       <c r="E283" t="n">
-        <v>130.968139648438</v>
+        <v>131.00276184082</v>
       </c>
       <c r="F283" t="n">
-        <v>81.93878</v>
+        <v>131.00276184082</v>
       </c>
       <c r="G283" t="n">
         <v>278.266022226661</v>
       </c>
       <c r="H283" t="n">
-        <v>194.535604581158</v>
+        <v>194.633999825159</v>
       </c>
     </row>
     <row r="284">
@@ -63826,22 +63763,22 @@
         <v>141.42</v>
       </c>
       <c r="C284" t="n">
-        <v>82.80342</v>
+        <v>82.95073</v>
       </c>
       <c r="D284" t="n">
-        <v>89.44785</v>
+        <v>89.4548</v>
       </c>
       <c r="E284" t="n">
-        <v>135.184265136719</v>
+        <v>135.158615112305</v>
       </c>
       <c r="F284" t="n">
-        <v>83.85539</v>
+        <v>135.158615112305</v>
       </c>
       <c r="G284" t="n">
         <v>294.302045325519</v>
       </c>
       <c r="H284" t="n">
-        <v>195.78841387466</v>
+        <v>195.932208603992</v>
       </c>
     </row>
     <row r="285">
@@ -63852,22 +63789,22 @@
         <v>142.04</v>
       </c>
       <c r="C285" t="n">
-        <v>83.12544</v>
+        <v>83.27333</v>
       </c>
       <c r="D285" t="n">
-        <v>91.40215</v>
+        <v>91.40926</v>
       </c>
       <c r="E285" t="n">
-        <v>135.08528137207</v>
+        <v>135.156951904297</v>
       </c>
       <c r="F285" t="n">
-        <v>85.51296</v>
+        <v>135.156951904297</v>
       </c>
       <c r="G285" t="n">
         <v>283.376296076887</v>
       </c>
       <c r="H285" t="n">
-        <v>196.839797657167</v>
+        <v>196.99220185254</v>
       </c>
     </row>
     <row r="286">
@@ -63878,22 +63815,22 @@
         <v>142.52</v>
       </c>
       <c r="C286" t="n">
-        <v>83.09308</v>
+        <v>83.24091</v>
       </c>
       <c r="D286" t="n">
-        <v>90.49465</v>
+        <v>90.41613</v>
       </c>
       <c r="E286" t="n">
-        <v>134.887649536133</v>
+        <v>134.137924194336</v>
       </c>
       <c r="F286" t="n">
-        <v>82.50222</v>
+        <v>134.137924194336</v>
       </c>
       <c r="G286" t="n">
         <v>286.413180113516</v>
       </c>
       <c r="H286" t="n">
-        <v>195.704032024685</v>
+        <v>195.493091196442</v>
       </c>
     </row>
     <row r="287">
@@ -63904,22 +63841,22 @@
         <v>142.34</v>
       </c>
       <c r="C287" t="n">
-        <v>83.29288</v>
+        <v>83.44106</v>
       </c>
       <c r="D287" t="n">
-        <v>92.06121</v>
+        <v>92.14905</v>
       </c>
       <c r="E287" t="n">
-        <v>133.778411865234</v>
+        <v>133.859741210938</v>
       </c>
       <c r="F287" t="n">
-        <v>81.62519</v>
+        <v>133.859741210938</v>
       </c>
       <c r="G287" t="n">
         <v>292.747866117343</v>
       </c>
       <c r="H287" t="n">
-        <v>197.604318175645</v>
+        <v>197.637650406867</v>
       </c>
     </row>
     <row r="288">
@@ -63930,22 +63867,22 @@
         <v>140.34</v>
       </c>
       <c r="C288" t="n">
-        <v>83.41682</v>
+        <v>83.56522</v>
       </c>
       <c r="D288" t="n">
-        <v>93.32215</v>
+        <v>93.29865</v>
       </c>
       <c r="E288" t="n">
-        <v>135.029388427734</v>
+        <v>135.083404541016</v>
       </c>
       <c r="F288" t="n">
-        <v>80.97764</v>
+        <v>135.083404541016</v>
       </c>
       <c r="G288" t="n">
         <v>239.604329899757</v>
       </c>
       <c r="H288" t="n">
-        <v>198.293957246078</v>
+        <v>198.272067264673</v>
       </c>
     </row>
     <row r="289">
@@ -63956,22 +63893,22 @@
         <v>139.38</v>
       </c>
       <c r="C289" t="n">
-        <v>83.60504</v>
+        <v>83.75378</v>
       </c>
       <c r="D289" t="n">
-        <v>92.04394</v>
+        <v>92.04896</v>
       </c>
       <c r="E289" t="n">
-        <v>135.11767578125</v>
+        <v>135.032089233398</v>
       </c>
       <c r="F289" t="n">
-        <v>81.7634</v>
+        <v>135.032089233398</v>
       </c>
       <c r="G289" t="n">
         <v>209.829089961219</v>
       </c>
       <c r="H289" t="n">
-        <v>198.29594018565</v>
+        <v>198.357324253597</v>
       </c>
     </row>
     <row r="290">
@@ -63982,22 +63919,22 @@
         <v>139.11</v>
       </c>
       <c r="C290" t="n">
-        <v>83.94306</v>
+        <v>84.0924</v>
       </c>
       <c r="D290" t="n">
-        <v>93.10967</v>
+        <v>93.08686</v>
       </c>
       <c r="E290" t="n">
-        <v>135.926147460938</v>
+        <v>135.845260620117</v>
       </c>
       <c r="F290" t="n">
-        <v>83.34591</v>
+        <v>135.845260620117</v>
       </c>
       <c r="G290" t="n">
         <v>215.962318794469</v>
       </c>
       <c r="H290" t="n">
-        <v>200.510905837524</v>
+        <v>200.636449909271</v>
       </c>
     </row>
     <row r="291">
@@ -64008,22 +63945,22 @@
         <v>141.37</v>
       </c>
       <c r="C291" t="n">
-        <v>84.29228</v>
+        <v>84.44224</v>
       </c>
       <c r="D291" t="n">
-        <v>94.20327</v>
+        <v>94.2084</v>
       </c>
       <c r="E291" t="n">
-        <v>137.78173828125</v>
+        <v>137.804672241211</v>
       </c>
       <c r="F291" t="n">
-        <v>83.66118</v>
+        <v>137.804672241211</v>
       </c>
       <c r="G291" t="n">
         <v>226.883187752019</v>
       </c>
       <c r="H291" t="n">
-        <v>202.08291133929</v>
+        <v>202.123166003099</v>
       </c>
     </row>
     <row r="292">
@@ -64034,22 +63971,22 @@
         <v>141.41</v>
       </c>
       <c r="C292" t="n">
-        <v>84.749</v>
+        <v>84.89978</v>
       </c>
       <c r="D292" t="n">
-        <v>94.03389</v>
+        <v>94.03901</v>
       </c>
       <c r="E292" t="n">
-        <v>136.12467956543</v>
+        <v>134.630722045898</v>
       </c>
       <c r="F292" t="n">
-        <v>84.45799</v>
+        <v>134.630722045898</v>
       </c>
       <c r="G292" t="n">
         <v>238.383647735278</v>
       </c>
       <c r="H292" t="n">
-        <v>202.153640358259</v>
+        <v>202.064550284958</v>
       </c>
     </row>
     <row r="293">
@@ -64060,22 +63997,22 @@
         <v>142.12</v>
       </c>
       <c r="C293" t="n">
-        <v>84.92097</v>
+        <v>85.07205</v>
       </c>
       <c r="D293" t="n">
-        <v>95.73882</v>
+        <v>95.68861</v>
       </c>
       <c r="E293" t="n">
-        <v>140.992340087891</v>
+        <v>141.69660949707</v>
       </c>
       <c r="F293" t="n">
-        <v>85.35791</v>
+        <v>141.69660949707</v>
       </c>
       <c r="G293" t="n">
         <v>259.284657467068</v>
       </c>
       <c r="H293" t="n">
-        <v>201.18936749375</v>
+        <v>201.44219147008</v>
       </c>
     </row>
     <row r="294">
@@ -64086,22 +64023,22 @@
         <v>142.49</v>
       </c>
       <c r="C294" t="n">
-        <v>84.96663</v>
+        <v>85.11779</v>
       </c>
       <c r="D294" t="n">
-        <v>95.31488</v>
+        <v>95.32129</v>
       </c>
       <c r="E294" t="n">
-        <v>138.835556030273</v>
+        <v>138.851989746094</v>
       </c>
       <c r="F294" t="n">
-        <v>84.3684</v>
+        <v>138.851989746094</v>
       </c>
       <c r="G294" t="n">
         <v>245.16660680623</v>
       </c>
       <c r="H294" t="n">
-        <v>199.815244113768</v>
+        <v>199.75813474939</v>
       </c>
     </row>
     <row r="295">
@@ -64112,22 +64049,22 @@
         <v>139.7</v>
       </c>
       <c r="C295" t="n">
-        <v>85.32408</v>
+        <v>85.47588</v>
       </c>
       <c r="D295" t="n">
-        <v>96.51982</v>
+        <v>96.5263</v>
       </c>
       <c r="E295" t="n">
-        <v>139.891159057617</v>
+        <v>139.975173950195</v>
       </c>
       <c r="F295" t="n">
-        <v>83.07318</v>
+        <v>139.975173950195</v>
       </c>
       <c r="G295" t="n">
         <v>221.85868783012</v>
       </c>
       <c r="H295" t="n">
-        <v>201.445736505736</v>
+        <v>201.32823368852</v>
       </c>
     </row>
     <row r="296">
@@ -64138,22 +64075,22 @@
         <v>139.21</v>
       </c>
       <c r="C296" t="n">
-        <v>85.52909</v>
+        <v>85.68125</v>
       </c>
       <c r="D296" t="n">
-        <v>98.33546</v>
+        <v>98.3144</v>
       </c>
       <c r="E296" t="n">
-        <v>139.40087890625</v>
+        <v>139.371200561523</v>
       </c>
       <c r="F296" t="n">
-        <v>86.22451</v>
+        <v>139.371200561523</v>
       </c>
       <c r="G296" t="n">
         <v>230.095957497607</v>
       </c>
       <c r="H296" t="n">
-        <v>203.589119142157</v>
+        <v>203.53881769442</v>
       </c>
     </row>
     <row r="297">
@@ -64164,22 +64101,22 @@
         <v>142.15</v>
       </c>
       <c r="C297" t="n">
-        <v>85.46823</v>
+        <v>85.62029</v>
       </c>
       <c r="D297" t="n">
-        <v>97.02999</v>
+        <v>96.98024</v>
       </c>
       <c r="E297" t="n">
-        <v>135.933486938477</v>
+        <v>136.012954711914</v>
       </c>
       <c r="F297" t="n">
-        <v>84.46124</v>
+        <v>136.012954711914</v>
       </c>
       <c r="G297" t="n">
         <v>217.35324470722</v>
       </c>
       <c r="H297" t="n">
-        <v>201.661130183881</v>
+        <v>201.698826782463</v>
       </c>
     </row>
     <row r="298">
@@ -64190,22 +64127,22 @@
         <v>141.62</v>
       </c>
       <c r="C298" t="n">
-        <v>85.77462</v>
+        <v>85.92722</v>
       </c>
       <c r="D298" t="n">
-        <v>99.34199</v>
+        <v>99.37494</v>
       </c>
       <c r="E298" t="n">
-        <v>139.323776245117</v>
+        <v>139.341339111328</v>
       </c>
       <c r="F298" t="n">
-        <v>85.1121</v>
+        <v>139.341339111328</v>
       </c>
       <c r="G298" t="n">
         <v>227.119215014234</v>
       </c>
       <c r="H298" t="n">
-        <v>203.268369391447</v>
+        <v>203.356791138614</v>
       </c>
     </row>
     <row r="299">
@@ -64216,22 +64153,22 @@
         <v>139.88</v>
       </c>
       <c r="C299" t="n">
-        <v>86.36465</v>
+        <v>86.5183</v>
       </c>
       <c r="D299" t="n">
-        <v>99.11628</v>
+        <v>99.09271</v>
       </c>
       <c r="E299" t="n">
-        <v>143.183395385742</v>
+        <v>143.220733642578</v>
       </c>
       <c r="F299" t="n">
-        <v>89.25615</v>
+        <v>143.220733642578</v>
       </c>
       <c r="G299" t="n">
         <v>214.073933426267</v>
       </c>
       <c r="H299" t="n">
-        <v>204.030625776664</v>
+        <v>204.044137092663</v>
       </c>
     </row>
     <row r="300">
@@ -64242,22 +64179,22 @@
         <v>139.89</v>
       </c>
       <c r="C300" t="n">
-        <v>86.86346</v>
+        <v>87.018</v>
       </c>
       <c r="D300" t="n">
-        <v>99.6503</v>
+        <v>99.59871</v>
       </c>
       <c r="E300" t="n">
-        <v>140.779907226562</v>
+        <v>140.704574584961</v>
       </c>
       <c r="F300" t="n">
-        <v>87.96141</v>
+        <v>140.704574584961</v>
       </c>
       <c r="G300" t="n">
         <v>224.537467786623</v>
       </c>
       <c r="H300" t="n">
-        <v>203.953094138869</v>
+        <v>204.044137092663</v>
       </c>
     </row>
     <row r="301">
@@ -64268,22 +64205,22 @@
         <v>140.46</v>
       </c>
       <c r="C301" t="n">
-        <v>87.38863</v>
+        <v>87.5441</v>
       </c>
       <c r="D301" t="n">
-        <v>102.621</v>
+        <v>102.5969</v>
       </c>
       <c r="E301" t="n">
-        <v>144.647674560547</v>
+        <v>144.828887939453</v>
       </c>
       <c r="F301" t="n">
-        <v>87.63675</v>
+        <v>144.828887939453</v>
       </c>
       <c r="G301" t="n">
         <v>235.272527163888</v>
       </c>
       <c r="H301" t="n">
-        <v>205.115626775461</v>
+        <v>205.090883515948</v>
       </c>
     </row>
     <row r="302">
@@ -64294,22 +64231,22 @@
         <v>140.99</v>
       </c>
       <c r="C302" t="n">
-        <v>87.49927</v>
+        <v>87.65494</v>
       </c>
       <c r="D302" t="n">
-        <v>104.0477</v>
+        <v>104.0514</v>
       </c>
       <c r="E302" t="n">
-        <v>146.018280029297</v>
+        <v>146.046340942383</v>
       </c>
       <c r="F302" t="n">
-        <v>88.2669</v>
+        <v>146.046340942383</v>
       </c>
       <c r="G302" t="n">
         <v>226.140354156524</v>
       </c>
       <c r="H302" t="n">
-        <v>207.726748704312</v>
+        <v>207.519159576777</v>
       </c>
     </row>
     <row r="303">
@@ -64320,22 +64257,22 @@
         <v>141.41</v>
       </c>
       <c r="C303" t="n">
-        <v>86.59114</v>
+        <v>86.74519</v>
       </c>
       <c r="D303" t="n">
-        <v>102.544</v>
+        <v>102.5191</v>
       </c>
       <c r="E303" t="n">
-        <v>142.975982666016</v>
+        <v>142.713348388672</v>
       </c>
       <c r="F303" t="n">
-        <v>88.03806</v>
+        <v>142.713348388672</v>
       </c>
       <c r="G303" t="n">
         <v>197.384986497944</v>
       </c>
       <c r="H303" t="n">
-        <v>206.324593150558</v>
+        <v>206.122555632825</v>
       </c>
     </row>
     <row r="304">
@@ -64346,22 +64283,22 @@
         <v>124.28</v>
       </c>
       <c r="C304" t="n">
-        <v>83.21746</v>
+        <v>83.36551</v>
       </c>
       <c r="D304" t="n">
-        <v>86.18141</v>
+        <v>86.0895</v>
       </c>
       <c r="E304" t="n">
-        <v>123.735610961914</v>
+        <v>124.419937133789</v>
       </c>
       <c r="F304" t="n">
-        <v>79.44319</v>
+        <v>124.419937133789</v>
       </c>
       <c r="G304" t="n">
         <v>121.185944180081</v>
       </c>
       <c r="H304" t="n">
-        <v>187.77188573446</v>
+        <v>188.305321923924</v>
       </c>
     </row>
     <row r="305">
@@ -64372,22 +64309,22 @@
         <v>115.56</v>
       </c>
       <c r="C305" t="n">
-        <v>80.77864</v>
+        <v>80.92236</v>
       </c>
       <c r="D305" t="n">
-        <v>72.1949</v>
+        <v>72.07056</v>
       </c>
       <c r="E305" t="n">
-        <v>110.754974365234</v>
+        <v>110.917060852051</v>
       </c>
       <c r="F305" t="n">
-        <v>79.87255</v>
+        <v>110.917060852051</v>
       </c>
       <c r="G305" t="n">
         <v>67.0818449689149</v>
       </c>
       <c r="H305" t="n">
-        <v>167.90186478604</v>
+        <v>167.563490714004</v>
       </c>
     </row>
     <row r="306">
@@ -64398,22 +64335,22 @@
         <v>127.66</v>
       </c>
       <c r="C306" t="n">
-        <v>82.24721</v>
+        <v>82.2787</v>
       </c>
       <c r="D306" t="n">
-        <v>94.39292</v>
+        <v>94.31959</v>
       </c>
       <c r="E306" t="n">
-        <v>128.431732177734</v>
+        <v>128.510894775391</v>
       </c>
       <c r="F306" t="n">
-        <v>84.02921</v>
+        <v>128.510894775391</v>
       </c>
       <c r="G306" t="n">
         <v>114.497873413383</v>
       </c>
       <c r="H306" t="n">
-        <v>185.706178527951</v>
+        <v>185.566512156316</v>
       </c>
     </row>
     <row r="307">
@@ -64424,22 +64361,22 @@
         <v>122.5</v>
       </c>
       <c r="C307" t="n">
-        <v>83.57181</v>
+        <v>83.57661</v>
       </c>
       <c r="D307" t="n">
-        <v>96.85898</v>
+        <v>96.81002</v>
       </c>
       <c r="E307" t="n">
-        <v>135.151397705078</v>
+        <v>135.186294555664</v>
       </c>
       <c r="F307" t="n">
-        <v>89.89004</v>
+        <v>135.186294555664</v>
       </c>
       <c r="G307" t="n">
         <v>151.128842497069</v>
       </c>
       <c r="H307" t="n">
-        <v>193.732399563929</v>
+        <v>194.169375659883</v>
       </c>
     </row>
     <row r="308">
@@ -64450,22 +64387,22 @@
         <v>102.8</v>
       </c>
       <c r="C308" t="n">
-        <v>84.7177</v>
+        <v>84.6862</v>
       </c>
       <c r="D308" t="n">
-        <v>95.58869</v>
+        <v>95.51374</v>
       </c>
       <c r="E308" t="n">
-        <v>138.098220825195</v>
+        <v>138.082611083984</v>
       </c>
       <c r="F308" t="n">
-        <v>86.30629</v>
+        <v>138.082611083984</v>
       </c>
       <c r="G308" t="n">
         <v>159.124190853812</v>
       </c>
       <c r="H308" t="n">
-        <v>194.063681967184</v>
+        <v>194.093649603376</v>
       </c>
     </row>
     <row r="309">
@@ -64476,22 +64413,22 @@
         <v>115.8</v>
       </c>
       <c r="C309" t="n">
-        <v>85.76433</v>
+        <v>85.73468</v>
       </c>
       <c r="D309" t="n">
-        <v>103.0455</v>
+        <v>102.9667</v>
       </c>
       <c r="E309" t="n">
-        <v>140.654098510742</v>
+        <v>140.733535766602</v>
       </c>
       <c r="F309" t="n">
-        <v>89.21512</v>
+        <v>140.733535766602</v>
       </c>
       <c r="G309" t="n">
         <v>163.933989458494</v>
       </c>
       <c r="H309" t="n">
-        <v>199.210250812953</v>
+        <v>199.044978604758</v>
       </c>
     </row>
     <row r="310">
@@ -64502,22 +64439,22 @@
         <v>109.8</v>
       </c>
       <c r="C310" t="n">
-        <v>85.95398</v>
+        <v>85.97081</v>
       </c>
       <c r="D310" t="n">
-        <v>96.58194</v>
+        <v>96.59002</v>
       </c>
       <c r="E310" t="n">
-        <v>136.509643554688</v>
+        <v>136.826782226562</v>
       </c>
       <c r="F310" t="n">
-        <v>89.96309</v>
+        <v>136.826782226562</v>
       </c>
       <c r="G310" t="n">
         <v>154.364224711263</v>
       </c>
       <c r="H310" t="n">
-        <v>199.136543020153</v>
+        <v>199.04895950433</v>
       </c>
     </row>
     <row r="311">
@@ -64528,22 +64465,22 @@
         <v>110.8</v>
       </c>
       <c r="C311" t="n">
-        <v>86.03651</v>
+        <v>86.06633</v>
       </c>
       <c r="D311" t="n">
-        <v>87.85424</v>
+        <v>87.78064</v>
       </c>
       <c r="E311" t="n">
-        <v>133.222534179688</v>
+        <v>133.437698364258</v>
       </c>
       <c r="F311" t="n">
-        <v>90.79962</v>
+        <v>133.437698364258</v>
       </c>
       <c r="G311" t="n">
         <v>151.972210844884</v>
       </c>
       <c r="H311" t="n">
-        <v>197.688820352396</v>
+        <v>197.589930631163</v>
       </c>
     </row>
     <row r="312">
@@ -64554,22 +64491,22 @@
         <v>120.5</v>
       </c>
       <c r="C312" t="n">
-        <v>86.99914</v>
+        <v>87.01731</v>
       </c>
       <c r="D312" t="n">
-        <v>97.76971</v>
+        <v>97.71383</v>
       </c>
       <c r="E312" t="n">
-        <v>143.598922729492</v>
+        <v>143.751281738281</v>
       </c>
       <c r="F312" t="n">
-        <v>89.86195</v>
+        <v>143.751281738281</v>
       </c>
       <c r="G312" t="n">
         <v>156.571470290939</v>
       </c>
       <c r="H312" t="n">
-        <v>204.447801120244</v>
+        <v>204.373192949731</v>
       </c>
     </row>
     <row r="313">
@@ -64580,22 +64517,22 @@
         <v>121.5</v>
       </c>
       <c r="C313" t="n">
-        <v>87.68814</v>
+        <v>87.70359</v>
       </c>
       <c r="D313" t="n">
-        <v>101.5286</v>
+        <v>101.4457</v>
       </c>
       <c r="E313" t="n">
-        <v>145.748352050781</v>
+        <v>145.749496459961</v>
       </c>
       <c r="F313" t="n">
-        <v>89.30569</v>
+        <v>145.749496459961</v>
       </c>
       <c r="G313" t="n">
         <v>174.038391573147</v>
       </c>
       <c r="H313" t="n">
-        <v>206.747838882847</v>
+        <v>206.733703328301</v>
       </c>
     </row>
     <row r="314">
@@ -64606,22 +64543,22 @@
         <v>122.6</v>
       </c>
       <c r="C314" t="n">
-        <v>87.76949</v>
+        <v>87.80456</v>
       </c>
       <c r="D314" t="n">
-        <v>90.00592</v>
+        <v>89.9293</v>
       </c>
       <c r="E314" t="n">
-        <v>143.349487304688</v>
+        <v>143.348648071289</v>
       </c>
       <c r="F314" t="n">
-        <v>87.30395</v>
+        <v>143.348648071289</v>
       </c>
       <c r="G314" t="n">
         <v>191.169131492064</v>
       </c>
       <c r="H314" t="n">
-        <v>200.011994292044</v>
+        <v>199.890817748134</v>
       </c>
     </row>
     <row r="315">
@@ -64632,22 +64569,22 @@
         <v>126.4</v>
       </c>
       <c r="C315" t="n">
-        <v>89.02063</v>
+        <v>89.05707</v>
       </c>
       <c r="D315" t="n">
-        <v>95.22187</v>
+        <v>95.14225</v>
       </c>
       <c r="E315" t="n">
-        <v>147.870880126953</v>
+        <v>147.765090942383</v>
       </c>
       <c r="F315" t="n">
-        <v>86.28117</v>
+        <v>147.765090942383</v>
       </c>
       <c r="G315" t="n">
         <v>219.586606487423</v>
       </c>
       <c r="H315" t="n">
-        <v>203.340193877064</v>
+        <v>203.207006414575</v>
       </c>
     </row>
     <row r="316">
@@ -64658,22 +64595,22 @@
         <v>133.2</v>
       </c>
       <c r="C316" t="n">
-        <v>90.55404</v>
+        <v>90.61921</v>
       </c>
       <c r="D316" t="n">
-        <v>103.8955</v>
+        <v>103.8109</v>
       </c>
       <c r="E316" t="n">
-        <v>153.30615234375</v>
+        <v>153.898056030273</v>
       </c>
       <c r="F316" t="n">
-        <v>90.76829</v>
+        <v>153.898056030273</v>
       </c>
       <c r="G316" t="n">
         <v>233.350955489462</v>
       </c>
       <c r="H316" t="n">
-        <v>208.037352355624</v>
+        <v>208.100231129038</v>
       </c>
     </row>
     <row r="317">
@@ -64684,22 +64621,22 @@
         <v>140.4</v>
       </c>
       <c r="C317" t="n">
-        <v>91.76076</v>
+        <v>91.87417</v>
       </c>
       <c r="D317" t="n">
-        <v>106.9918</v>
+        <v>106.7566</v>
       </c>
       <c r="E317" t="n">
-        <v>157.277923583984</v>
+        <v>158.720367431641</v>
       </c>
       <c r="F317" t="n">
-        <v>89.39277</v>
+        <v>158.720367431641</v>
       </c>
       <c r="G317" t="n">
         <v>227.867564846153</v>
       </c>
       <c r="H317" t="n">
-        <v>210.941553794508</v>
+        <v>211.046930401826</v>
       </c>
     </row>
     <row r="318">
@@ -64710,22 +64647,22 @@
         <v>139.3</v>
       </c>
       <c r="C318" t="n">
-        <v>92.38593</v>
+        <v>92.46809</v>
       </c>
       <c r="D318" t="n">
-        <v>100.8418</v>
+        <v>100.8256</v>
       </c>
       <c r="E318" t="n">
-        <v>154.207077026367</v>
+        <v>154.338027954102</v>
       </c>
       <c r="F318" t="n">
-        <v>86.97879</v>
+        <v>154.338027954102</v>
       </c>
       <c r="G318" t="n">
         <v>238.700965996955</v>
       </c>
       <c r="H318" t="n">
-        <v>208.161344115497</v>
+        <v>208.079610560376</v>
       </c>
     </row>
     <row r="319">
@@ -64736,22 +64673,22 @@
         <v>141.8</v>
       </c>
       <c r="C319" t="n">
-        <v>93.33032</v>
+        <v>93.39085</v>
       </c>
       <c r="D319" t="n">
-        <v>107.1666</v>
+        <v>107.1239</v>
       </c>
       <c r="E319" t="n">
-        <v>164.022796630859</v>
+        <v>164.100082397461</v>
       </c>
       <c r="F319" t="n">
-        <v>92.51676</v>
+        <v>164.100082397461</v>
       </c>
       <c r="G319" t="n">
         <v>260.340587864837</v>
       </c>
       <c r="H319" t="n">
-        <v>213.082278290387</v>
+        <v>212.836310457786</v>
       </c>
     </row>
     <row r="320">
@@ -64762,22 +64699,22 @@
         <v>138.2</v>
       </c>
       <c r="C320" t="n">
-        <v>93.83577</v>
+        <v>93.89352</v>
       </c>
       <c r="D320" t="n">
-        <v>107.8768</v>
+        <v>107.8085</v>
       </c>
       <c r="E320" t="n">
-        <v>160.673965454102</v>
+        <v>160.735656738281</v>
       </c>
       <c r="F320" t="n">
-        <v>92.36704</v>
+        <v>160.735656738281</v>
       </c>
       <c r="G320" t="n">
         <v>264.867983807143</v>
       </c>
       <c r="H320" t="n">
-        <v>212.17454778487</v>
+        <v>212.016890662524</v>
       </c>
     </row>
     <row r="321">
@@ -64788,22 +64725,22 @@
         <v>134.7</v>
       </c>
       <c r="C321" t="n">
-        <v>94.39506</v>
+        <v>94.44477</v>
       </c>
       <c r="D321" t="n">
-        <v>107.5454</v>
+        <v>107.5028</v>
       </c>
       <c r="E321" t="n">
-        <v>167.925964355469</v>
+        <v>168.009979248047</v>
       </c>
       <c r="F321" t="n">
-        <v>90.3488</v>
+        <v>168.009979248047</v>
       </c>
       <c r="G321" t="n">
         <v>243.227742428768</v>
       </c>
       <c r="H321" t="n">
-        <v>214.321754208453</v>
+        <v>214.251548690107</v>
       </c>
     </row>
     <row r="322">
@@ -64814,22 +64751,22 @@
         <v>139</v>
       </c>
       <c r="C322" t="n">
-        <v>94.90853</v>
+        <v>94.97058</v>
       </c>
       <c r="D322" t="n">
-        <v>106.1108</v>
+        <v>106.1461</v>
       </c>
       <c r="E322" t="n">
-        <v>168.690475463867</v>
+        <v>169.417541503906</v>
       </c>
       <c r="F322" t="n">
-        <v>92.54245</v>
+        <v>169.417541503906</v>
       </c>
       <c r="G322" t="n">
         <v>255.270307507371</v>
       </c>
       <c r="H322" t="n">
-        <v>216.726444290672</v>
+        <v>216.739009170399</v>
       </c>
     </row>
     <row r="323">
@@ -64840,22 +64777,22 @@
         <v>137.6</v>
       </c>
       <c r="C323" t="n">
-        <v>95.49781</v>
+        <v>95.51907</v>
       </c>
       <c r="D323" t="n">
-        <v>112.4089</v>
+        <v>112.4179</v>
       </c>
       <c r="E323" t="n">
-        <v>169.675308227539</v>
+        <v>169.553909301758</v>
       </c>
       <c r="F323" t="n">
-        <v>95.60804</v>
+        <v>169.553909301758</v>
       </c>
       <c r="G323" t="n">
         <v>290.992671605447</v>
       </c>
       <c r="H323" t="n">
-        <v>222.669083393122</v>
+        <v>222.385060359288</v>
       </c>
     </row>
     <row r="324">
@@ -64866,22 +64803,22 @@
         <v>138.1</v>
       </c>
       <c r="C324" t="n">
-        <v>95.8287</v>
+        <v>95.83906</v>
       </c>
       <c r="D324" t="n">
-        <v>109.1094</v>
+        <v>109.0411</v>
       </c>
       <c r="E324" t="n">
-        <v>172.089141845703</v>
+        <v>171.995132446289</v>
       </c>
       <c r="F324" t="n">
-        <v>90.87302</v>
+        <v>171.995132446289</v>
       </c>
       <c r="G324" t="n">
         <v>274.590808749652</v>
       </c>
       <c r="H324" t="n">
-        <v>225.50588751555</v>
+        <v>225.502898905525</v>
       </c>
     </row>
     <row r="325">
@@ -64892,22 +64829,22 @@
         <v>138.3</v>
       </c>
       <c r="C325" t="n">
-        <v>96.12511</v>
+        <v>96.12642</v>
       </c>
       <c r="D325" t="n">
-        <v>106.7998</v>
+        <v>106.7325</v>
       </c>
       <c r="E325" t="n">
-        <v>169.718276977539</v>
+        <v>169.815582275391</v>
       </c>
       <c r="F325" t="n">
-        <v>98.05566</v>
+        <v>169.815582275391</v>
       </c>
       <c r="G325" t="n">
         <v>248.980518962851</v>
       </c>
       <c r="H325" t="n">
-        <v>224.441499726477</v>
+        <v>224.445290309658</v>
       </c>
     </row>
     <row r="326">
@@ -64918,22 +64855,22 @@
         <v>132.5</v>
       </c>
       <c r="C326" t="n">
-        <v>96.62052</v>
+        <v>96.59776</v>
       </c>
       <c r="D326" t="n">
-        <v>107.9612</v>
+        <v>107.8934</v>
       </c>
       <c r="E326" t="n">
-        <v>169.897720336914</v>
+        <v>169.668701171875</v>
       </c>
       <c r="F326" t="n">
-        <v>99.81537</v>
+        <v>169.668701171875</v>
       </c>
       <c r="G326" t="n">
         <v>288.593030091291</v>
       </c>
       <c r="H326" t="n">
-        <v>222.300327819086</v>
+        <v>222.420793791065</v>
       </c>
     </row>
     <row r="327">
@@ -64944,22 +64881,22 @@
         <v>128.2</v>
       </c>
       <c r="C327" t="n">
-        <v>96.953</v>
+        <v>96.91156</v>
       </c>
       <c r="D327" t="n">
-        <v>109.6488</v>
+        <v>109.5803</v>
       </c>
       <c r="E327" t="n">
-        <v>175.884399414062</v>
+        <v>175.565078735352</v>
       </c>
       <c r="F327" t="n">
-        <v>102.9319</v>
+        <v>175.565078735352</v>
       </c>
       <c r="G327" t="n">
         <v>323.654999805255</v>
       </c>
       <c r="H327" t="n">
-        <v>223.196198140197</v>
+        <v>223.001312062859</v>
       </c>
     </row>
     <row r="328">
@@ -64970,22 +64907,22 @@
         <v>127.6</v>
       </c>
       <c r="C328" t="n">
-        <v>97.31262</v>
+        <v>97.27297</v>
       </c>
       <c r="D328" t="n">
-        <v>109.5726</v>
+        <v>109.5549</v>
       </c>
       <c r="E328" t="n">
-        <v>174.210311889648</v>
+        <v>174.161117553711</v>
       </c>
       <c r="F328" t="n">
-        <v>100.2269</v>
+        <v>174.161117553711</v>
       </c>
       <c r="G328" t="n">
         <v>384.482709455254</v>
       </c>
       <c r="H328" t="n">
-        <v>223.133703204718</v>
+        <v>223.030302233428</v>
       </c>
     </row>
     <row r="329">
@@ -64996,22 +64933,22 @@
         <v>133.9</v>
       </c>
       <c r="C329" t="n">
-        <v>97.81236</v>
+        <v>97.80769</v>
       </c>
       <c r="D329" t="n">
-        <v>110.6837</v>
+        <v>110.7158</v>
       </c>
       <c r="E329" t="n">
-        <v>174.771423339844</v>
+        <v>174.986724853516</v>
       </c>
       <c r="F329" t="n">
-        <v>99.48666</v>
+        <v>174.986724853516</v>
       </c>
       <c r="G329" t="n">
         <v>357.780225662819</v>
       </c>
       <c r="H329" t="n">
-        <v>226.529798167494</v>
+        <v>226.540799190582</v>
       </c>
     </row>
     <row r="330">
@@ -65022,22 +64959,22 @@
         <v>129.3</v>
       </c>
       <c r="C330" t="n">
-        <v>98.09082</v>
+        <v>98.06764</v>
       </c>
       <c r="D330" t="n">
-        <v>111.4173</v>
+        <v>111.3735</v>
       </c>
       <c r="E330" t="n">
-        <v>175.830215454102</v>
+        <v>176.059036254883</v>
       </c>
       <c r="F330" t="n">
-        <v>103.1563</v>
+        <v>176.059036254883</v>
       </c>
       <c r="G330" t="n">
         <v>409.067416537785</v>
       </c>
       <c r="H330" t="n">
-        <v>227.173142794289</v>
+        <v>227.052781396752</v>
       </c>
     </row>
     <row r="331">
@@ -65048,22 +64985,22 @@
         <v>128.6</v>
       </c>
       <c r="C331" t="n">
-        <v>98.29223</v>
+        <v>98.27921</v>
       </c>
       <c r="D331" t="n">
-        <v>110.551</v>
+        <v>110.482</v>
       </c>
       <c r="E331" t="n">
-        <v>174.403045654297</v>
+        <v>174.561721801758</v>
       </c>
       <c r="F331" t="n">
-        <v>105.2853</v>
+        <v>174.561721801758</v>
       </c>
       <c r="G331" t="n">
         <v>420.691481459921</v>
       </c>
       <c r="H331" t="n">
-        <v>226.605209937304</v>
+        <v>226.498772610144</v>
       </c>
     </row>
     <row r="332">
@@ -65074,22 +65011,22 @@
         <v>125</v>
       </c>
       <c r="C332" t="n">
-        <v>98.35487</v>
+        <v>98.31673</v>
       </c>
       <c r="D332" t="n">
-        <v>109.7359</v>
+        <v>109.6928</v>
       </c>
       <c r="E332" t="n">
-        <v>172.866836547852</v>
+        <v>172.987976074219</v>
       </c>
       <c r="F332" t="n">
-        <v>98.48563</v>
+        <v>172.987976074219</v>
       </c>
       <c r="G332" t="n">
         <v>373.985336554144</v>
       </c>
       <c r="H332" t="n">
-        <v>224.617882246154</v>
+        <v>224.39233402487</v>
       </c>
     </row>
     <row r="333">
@@ -65100,22 +65037,22 @@
         <v>130.4</v>
       </c>
       <c r="C333" t="n">
-        <v>98.69351</v>
+        <v>98.64948</v>
       </c>
       <c r="D333" t="n">
-        <v>110.9223</v>
+        <v>110.8284</v>
       </c>
       <c r="E333" t="n">
-        <v>171.675674438477</v>
+        <v>171.796005249023</v>
       </c>
       <c r="F333" t="n">
-        <v>101.8943</v>
+        <v>171.796005249023</v>
       </c>
       <c r="G333" t="n">
         <v>327.983100659284</v>
       </c>
       <c r="H333" t="n">
-        <v>226.073406123109</v>
+        <v>226.070788683376</v>
       </c>
     </row>
     <row r="334">
@@ -65126,22 +65063,22 @@
         <v>129.4</v>
       </c>
       <c r="C334" t="n">
-        <v>99.10622</v>
+        <v>99.02125</v>
       </c>
       <c r="D334" t="n">
-        <v>113.0337</v>
+        <v>112.8893</v>
       </c>
       <c r="E334" t="n">
-        <v>174.605773925781</v>
+        <v>174.031387329102</v>
       </c>
       <c r="F334" t="n">
-        <v>103.8338</v>
+        <v>174.031387329102</v>
       </c>
       <c r="G334" t="n">
         <v>308.293381401209</v>
       </c>
       <c r="H334" t="n">
-        <v>228.019898149829</v>
+        <v>227.958479768882</v>
       </c>
     </row>
     <row r="335">
@@ -65152,22 +65089,22 @@
         <v>129</v>
       </c>
       <c r="C335" t="n">
-        <v>99.41564</v>
+        <v>99.32008</v>
       </c>
       <c r="D335" t="n">
-        <v>113.4389</v>
+        <v>113.2185</v>
       </c>
       <c r="E335" t="n">
-        <v>178.727447509766</v>
+        <v>177.934204101562</v>
       </c>
       <c r="F335" t="n">
-        <v>98.82246</v>
+        <v>177.934204101562</v>
       </c>
       <c r="G335" t="n">
         <v>328.35539195552</v>
       </c>
       <c r="H335" t="n">
-        <v>230.01507225864</v>
+        <v>229.89384726212</v>
       </c>
     </row>
     <row r="336">
@@ -65178,22 +65115,22 @@
         <v>131.5</v>
       </c>
       <c r="C336" t="n">
-        <v>99.55224</v>
+        <v>99.48232</v>
       </c>
       <c r="D336" t="n">
-        <v>112.9049</v>
+        <v>112.8374</v>
       </c>
       <c r="E336" t="n">
-        <v>175.890411376953</v>
+        <v>175.861618041992</v>
       </c>
       <c r="F336" t="n">
-        <v>100.8802</v>
+        <v>175.861618041992</v>
       </c>
       <c r="G336" t="n">
         <v>310.027911418558</v>
       </c>
       <c r="H336" t="n">
-        <v>230.923631794061</v>
+        <v>230.932967451745</v>
       </c>
     </row>
     <row r="337">
@@ -65204,22 +65141,22 @@
         <v>127</v>
       </c>
       <c r="C337" t="n">
-        <v>99.57765</v>
+        <v>99.51741</v>
       </c>
       <c r="D337" t="n">
-        <v>111.192</v>
+        <v>111.1252</v>
       </c>
       <c r="E337" t="n">
-        <v>174.691497802734</v>
+        <v>174.176940917969</v>
       </c>
       <c r="F337" t="n">
-        <v>103.2334</v>
+        <v>174.176940917969</v>
       </c>
       <c r="G337" t="n">
         <v>277.841936024409</v>
       </c>
       <c r="H337" t="n">
-        <v>230.803551505528</v>
+        <v>230.646610572105</v>
       </c>
     </row>
     <row r="338">
@@ -65230,22 +65167,22 @@
         <v>127.4</v>
       </c>
       <c r="C338" t="n">
-        <v>99.66749</v>
+        <v>99.61972</v>
       </c>
       <c r="D338" t="n">
-        <v>112.8039</v>
+        <v>112.7365</v>
       </c>
       <c r="E338" t="n">
-        <v>173.84684753418</v>
+        <v>173.863494873047</v>
       </c>
       <c r="F338" t="n">
-        <v>99.10604</v>
+        <v>173.863494873047</v>
       </c>
       <c r="G338" t="n">
         <v>280.020759305536</v>
       </c>
       <c r="H338" t="n">
-        <v>231.782158563912</v>
+        <v>231.746794904534</v>
       </c>
     </row>
     <row r="339">
@@ -65256,22 +65193,22 @@
         <v>125.7</v>
       </c>
       <c r="C339" t="n">
-        <v>99.86781</v>
+        <v>99.81903</v>
       </c>
       <c r="D339" t="n">
-        <v>113.4615</v>
+        <v>113.3938</v>
       </c>
       <c r="E339" t="n">
-        <v>175.474731445312</v>
+        <v>175.243713378906</v>
       </c>
       <c r="F339" t="n">
-        <v>107.0811</v>
+        <v>175.243713378906</v>
       </c>
       <c r="G339" t="n">
         <v>284.411015986104</v>
       </c>
       <c r="H339" t="n">
-        <v>233.775485127561</v>
+        <v>233.415371827846</v>
       </c>
     </row>
     <row r="340">
@@ -65282,22 +65219,22 @@
         <v>128</v>
       </c>
       <c r="C340" t="n">
-        <v>100.0603</v>
+        <v>100.0755</v>
       </c>
       <c r="D340" t="n">
-        <v>112.0577</v>
+        <v>112.0162</v>
       </c>
       <c r="E340" t="n">
-        <v>177.15934753418</v>
+        <v>178.9521484375</v>
       </c>
       <c r="F340" t="n">
-        <v>104.0716</v>
+        <v>178.9521484375</v>
       </c>
       <c r="G340" t="n">
         <v>276.057797334736</v>
       </c>
       <c r="H340" t="n">
-        <v>233.927439192894</v>
+        <v>234.206649938343</v>
       </c>
     </row>
     <row r="341">
@@ -65308,22 +65245,22 @@
         <v>126.6</v>
       </c>
       <c r="C341" t="n">
-        <v>100.3896</v>
+        <v>100.362</v>
       </c>
       <c r="D341" t="n">
-        <v>112.7405</v>
+        <v>112.5727</v>
       </c>
       <c r="E341" t="n">
-        <v>175.981506347656</v>
+        <v>176.455795288086</v>
       </c>
       <c r="F341" t="n">
-        <v>103.3118</v>
+        <v>176.455795288086</v>
       </c>
       <c r="G341" t="n">
         <v>298.503915139768</v>
       </c>
       <c r="H341" t="n">
-        <v>234.369562052969</v>
+        <v>234.328437396311</v>
       </c>
     </row>
     <row r="342">
@@ -65334,22 +65271,22 @@
         <v>121.5</v>
       </c>
       <c r="C342" t="n">
-        <v>100.8649</v>
+        <v>100.8279</v>
       </c>
       <c r="D342" t="n">
-        <v>114.1018</v>
+        <v>114.0337</v>
       </c>
       <c r="E342" t="n">
-        <v>177.272659301758</v>
+        <v>177.636566162109</v>
       </c>
       <c r="F342" t="n">
-        <v>99.48026</v>
+        <v>177.636566162109</v>
       </c>
       <c r="G342" t="n">
         <v>270.028504456526</v>
       </c>
       <c r="H342" t="n">
-        <v>235.246104215047</v>
+        <v>235.071258542857</v>
       </c>
     </row>
     <row r="343">
@@ -65360,22 +65297,22 @@
         <v>125.1</v>
       </c>
       <c r="C343" t="n">
-        <v>101.1486</v>
+        <v>101.145</v>
       </c>
       <c r="D343" t="n">
-        <v>114.2286</v>
+        <v>114.211</v>
       </c>
       <c r="E343" t="n">
-        <v>174.837127685547</v>
+        <v>175.036041259766</v>
       </c>
       <c r="F343" t="n">
-        <v>99.20244</v>
+        <v>175.036041259766</v>
       </c>
       <c r="G343" t="n">
         <v>272.109380371227</v>
       </c>
       <c r="H343" t="n">
-        <v>235.020267955001</v>
+        <v>235.050102129588</v>
       </c>
     </row>
     <row r="344">
@@ -65386,22 +65323,22 @@
         <v>126.3</v>
       </c>
       <c r="C344" t="n">
-        <v>101.302</v>
+        <v>101.2925</v>
       </c>
       <c r="D344" t="n">
-        <v>113.7457</v>
+        <v>113.7028</v>
       </c>
       <c r="E344" t="n">
-        <v>173.473495483398</v>
+        <v>173.562042236328</v>
       </c>
       <c r="F344" t="n">
-        <v>99.26073</v>
+        <v>173.562042236328</v>
       </c>
       <c r="G344" t="n">
         <v>286.317331861766</v>
       </c>
       <c r="H344" t="n">
-        <v>234.818150524559</v>
+        <v>234.918474072396</v>
       </c>
     </row>
     <row r="345">
@@ -65412,22 +65349,22 @@
         <v>125.7</v>
       </c>
       <c r="C345" t="n">
-        <v>101.4574</v>
+        <v>101.4328</v>
       </c>
       <c r="D345" t="n">
-        <v>118.6595</v>
+        <v>118.5906</v>
       </c>
       <c r="E345" t="n">
-        <v>180.318008422852</v>
+        <v>180.442352294922</v>
       </c>
       <c r="F345" t="n">
-        <v>103.9447</v>
+        <v>180.442352294922</v>
       </c>
       <c r="G345" t="n">
         <v>311.999891259368</v>
       </c>
       <c r="H345" t="n">
-        <v>235.945277647077</v>
+        <v>235.961512097277</v>
       </c>
     </row>
     <row r="346">
@@ -65438,22 +65375,22 @@
         <v>127.9</v>
       </c>
       <c r="C346" t="n">
-        <v>100.8163</v>
+        <v>100.8029</v>
       </c>
       <c r="D346" t="n">
-        <v>114.9012</v>
+        <v>114.8075</v>
       </c>
       <c r="E346" t="n">
-        <v>172.772720336914</v>
+        <v>172.637268066406</v>
       </c>
       <c r="F346" t="n">
-        <v>101.1709</v>
+        <v>172.637268066406</v>
       </c>
       <c r="G346" t="n">
         <v>349.759126403755</v>
       </c>
       <c r="H346" t="n">
-        <v>233.078542523665</v>
+        <v>232.667489388399</v>
       </c>
     </row>
     <row r="347">
@@ -65464,22 +65401,22 @@
         <v>122.5</v>
       </c>
       <c r="C347" t="n">
-        <v>98.37875</v>
+        <v>98.4523</v>
       </c>
       <c r="D347" t="n">
-        <v>96.1546</v>
+        <v>96.15655</v>
       </c>
       <c r="E347" t="n">
-        <v>149.828582763672</v>
+        <v>149.991348266602</v>
       </c>
       <c r="F347" t="n">
-        <v>95.78722</v>
+        <v>149.991348266602</v>
       </c>
       <c r="G347" t="n">
         <v>347.162227905237</v>
       </c>
       <c r="H347" t="n">
-        <v>218.851428288021</v>
+        <v>218.847040518728</v>
       </c>
     </row>
     <row r="348">
@@ -65490,22 +65427,22 @@
         <v>126.6</v>
       </c>
       <c r="C348" t="n">
-        <v>97.79372</v>
+        <v>97.87089</v>
       </c>
       <c r="D348" t="n">
-        <v>102.2916</v>
+        <v>102.2454</v>
       </c>
       <c r="E348" t="n">
-        <v>154.507263183594</v>
+        <v>154.222808837891</v>
       </c>
       <c r="F348" t="n">
-        <v>96.35997</v>
+        <v>154.222808837891</v>
       </c>
       <c r="G348" t="n">
         <v>302.121467114986</v>
       </c>
       <c r="H348" t="n">
-        <v>219.510171087168</v>
+        <v>219.346011771111</v>
       </c>
     </row>
     <row r="349">
@@ -65516,22 +65453,22 @@
         <v>125</v>
       </c>
       <c r="C349" t="n">
-        <v>98.25312</v>
+        <v>98.29948</v>
       </c>
       <c r="D349" t="n">
-        <v>114.085</v>
+        <v>114.0361</v>
       </c>
       <c r="E349" t="n">
-        <v>166.893951416016</v>
+        <v>166.562164306641</v>
       </c>
       <c r="F349" t="n">
-        <v>93.29574</v>
+        <v>166.562164306641</v>
       </c>
       <c r="G349" t="n">
         <v>269.977926285691</v>
       </c>
       <c r="H349" t="n">
-        <v>224.370126275037</v>
+        <v>224.27252319549</v>
       </c>
     </row>
     <row r="350">
@@ -65542,22 +65479,22 @@
         <v>123.9</v>
       </c>
       <c r="C350" t="n">
-        <v>98.83803</v>
+        <v>98.82003</v>
       </c>
       <c r="D350" t="n">
-        <v>118.8352</v>
+        <v>118.7615</v>
       </c>
       <c r="E350" t="n">
-        <v>171.91178894043</v>
+        <v>171.722198486328</v>
       </c>
       <c r="F350" t="n">
-        <v>97.21147</v>
+        <v>171.722198486328</v>
       </c>
       <c r="G350" t="n">
         <v>282.520523634855</v>
       </c>
       <c r="H350" t="n">
-        <v>228.756562243714</v>
+        <v>228.650322848266</v>
       </c>
     </row>
     <row r="351">
@@ -65568,22 +65505,22 @@
         <v>123.5</v>
       </c>
       <c r="C351" t="n">
-        <v>98.81816</v>
+        <v>98.84552</v>
       </c>
       <c r="D351" t="n">
-        <v>115.3984</v>
+        <v>115.3509</v>
       </c>
       <c r="E351" t="n">
-        <v>170.056243896484</v>
+        <v>169.647827148438</v>
       </c>
       <c r="F351" t="n">
-        <v>93.78981</v>
+        <v>169.647827148438</v>
       </c>
       <c r="G351" t="n">
         <v>286.982446282758</v>
       </c>
       <c r="H351" t="n">
-        <v>227.809510076025</v>
+        <v>227.856906227982</v>
       </c>
     </row>
     <row r="352">
@@ -65594,22 +65531,22 @@
         <v>127.6</v>
       </c>
       <c r="C352" t="n">
-        <v>98.99689</v>
+        <v>99.03889</v>
       </c>
       <c r="D352" t="n">
-        <v>117.7955</v>
+        <v>117.8201</v>
       </c>
       <c r="E352" t="n">
-        <v>173.067794799805</v>
+        <v>172.023315429688</v>
       </c>
       <c r="F352" t="n">
-        <v>94.56214</v>
+        <v>172.023315429688</v>
       </c>
       <c r="G352" t="n">
         <v>298.758177526572</v>
       </c>
       <c r="H352" t="n">
-        <v>229.837014715702</v>
+        <v>229.848375588415</v>
       </c>
     </row>
     <row r="353">
@@ -65620,22 +65557,22 @@
         <v>126.7</v>
       </c>
       <c r="C353" t="n">
-        <v>98.95519</v>
+        <v>99.09172</v>
       </c>
       <c r="D353" t="n">
-        <v>117.2755</v>
+        <v>117.3001</v>
       </c>
       <c r="E353" t="n">
-        <v>173.109069824219</v>
+        <v>174.415069580078</v>
       </c>
       <c r="F353" t="n">
-        <v>96.61925</v>
+        <v>174.415069580078</v>
       </c>
       <c r="G353" t="n">
         <v>320.976095709972</v>
       </c>
       <c r="H353" t="n">
-        <v>228.825731850953</v>
+        <v>228.928982086061</v>
       </c>
     </row>
     <row r="354">
@@ -65646,22 +65583,22 @@
         <v>120.3</v>
       </c>
       <c r="C354" t="n">
-        <v>99.00507</v>
+        <v>99.08965</v>
       </c>
       <c r="D354" t="n">
         <v>117.867</v>
       </c>
       <c r="E354" t="n">
-        <v>175.859725952148</v>
+        <v>176.321441650391</v>
       </c>
       <c r="F354" t="n">
-        <v>97.89785</v>
+        <v>176.321441650391</v>
       </c>
       <c r="G354" t="n">
         <v>293.717898806925</v>
       </c>
       <c r="H354" t="n">
-        <v>229.596874567291</v>
+        <v>229.540222468231</v>
       </c>
     </row>
     <row r="355">
@@ -65672,22 +65609,22 @@
         <v>121.2</v>
       </c>
       <c r="C355" t="n">
-        <v>98.96372</v>
+        <v>99.14004</v>
       </c>
       <c r="D355" t="n">
-        <v>119.4379</v>
+        <v>119.4376</v>
       </c>
       <c r="E355" t="n">
-        <v>177.609390258789</v>
+        <v>177.94775390625</v>
       </c>
       <c r="F355" t="n">
-        <v>97.92936</v>
+        <v>177.94775390625</v>
       </c>
       <c r="G355" t="n">
         <v>297.666770239201</v>
       </c>
       <c r="H355" t="n">
-        <v>231.093846189469</v>
+        <v>230.908282194142</v>
       </c>
     </row>
     <row r="356">
@@ -65698,22 +65635,22 @@
         <v>124.2</v>
       </c>
       <c r="C356" t="n">
-        <v>99.02024</v>
+        <v>99.07849</v>
       </c>
       <c r="D356" t="n">
-        <v>121.2038</v>
+        <v>121.1787</v>
       </c>
       <c r="E356" t="n">
-        <v>179.413818359375</v>
+        <v>179.478210449219</v>
       </c>
       <c r="F356" t="n">
-        <v>99.16934</v>
+        <v>179.478210449219</v>
       </c>
       <c r="G356" t="n">
         <v>300.025624724448</v>
       </c>
       <c r="H356" t="n">
-        <v>233.471801866759</v>
+        <v>233.233528595837</v>
       </c>
     </row>
     <row r="357">
@@ -65724,22 +65661,22 @@
         <v>124.4</v>
       </c>
       <c r="C357" t="n">
-        <v>98.72597</v>
+        <v>98.85982</v>
       </c>
       <c r="D357" t="n">
-        <v>116.9038</v>
+        <v>116.8285</v>
       </c>
       <c r="E357" t="n">
-        <v>175.428939819336</v>
+        <v>175.545776367188</v>
       </c>
       <c r="F357" t="n">
-        <v>97.73723</v>
+        <v>175.545776367188</v>
       </c>
       <c r="G357" t="n">
         <v>282.481127313322</v>
       </c>
       <c r="H357" t="n">
-        <v>231.597023297769</v>
+        <v>231.554247189947</v>
       </c>
     </row>
     <row r="358">
@@ -65750,22 +65687,22 @@
         <v>126.9</v>
       </c>
       <c r="C358" t="n">
-        <v>98.87035</v>
+        <v>99.01772</v>
       </c>
       <c r="D358" t="n">
-        <v>118.5221</v>
+        <v>118.495</v>
       </c>
       <c r="E358" t="n">
-        <v>176.320556640625</v>
+        <v>176.013732910156</v>
       </c>
       <c r="F358" t="n">
-        <v>99.3444</v>
+        <v>176.013732910156</v>
       </c>
       <c r="G358" t="n">
         <v>259.280619551579</v>
       </c>
       <c r="H358" t="n">
-        <v>232.303394218827</v>
+        <v>232.299851865898</v>
       </c>
     </row>
     <row r="359">
@@ -65776,22 +65713,22 @@
         <v>124.9</v>
       </c>
       <c r="C359" t="n">
-        <v>99.0363</v>
+        <v>99.12198</v>
       </c>
       <c r="D359" t="n">
-        <v>119.7989</v>
+        <v>119.6738</v>
       </c>
       <c r="E359" t="n">
-        <v>175.626678466797</v>
+        <v>176.51921081543</v>
       </c>
       <c r="F359" t="n">
-        <v>100.5372</v>
+        <v>176.51921081543</v>
       </c>
       <c r="G359" t="n">
         <v>265.850024722558</v>
       </c>
       <c r="H359" t="n">
-        <v>231.560023357327</v>
+        <v>231.772531202163</v>
       </c>
     </row>
     <row r="360">
@@ -65802,22 +65739,22 @@
         <v>124.1</v>
       </c>
       <c r="C360" t="n">
-        <v>99.15775</v>
+        <v>99.18097</v>
       </c>
       <c r="D360" t="n">
-        <v>122.0971</v>
+        <v>122.02</v>
       </c>
       <c r="E360" t="n">
-        <v>178.491622924805</v>
+        <v>177.879852294922</v>
       </c>
       <c r="F360" t="n">
-        <v>98.7291</v>
+        <v>177.879852294922</v>
       </c>
       <c r="G360" t="n">
         <v>257.155637517415</v>
       </c>
       <c r="H360" t="n">
-        <v>230.886183689357</v>
+        <v>230.831534725482</v>
       </c>
     </row>
     <row r="361">
@@ -65828,22 +65765,22 @@
         <v>123.9</v>
       </c>
       <c r="C361" t="n">
-        <v>99.56221</v>
+        <v>99.64679</v>
       </c>
       <c r="D361" t="n">
-        <v>125.6964</v>
+        <v>125.6663</v>
       </c>
       <c r="E361" t="n">
-        <v>188.625671386719</v>
+        <v>187.97119140625</v>
       </c>
       <c r="F361" t="n">
-        <v>103.3226</v>
+        <v>187.97119140625</v>
       </c>
       <c r="G361" t="n">
         <v>251.323823032764</v>
       </c>
       <c r="H361" t="n">
-        <v>236.854591537727</v>
+        <v>236.459207542089</v>
       </c>
     </row>
     <row r="362">
@@ -65854,22 +65791,22 @@
         <v>123.4</v>
       </c>
       <c r="C362" t="n">
-        <v>99.61244</v>
+        <v>99.34487</v>
       </c>
       <c r="D362" t="n">
-        <v>123.4813</v>
+        <v>123.3764</v>
       </c>
       <c r="E362" t="n">
-        <v>178.288177490234</v>
+        <v>178.046020507812</v>
       </c>
       <c r="F362" t="n">
-        <v>99.79612</v>
+        <v>178.046020507812</v>
       </c>
       <c r="G362" t="n">
         <v>263.884633407971</v>
       </c>
       <c r="H362" t="n">
-        <v>233.692582740698</v>
+        <v>233.713916142526</v>
       </c>
     </row>
     <row r="363">
@@ -65880,22 +65817,22 @@
         <v>128.7</v>
       </c>
       <c r="C363" t="n">
-        <v>99.71182</v>
+        <v>99.41697</v>
       </c>
       <c r="D363" t="n">
-        <v>123.6785</v>
+        <v>123.6227</v>
       </c>
       <c r="E363" t="n">
-        <v>182.730728149414</v>
+        <v>182.289321899414</v>
       </c>
       <c r="F363" t="n">
-        <v>104.1126</v>
+        <v>182.289321899414</v>
       </c>
       <c r="G363" t="n">
         <v>251.444335701322</v>
       </c>
       <c r="H363" t="n">
-        <v>236.847432607698</v>
+        <v>236.490437466299</v>
       </c>
     </row>
     <row r="364">
@@ -65904,22 +65841,22 @@
       </c>
       <c r="B364"/>
       <c r="C364" t="n">
-        <v>99.87675</v>
+        <v>99.73806</v>
       </c>
       <c r="D364" t="n">
-        <v>125.3688</v>
+        <v>125.4586</v>
       </c>
       <c r="E364" t="n">
-        <v>181.247543334961</v>
+        <v>182.767913818359</v>
       </c>
       <c r="F364" t="n">
-        <v>103.8999</v>
+        <v>182.767913818359</v>
       </c>
       <c r="G364" t="n">
         <v>244.529944070962</v>
       </c>
       <c r="H364" t="n">
-        <v>238.299307369583</v>
+        <v>238.720542291606</v>
       </c>
     </row>
     <row r="365">
@@ -65928,22 +65865,22 @@
       </c>
       <c r="B365"/>
       <c r="C365" t="n">
-        <v>99.57958</v>
+        <v>99.35327</v>
       </c>
       <c r="D365" t="n">
-        <v>124.0298</v>
+        <v>123.9204</v>
       </c>
       <c r="E365" t="n">
-        <v>180.529632568359</v>
+        <v>181.410659790039</v>
       </c>
       <c r="F365" t="n">
-        <v>104.5017</v>
+        <v>181.410659790039</v>
       </c>
       <c r="G365" t="n">
         <v>227.264646485272</v>
       </c>
       <c r="H365" t="n">
-        <v>236.159379589404</v>
+        <v>236.388242593417</v>
       </c>
     </row>
     <row r="366">
@@ -65952,22 +65889,22 @@
       </c>
       <c r="B366"/>
       <c r="C366" t="n">
-        <v>99.43676</v>
+        <v>99.31601</v>
       </c>
       <c r="D366" t="n">
-        <v>124.8656</v>
+        <v>124.8783</v>
       </c>
       <c r="E366" t="n">
-        <v>180.577041625977</v>
+        <v>181.141464233398</v>
       </c>
       <c r="F366" t="n">
-        <v>111.9228</v>
+        <v>181.141464233398</v>
       </c>
       <c r="G366" t="n">
         <v>215.451922549565</v>
       </c>
       <c r="H366" t="n">
-        <v>237.970722030855</v>
+        <v>237.7994804017</v>
       </c>
     </row>
     <row r="367">
@@ -65976,22 +65913,22 @@
       </c>
       <c r="B367"/>
       <c r="C367" t="n">
-        <v>98.45265</v>
+        <v>98.26225</v>
       </c>
       <c r="D367" t="n">
-        <v>111.1411</v>
+        <v>111.1307</v>
       </c>
       <c r="E367" t="n">
-        <v>162.265090942383</v>
+        <v>162.6376953125</v>
       </c>
       <c r="F367" t="n">
-        <v>98.54633</v>
+        <v>162.6376953125</v>
       </c>
       <c r="G367" t="n">
         <v>230.267079922405</v>
       </c>
       <c r="H367" t="n">
-        <v>226.681390977711</v>
+        <v>226.565832947523</v>
       </c>
     </row>
     <row r="368">
@@ -66000,22 +65937,22 @@
       </c>
       <c r="B368"/>
       <c r="C368" t="n">
-        <v>99.88517</v>
+        <v>99.66751</v>
       </c>
       <c r="D368" t="n">
-        <v>131.5841</v>
+        <v>131.5676</v>
       </c>
       <c r="E368" t="n">
-        <v>187.891693115234</v>
+        <v>187.933242797852</v>
       </c>
       <c r="F368" t="n">
-        <v>109.0319</v>
+        <v>187.933242797852</v>
       </c>
       <c r="G368" t="n">
         <v>221.505527868477</v>
       </c>
       <c r="H368" t="n">
-        <v>241.198067255924</v>
+        <v>241.201985755933</v>
       </c>
     </row>
     <row r="369">
@@ -66024,22 +65961,22 @@
       </c>
       <c r="B369"/>
       <c r="C369" t="n">
-        <v>99.90229</v>
+        <v>99.60308</v>
       </c>
       <c r="D369" t="n">
-        <v>125.8369</v>
+        <v>125.7718</v>
       </c>
       <c r="E369" t="n">
-        <v>180.991119384766</v>
+        <v>181.109359741211</v>
       </c>
       <c r="F369" t="n">
-        <v>114.5862</v>
+        <v>181.109359741211</v>
       </c>
       <c r="G369" t="n">
         <v>211.38548023816</v>
       </c>
       <c r="H369" t="n">
-        <v>237.90571363788</v>
+        <v>237.774505538342</v>
       </c>
     </row>
     <row r="370">
@@ -66048,22 +65985,22 @@
       </c>
       <c r="B370"/>
       <c r="C370" t="n">
-        <v>100.1379</v>
+        <v>99.83798</v>
       </c>
       <c r="D370" t="n">
-        <v>129.2385</v>
+        <v>129.1018</v>
       </c>
       <c r="E370" t="n">
-        <v>186.383285522461</v>
+        <v>186.931518554688</v>
       </c>
       <c r="F370" t="n">
-        <v>108.7982</v>
+        <v>186.931518554688</v>
       </c>
       <c r="G370" t="n">
         <v>206.398225147812</v>
       </c>
       <c r="H370" t="n">
-        <v>240.220536231577</v>
+        <v>240.111828927784</v>
       </c>
     </row>
     <row r="371">
@@ -66072,22 +66009,22 @@
       </c>
       <c r="B371"/>
       <c r="C371" t="n">
-        <v>100.6141</v>
+        <v>100.2287</v>
       </c>
       <c r="D371" t="n">
-        <v>128.5134</v>
+        <v>128.498</v>
       </c>
       <c r="E371" t="n">
-        <v>186.45719909668</v>
+        <v>185.119812011719</v>
       </c>
       <c r="F371" t="n">
-        <v>110.5801</v>
+        <v>185.119812011719</v>
       </c>
       <c r="G371" t="n">
         <v>191.901406174593</v>
       </c>
       <c r="H371" t="n">
-        <v>240.636117759258</v>
+        <v>239.95815735727</v>
       </c>
     </row>
     <row r="372">
@@ -66096,22 +66033,22 @@
       </c>
       <c r="B372"/>
       <c r="C372" t="n">
-        <v>101.2517</v>
+        <v>100.8512</v>
       </c>
       <c r="D372" t="n">
-        <v>131.2085</v>
+        <v>131.1215</v>
       </c>
       <c r="E372" t="n">
-        <v>186.434356689453</v>
+        <v>185.928695678711</v>
       </c>
       <c r="F372" t="n">
-        <v>117.4711</v>
+        <v>185.928695678711</v>
       </c>
       <c r="G372" t="n">
         <v>188.697413985414</v>
       </c>
       <c r="H372" t="n">
-        <v>243.105044327468</v>
+        <v>242.794462777233</v>
       </c>
     </row>
     <row r="373">
@@ -66120,22 +66057,22 @@
       </c>
       <c r="B373"/>
       <c r="C373" t="n">
-        <v>101.5762</v>
+        <v>101.1626</v>
       </c>
       <c r="D373" t="n">
-        <v>130.6531</v>
+        <v>130.6388</v>
       </c>
       <c r="E373" t="n">
-        <v>184.518005371094</v>
+        <v>183.729553222656</v>
       </c>
       <c r="F373" t="n">
-        <v>113.2994</v>
+        <v>183.729553222656</v>
       </c>
       <c r="G373" t="n">
         <v>179.912295918367</v>
       </c>
       <c r="H373" t="n">
-        <v>240.717752792172</v>
+        <v>241.291565052642</v>
       </c>
     </row>
     <row r="374">
@@ -66144,22 +66081,22 @@
       </c>
       <c r="B374"/>
       <c r="C374" t="n">
-        <v>102.0437</v>
+        <v>101.4454</v>
       </c>
       <c r="D374" t="n">
-        <v>132.0671</v>
+        <v>131.9332</v>
       </c>
       <c r="E374" t="n">
-        <v>190.442108154297</v>
+        <v>190.224792480469</v>
       </c>
       <c r="F374" t="n">
-        <v>116.3585</v>
+        <v>190.224792480469</v>
       </c>
       <c r="G374" t="n">
         <v>183.62362029226</v>
       </c>
       <c r="H374" t="n">
-        <v>242.07540091792</v>
+        <v>243.663461137109</v>
       </c>
     </row>
     <row r="375">
@@ -66168,20 +66105,22 @@
       </c>
       <c r="B375"/>
       <c r="C375" t="n">
-        <v>101.7888</v>
+        <v>101.0048</v>
       </c>
       <c r="D375" t="n">
-        <v>131.9224</v>
+        <v>131.8368</v>
       </c>
       <c r="E375" t="n">
-        <v>190.888442993164</v>
-      </c>
-      <c r="F375"/>
+        <v>190.592468261719</v>
+      </c>
+      <c r="F375" t="n">
+        <v>190.592468261719</v>
+      </c>
       <c r="G375" t="n">
         <v>193.378794762268</v>
       </c>
       <c r="H375" t="n">
-        <v>241.438742613506</v>
+        <v>243.814532483014</v>
       </c>
     </row>
     <row r="376">
@@ -66190,18 +66129,22 @@
       </c>
       <c r="B376"/>
       <c r="C376" t="n">
-        <v>100.6541</v>
+        <v>99.12529</v>
       </c>
       <c r="D376" t="n">
-        <v>115.2499</v>
-      </c>
-      <c r="E376"/>
-      <c r="F376"/>
+        <v>115.1959</v>
+      </c>
+      <c r="E376" t="n">
+        <v>169.402206420898</v>
+      </c>
+      <c r="F376" t="n">
+        <v>169.402206420898</v>
+      </c>
       <c r="G376" t="n">
         <v>274.027774258465</v>
       </c>
       <c r="H376" t="n">
-        <v>234.770204542521</v>
+        <v>229.329511108198</v>
       </c>
     </row>
     <row r="377">
@@ -66209,15 +66152,19 @@
         <v>46113</v>
       </c>
       <c r="B377"/>
-      <c r="C377"/>
-      <c r="D377"/>
+      <c r="C377" t="n">
+        <v>98.68008</v>
+      </c>
+      <c r="D377" t="n">
+        <v>128.9337</v>
+      </c>
       <c r="E377"/>
       <c r="F377"/>
       <c r="G377" t="n">
         <v>287.80193070092</v>
       </c>
       <c r="H377" t="n">
-        <v>240.242698010407</v>
+        <v>237.589960098316</v>
       </c>
     </row>
     <row r="378">
@@ -66230,7 +66177,9 @@
       <c r="E378"/>
       <c r="F378"/>
       <c r="G378"/>
-      <c r="H378"/>
+      <c r="H378" t="n">
+        <v>240.177314763786</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" s="1" t="n">
@@ -72536,10 +72485,10 @@
         <v>46082</v>
       </c>
       <c r="B376" t="n">
-        <v>0</v>
+        <v>11832.5404129962</v>
       </c>
       <c r="C376" t="n">
-        <v>0</v>
+        <v>4045.69995117188</v>
       </c>
       <c r="D376" t="n">
         <v>0.0250989259468626</v>
@@ -72569,21 +72518,13 @@
       <c r="A378" s="1" t="n">
         <v>46143</v>
       </c>
-      <c r="B378"/>
+      <c r="B378" t="n">
+        <v>0</v>
+      </c>
       <c r="C378"/>
       <c r="D378"/>
       <c r="E378"/>
       <c r="F378"/>
-    </row>
-    <row r="379">
-      <c r="A379" s="1" t="n">
-        <v>46174</v>
-      </c>
-      <c r="B379"/>
-      <c r="C379"/>
-      <c r="D379"/>
-      <c r="E379"/>
-      <c r="F379"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -79022,15 +78963,6 @@
         <v>7379.95333333333</v>
       </c>
     </row>
-    <row r="379">
-      <c r="A379" s="1" t="n">
-        <v>46174</v>
-      </c>
-      <c r="B379"/>
-      <c r="C379"/>
-      <c r="D379"/>
-      <c r="E379"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/blocks_real.xlsx
+++ b/blocks_real.xlsx
@@ -15548,199 +15548,52 @@
       <c r="A374" s="1" t="n">
         <v>46023</v>
       </c>
-      <c r="B374" t="n">
-        <v>38894468.5382381</v>
-      </c>
-      <c r="C374" t="n">
-        <v>-2324607.93804453</v>
-      </c>
-      <c r="D374" t="n">
-        <v>36569860.6001936</v>
-      </c>
-      <c r="E374" t="n">
-        <v>20033142.303969</v>
-      </c>
-      <c r="F374" t="n">
-        <v>12011926.42788</v>
-      </c>
-      <c r="G374" t="n">
-        <v>60356.2439496612</v>
-      </c>
-      <c r="H374" t="n">
-        <v>6397486.93126815</v>
-      </c>
-      <c r="I374" t="n">
-        <v>-770622.458857696</v>
-      </c>
-      <c r="J374" t="n">
-        <v>-879800.580832527</v>
-      </c>
-      <c r="K374" t="n">
-        <v>-122362.052274927</v>
-      </c>
-      <c r="L374" t="n">
-        <v>-138827.686350436</v>
-      </c>
-      <c r="M374" t="n">
-        <v>1047911.9070668</v>
-      </c>
+      <c r="B374"/>
+      <c r="C374"/>
+      <c r="D374"/>
+      <c r="E374"/>
+      <c r="F374"/>
+      <c r="G374"/>
+      <c r="H374"/>
+      <c r="I374"/>
+      <c r="J374"/>
+      <c r="K374"/>
+      <c r="L374"/>
+      <c r="M374"/>
     </row>
     <row r="375">
       <c r="A375" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="B375" t="n">
-        <v>29545833.8164251</v>
-      </c>
-      <c r="C375" t="n">
-        <v>-2446720.77294686</v>
-      </c>
-      <c r="D375" t="n">
-        <v>27099113.0434783</v>
-      </c>
-      <c r="E375" t="n">
-        <v>14990038.647343</v>
-      </c>
-      <c r="F375" t="n">
-        <v>9567246.3768116</v>
-      </c>
-      <c r="G375" t="n">
-        <v>1106809.66183575</v>
-      </c>
-      <c r="H375" t="n">
-        <v>2245240.57971015</v>
-      </c>
-      <c r="I375" t="n">
-        <v>-56621.2560386473</v>
-      </c>
-      <c r="J375" t="n">
-        <v>-699714.009661836</v>
-      </c>
-      <c r="K375" t="n">
-        <v>-56055.0724637681</v>
-      </c>
-      <c r="L375" t="n">
-        <v>-148520.77294686</v>
-      </c>
-      <c r="M375" t="n">
-        <v>1331066.66666667</v>
-      </c>
+      <c r="B375"/>
+      <c r="C375"/>
+      <c r="D375"/>
+      <c r="E375"/>
+      <c r="F375"/>
+      <c r="G375"/>
+      <c r="H375"/>
+      <c r="I375"/>
+      <c r="J375"/>
+      <c r="K375"/>
+      <c r="L375"/>
+      <c r="M375"/>
     </row>
     <row r="376">
       <c r="A376" s="1" t="n">
         <v>46082</v>
       </c>
-      <c r="B376" t="n">
-        <v>36741078.9220404</v>
-      </c>
-      <c r="C376" t="n">
-        <v>-3614629.45139557</v>
-      </c>
-      <c r="D376" t="n">
-        <v>33126449.4706448</v>
-      </c>
-      <c r="E376" t="n">
-        <v>23812653.5129933</v>
-      </c>
-      <c r="F376" t="n">
-        <v>16393634.2637151</v>
-      </c>
-      <c r="G376" t="n">
-        <v>1504504.33108758</v>
-      </c>
-      <c r="H376" t="n">
-        <v>1093974.9759384</v>
-      </c>
-      <c r="I376" t="n">
-        <v>-24024.0615976901</v>
-      </c>
-      <c r="J376" t="n">
-        <v>-891192.492781521</v>
-      </c>
-      <c r="K376" t="n">
-        <v>-62339.749759384</v>
-      </c>
-      <c r="L376" t="n">
-        <v>-152010.587102984</v>
-      </c>
-      <c r="M376" t="n">
-        <v>1242749.75938402</v>
-      </c>
-    </row>
-    <row r="377">
-      <c r="A377" s="1" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B377" t="n">
-        <v>29612579.4481446</v>
-      </c>
-      <c r="C377" t="n">
-        <v>-1520869.64795433</v>
-      </c>
-      <c r="D377" t="n">
-        <v>28091709.8001903</v>
-      </c>
-      <c r="E377" t="n">
-        <v>18450498.5727878</v>
-      </c>
-      <c r="F377" t="n">
-        <v>13926738.3444339</v>
-      </c>
-      <c r="G377" t="n">
-        <v>1219691.72216936</v>
-      </c>
-      <c r="H377" t="n">
-        <v>1032004.75737393</v>
-      </c>
-      <c r="I377" t="n">
-        <v>-10689.8192197907</v>
-      </c>
-      <c r="J377" t="n">
-        <v>-448478.591817317</v>
-      </c>
-      <c r="K377" t="n">
-        <v>-44232.159847764</v>
-      </c>
-      <c r="L377" t="n">
-        <v>-157884.871550904</v>
-      </c>
-      <c r="M377" t="n">
-        <v>1134169.36251189</v>
-      </c>
-    </row>
-    <row r="378">
-      <c r="A378" s="1" t="n">
-        <v>46143</v>
-      </c>
-      <c r="B378"/>
-      <c r="C378"/>
-      <c r="D378"/>
-      <c r="E378"/>
-      <c r="F378"/>
-      <c r="G378"/>
-      <c r="H378"/>
-      <c r="I378"/>
-      <c r="J378"/>
-      <c r="K378"/>
-      <c r="L378"/>
-      <c r="M378"/>
-    </row>
-    <row r="379">
-      <c r="A379" s="1" t="n">
-        <v>46174</v>
-      </c>
-      <c r="B379"/>
-      <c r="C379"/>
-      <c r="D379"/>
-      <c r="E379"/>
-      <c r="F379"/>
-      <c r="G379"/>
-      <c r="H379"/>
-      <c r="I379"/>
-      <c r="J379"/>
-      <c r="K379"/>
-      <c r="L379"/>
-      <c r="M379"/>
+      <c r="B376"/>
+      <c r="C376"/>
+      <c r="D376"/>
+      <c r="E376"/>
+      <c r="F376"/>
+      <c r="G376"/>
+      <c r="H376"/>
+      <c r="I376"/>
+      <c r="J376"/>
+      <c r="K376"/>
+      <c r="L376"/>
+      <c r="M376"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -16757,9 +16610,7 @@
       <c r="A126" s="1" t="n">
         <v>46082</v>
       </c>
-      <c r="B126" t="n">
-        <v>437142.3</v>
-      </c>
+      <c r="B126"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -20882,60 +20733,21 @@
       <c r="B374" t="n">
         <v>0.18</v>
       </c>
-      <c r="C374" t="n">
-        <v>103.3</v>
-      </c>
+      <c r="C374"/>
     </row>
     <row r="375">
       <c r="A375" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="B375" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="C375" t="n">
-        <v>103.5</v>
-      </c>
+      <c r="B375"/>
+      <c r="C375"/>
     </row>
     <row r="376">
       <c r="A376" s="1" t="n">
         <v>46082</v>
       </c>
-      <c r="B376" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="C376" t="n">
-        <v>103.9</v>
-      </c>
-    </row>
-    <row r="377">
-      <c r="A377" s="1" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B377" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="C377" t="n">
-        <v>105.1</v>
-      </c>
-    </row>
-    <row r="378">
-      <c r="A378" s="1" t="n">
-        <v>46143</v>
-      </c>
-      <c r="B378" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="C378"/>
-    </row>
-    <row r="379">
-      <c r="A379" s="1" t="n">
-        <v>46174</v>
-      </c>
-      <c r="B379" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="C379"/>
+      <c r="B376"/>
+      <c r="C376"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -32672,157 +32484,43 @@
       <c r="A374" s="1" t="n">
         <v>46023</v>
       </c>
-      <c r="B374" t="n">
-        <v>415531.472410455</v>
-      </c>
-      <c r="C374" t="n">
-        <v>10862849.9515973</v>
-      </c>
-      <c r="D374" t="n">
-        <v>-38309.7773475315</v>
-      </c>
-      <c r="E374" t="n">
-        <v>16924387.232333</v>
-      </c>
-      <c r="F374" t="n">
-        <v>-1205051.30687319</v>
-      </c>
-      <c r="G374" t="n">
-        <v>175431.752178122</v>
-      </c>
-      <c r="H374" t="n">
-        <v>3035530.49370765</v>
-      </c>
-      <c r="I374" t="n">
-        <v>-252187.802516941</v>
-      </c>
-      <c r="J374" t="n">
-        <v>2350156.82478219</v>
-      </c>
+      <c r="B374"/>
+      <c r="C374"/>
+      <c r="D374"/>
+      <c r="E374"/>
+      <c r="F374"/>
+      <c r="G374"/>
+      <c r="H374"/>
+      <c r="I374"/>
+      <c r="J374"/>
     </row>
     <row r="375">
       <c r="A375" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="B375" t="n">
-        <v>5534117.65797101</v>
-      </c>
-      <c r="C375" t="n">
-        <v>3565542.99516908</v>
-      </c>
-      <c r="D375" t="n">
-        <v>-56744.9275362319</v>
-      </c>
-      <c r="E375" t="n">
-        <v>12336413.3101449</v>
-      </c>
-      <c r="F375" t="n">
-        <v>-1517906.28019324</v>
-      </c>
-      <c r="G375" t="n">
-        <v>66060.8695652174</v>
-      </c>
-      <c r="H375" t="n">
-        <v>551305.314009662</v>
-      </c>
-      <c r="I375" t="n">
-        <v>-91753.6231884058</v>
-      </c>
-      <c r="J375" t="n">
-        <v>1548643.47826087</v>
-      </c>
+      <c r="B375"/>
+      <c r="C375"/>
+      <c r="D375"/>
+      <c r="E375"/>
+      <c r="F375"/>
+      <c r="G375"/>
+      <c r="H375"/>
+      <c r="I375"/>
+      <c r="J375"/>
     </row>
     <row r="376">
       <c r="A376" s="1" t="n">
         <v>46082</v>
       </c>
-      <c r="B376" t="n">
-        <v>6166049.4292589</v>
-      </c>
-      <c r="C376" t="n">
-        <v>2128503.36862368</v>
-      </c>
-      <c r="D376" t="n">
-        <v>-19737.2473532243</v>
-      </c>
-      <c r="E376" t="n">
-        <v>10847345.8681424</v>
-      </c>
-      <c r="F376" t="n">
-        <v>-2566356.11164581</v>
-      </c>
-      <c r="G376" t="n">
-        <v>65954.7641963426</v>
-      </c>
-      <c r="H376" t="n">
-        <v>2981380.1732435</v>
-      </c>
-      <c r="I376" t="n">
-        <v>-28411.9345524543</v>
-      </c>
-      <c r="J376" t="n">
-        <v>1760451.39557267</v>
-      </c>
-    </row>
-    <row r="377">
-      <c r="A377" s="1" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B377" t="n">
-        <v>6135940.05708849</v>
-      </c>
-      <c r="C377" t="n">
-        <v>1518078.97240723</v>
-      </c>
-      <c r="D377" t="n">
-        <v>-7662.22645099905</v>
-      </c>
-      <c r="E377" t="n">
-        <v>9885460.51379639</v>
-      </c>
-      <c r="F377" t="n">
-        <v>-931356.803044719</v>
-      </c>
-      <c r="G377" t="n">
-        <v>69794.4814462417</v>
-      </c>
-      <c r="H377" t="n">
-        <v>572354.900095148</v>
-      </c>
-      <c r="I377" t="n">
-        <v>-17108.4681255947</v>
-      </c>
-      <c r="J377" t="n">
-        <v>991324.452901998</v>
-      </c>
-    </row>
-    <row r="378">
-      <c r="A378" s="1" t="n">
-        <v>46143</v>
-      </c>
-      <c r="B378"/>
-      <c r="C378"/>
-      <c r="D378"/>
-      <c r="E378"/>
-      <c r="F378"/>
-      <c r="G378"/>
-      <c r="H378"/>
-      <c r="I378"/>
-      <c r="J378"/>
-    </row>
-    <row r="379">
-      <c r="A379" s="1" t="n">
-        <v>46174</v>
-      </c>
-      <c r="B379"/>
-      <c r="C379"/>
-      <c r="D379"/>
-      <c r="E379"/>
-      <c r="F379"/>
-      <c r="G379"/>
-      <c r="H379"/>
-      <c r="I379"/>
-      <c r="J379"/>
+      <c r="B376"/>
+      <c r="C376"/>
+      <c r="D376"/>
+      <c r="E376"/>
+      <c r="F376"/>
+      <c r="G376"/>
+      <c r="H376"/>
+      <c r="I376"/>
+      <c r="J376"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -33186,7 +32884,7 @@
         <v>-1549.57450113536</v>
       </c>
       <c r="D24" t="n">
-        <v>4342.30141212713</v>
+        <v>4342.30141212714</v>
       </c>
       <c r="E24" t="n">
         <v>45.3728524231825</v>
@@ -33266,7 +32964,7 @@
         <v>-1408.16161261076</v>
       </c>
       <c r="D28" t="n">
-        <v>5195.81318390612</v>
+        <v>5195.81318390611</v>
       </c>
       <c r="E28" t="n">
         <v>144.63419358223</v>
@@ -33860,7 +33558,7 @@
         <v>36404</v>
       </c>
       <c r="B58" t="n">
-        <v>4678.60738956586</v>
+        <v>4678.60738956585</v>
       </c>
       <c r="C58" t="n">
         <v>-1845.47930978322</v>
@@ -40179,101 +39877,31 @@
       <c r="A374" s="1" t="n">
         <v>46023</v>
       </c>
-      <c r="B374" t="n">
-        <v>15411.4230396902</v>
-      </c>
-      <c r="C374" t="n">
-        <v>-3891.57792836399</v>
-      </c>
-      <c r="D374" t="n">
-        <v>16524.6853823814</v>
-      </c>
-      <c r="E374" t="n">
-        <v>36.7860600193611</v>
-      </c>
-      <c r="F374" t="n">
-        <v>2424.00774443369</v>
-      </c>
+      <c r="B374"/>
+      <c r="C374"/>
+      <c r="D374"/>
+      <c r="E374"/>
+      <c r="F374"/>
     </row>
     <row r="375">
       <c r="A375" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="B375" t="n">
-        <v>12397.1014492754</v>
-      </c>
-      <c r="C375" t="n">
-        <v>-4941.06280193237</v>
-      </c>
-      <c r="D375" t="n">
-        <v>12624.154589372</v>
-      </c>
-      <c r="E375" t="n">
-        <v>25.1207729468599</v>
-      </c>
-      <c r="F375" t="n">
-        <v>2301.44927536232</v>
-      </c>
+      <c r="B375"/>
+      <c r="C375"/>
+      <c r="D375"/>
+      <c r="E375"/>
+      <c r="F375"/>
     </row>
     <row r="376">
       <c r="A376" s="1" t="n">
         <v>46082</v>
       </c>
-      <c r="B376" t="n">
-        <v>12541.8671799807</v>
-      </c>
-      <c r="C376" t="n">
-        <v>-6570.74109720885</v>
-      </c>
-      <c r="D376" t="n">
-        <v>11179.0182868142</v>
-      </c>
-      <c r="E376" t="n">
-        <v>20.2117420596728</v>
-      </c>
-      <c r="F376" t="n">
-        <v>2335.89990375361</v>
-      </c>
-    </row>
-    <row r="377">
-      <c r="A377" s="1" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B377" t="n">
-        <v>11644.1484300666</v>
-      </c>
-      <c r="C377" t="n">
-        <v>-3208.05581985411</v>
-      </c>
-      <c r="D377" t="n">
-        <v>13643.1969552807</v>
-      </c>
-      <c r="E377" t="n">
-        <v>40.9134157944815</v>
-      </c>
-      <c r="F377" t="n">
-        <v>1993.65683476055</v>
-      </c>
-    </row>
-    <row r="378">
-      <c r="A378" s="1" t="n">
-        <v>46143</v>
-      </c>
-      <c r="B378"/>
-      <c r="C378"/>
-      <c r="D378"/>
-      <c r="E378"/>
-      <c r="F378"/>
-    </row>
-    <row r="379">
-      <c r="A379" s="1" t="n">
-        <v>46174</v>
-      </c>
-      <c r="B379"/>
-      <c r="C379"/>
-      <c r="D379"/>
-      <c r="E379"/>
-      <c r="F379"/>
+      <c r="B376"/>
+      <c r="C376"/>
+      <c r="D376"/>
+      <c r="E376"/>
+      <c r="F376"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -41164,7 +40792,7 @@
         <v>36404</v>
       </c>
       <c r="B58" t="n">
-        <v>2210.58793314549</v>
+        <v>2210.5879331455</v>
       </c>
       <c r="C58" t="n">
         <v>189.066742695316</v>
@@ -46535,87 +46163,28 @@
       <c r="A374" s="1" t="n">
         <v>46023</v>
       </c>
-      <c r="B374" t="n">
-        <v>5004.84027105518</v>
-      </c>
-      <c r="C374" t="n">
-        <v>123.910939012585</v>
-      </c>
-      <c r="D374" t="n">
-        <v>1767.6669893514</v>
-      </c>
-      <c r="E374" t="n">
-        <v>1891.57792836399</v>
-      </c>
+      <c r="B374"/>
+      <c r="C374"/>
+      <c r="D374"/>
+      <c r="E374"/>
     </row>
     <row r="375">
       <c r="A375" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="B375" t="n">
-        <v>5168.11594202899</v>
-      </c>
-      <c r="C375" t="n">
-        <v>167.149758454106</v>
-      </c>
-      <c r="D375" t="n">
-        <v>2358.45410628019</v>
-      </c>
-      <c r="E375" t="n">
-        <v>2525.6038647343</v>
-      </c>
+      <c r="B375"/>
+      <c r="C375"/>
+      <c r="D375"/>
+      <c r="E375"/>
     </row>
     <row r="376">
       <c r="A376" s="1" t="n">
         <v>46082</v>
       </c>
-      <c r="B376" t="n">
-        <v>5207.89220404235</v>
-      </c>
-      <c r="C376" t="n">
-        <v>153.031761308951</v>
-      </c>
-      <c r="D376" t="n">
-        <v>2326.27526467757</v>
-      </c>
-      <c r="E376" t="n">
-        <v>2479.30702598653</v>
-      </c>
-    </row>
-    <row r="377">
-      <c r="A377" s="1" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B377" t="n">
-        <v>5207.10434506819</v>
-      </c>
-      <c r="C377" t="n">
-        <v>116.079923882017</v>
-      </c>
-      <c r="D377" t="n">
-        <v>1799.23882017127</v>
-      </c>
-      <c r="E377" t="n">
-        <v>1915.31874405328</v>
-      </c>
-    </row>
-    <row r="378">
-      <c r="A378" s="1" t="n">
-        <v>46143</v>
-      </c>
-      <c r="B378"/>
-      <c r="C378"/>
-      <c r="D378"/>
-      <c r="E378"/>
-    </row>
-    <row r="379">
-      <c r="A379" s="1" t="n">
-        <v>46174</v>
-      </c>
-      <c r="B379"/>
-      <c r="C379"/>
-      <c r="D379"/>
-      <c r="E379"/>
+      <c r="B376"/>
+      <c r="C376"/>
+      <c r="D376"/>
+      <c r="E376"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -57233,141 +56802,40 @@
       <c r="A374" s="1" t="n">
         <v>46023</v>
       </c>
-      <c r="B374" t="n">
-        <v>1803991.2875121</v>
-      </c>
-      <c r="C374" t="n">
-        <v>1565.34365924492</v>
-      </c>
-      <c r="D374" t="n">
-        <v>707478.218780252</v>
-      </c>
-      <c r="E374" t="n">
-        <v>1101759.92255566</v>
-      </c>
-      <c r="F374" t="n">
-        <v>-122362.052274927</v>
-      </c>
-      <c r="G374" t="n">
-        <v>-56448.2090997096</v>
-      </c>
-      <c r="H374" t="n">
-        <v>58609</v>
-      </c>
-      <c r="I374" t="n">
-        <v>599.6</v>
-      </c>
+      <c r="B374"/>
+      <c r="C374"/>
+      <c r="D374"/>
+      <c r="E374"/>
+      <c r="F374"/>
+      <c r="G374"/>
+      <c r="H374"/>
+      <c r="I374"/>
     </row>
     <row r="375">
       <c r="A375" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="B375" t="n">
-        <v>2110128.50241546</v>
-      </c>
-      <c r="C375" t="n">
-        <v>2636.71497584541</v>
-      </c>
-      <c r="D375" t="n">
-        <v>751660.869565217</v>
-      </c>
-      <c r="E375" t="n">
-        <v>1360300.48309179</v>
-      </c>
-      <c r="F375" t="n">
-        <v>-56055.0724637681</v>
-      </c>
-      <c r="G375" t="n">
-        <v>-50272.4637681159</v>
-      </c>
-      <c r="H375" t="n">
-        <v>58610</v>
-      </c>
-      <c r="I375" t="n">
-        <v>601.4</v>
-      </c>
+      <c r="B375"/>
+      <c r="C375"/>
+      <c r="D375"/>
+      <c r="E375"/>
+      <c r="F375"/>
+      <c r="G375"/>
+      <c r="H375"/>
+      <c r="I375"/>
     </row>
     <row r="376">
       <c r="A376" s="1" t="n">
         <v>46082</v>
       </c>
-      <c r="B376" t="n">
-        <v>1866200.19249278</v>
-      </c>
-      <c r="C376" t="n">
-        <v>712.223291626564</v>
-      </c>
-      <c r="D376" t="n">
-        <v>715628.488931665</v>
-      </c>
-      <c r="E376" t="n">
-        <v>1156601.53994225</v>
-      </c>
-      <c r="F376" t="n">
-        <v>-62339.749759384</v>
-      </c>
-      <c r="G376" t="n">
-        <v>-43282.0019249278</v>
-      </c>
-      <c r="H376" t="n">
-        <v>58611</v>
-      </c>
+      <c r="B376"/>
+      <c r="C376"/>
+      <c r="D376"/>
+      <c r="E376"/>
+      <c r="F376"/>
+      <c r="G376"/>
+      <c r="H376"/>
       <c r="I376"/>
-    </row>
-    <row r="377">
-      <c r="A377" s="1" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B377" t="n">
-        <v>1150601.3320647</v>
-      </c>
-      <c r="C377" t="n">
-        <v>863.939105613701</v>
-      </c>
-      <c r="D377" t="n">
-        <v>414217.887725975</v>
-      </c>
-      <c r="E377" t="n">
-        <v>741447.193149382</v>
-      </c>
-      <c r="F377" t="n">
-        <v>-44232.159847764</v>
-      </c>
-      <c r="G377" t="n">
-        <v>-35092.2930542341</v>
-      </c>
-      <c r="H377" t="n">
-        <v>58612</v>
-      </c>
-      <c r="I377"/>
-    </row>
-    <row r="378">
-      <c r="A378" s="1" t="n">
-        <v>46143</v>
-      </c>
-      <c r="B378"/>
-      <c r="C378"/>
-      <c r="D378"/>
-      <c r="E378"/>
-      <c r="F378"/>
-      <c r="G378"/>
-      <c r="H378" t="n">
-        <v>58613</v>
-      </c>
-      <c r="I378"/>
-    </row>
-    <row r="379">
-      <c r="A379" s="1" t="n">
-        <v>46174</v>
-      </c>
-      <c r="B379"/>
-      <c r="C379"/>
-      <c r="D379"/>
-      <c r="E379"/>
-      <c r="F379"/>
-      <c r="G379"/>
-      <c r="H379"/>
-      <c r="I379"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -57970,7 +57438,7 @@
         <v>54.2524995642211</v>
       </c>
       <c r="G28" t="n">
-        <v>122.250192685306</v>
+        <v>122.250192685307</v>
       </c>
       <c r="H28"/>
     </row>
@@ -57992,7 +57460,7 @@
         <v>53.8380133936198</v>
       </c>
       <c r="G29" t="n">
-        <v>114.785160332972</v>
+        <v>114.785160332971</v>
       </c>
       <c r="H29"/>
     </row>
@@ -58080,7 +57548,7 @@
         <v>54.0684531225462</v>
       </c>
       <c r="G33" t="n">
-        <v>117.592873277475</v>
+        <v>117.592873277474</v>
       </c>
       <c r="H33"/>
     </row>
@@ -58168,7 +57636,7 @@
         <v>55.5538432023376</v>
       </c>
       <c r="G37" t="n">
-        <v>107.612117139915</v>
+        <v>107.612117139916</v>
       </c>
       <c r="H37"/>
     </row>
@@ -58190,7 +57658,7 @@
         <v>56.1315846366565</v>
       </c>
       <c r="G38" t="n">
-        <v>99.0343748561887</v>
+        <v>99.0343748561888</v>
       </c>
       <c r="H38"/>
     </row>
@@ -58234,7 +57702,7 @@
         <v>56.7730784549298</v>
       </c>
       <c r="G40" t="n">
-        <v>89.9700502542306</v>
+        <v>89.9700502542303</v>
       </c>
       <c r="H40"/>
     </row>
@@ -58278,7 +57746,7 @@
         <v>56.9815238088347</v>
       </c>
       <c r="G42" t="n">
-        <v>89.1606210561612</v>
+        <v>89.1606210561613</v>
       </c>
       <c r="H42"/>
     </row>
@@ -58300,7 +57768,7 @@
         <v>56.4651819248757</v>
       </c>
       <c r="G43" t="n">
-        <v>81.6910873770982</v>
+        <v>81.6910873770983</v>
       </c>
       <c r="H43"/>
     </row>
@@ -58322,7 +57790,7 @@
         <v>56.8977386246237</v>
       </c>
       <c r="G44" t="n">
-        <v>84.3870202460052</v>
+        <v>84.3870202460053</v>
       </c>
       <c r="H44"/>
     </row>
@@ -58344,7 +57812,7 @@
         <v>58.1001548250512</v>
       </c>
       <c r="G45" t="n">
-        <v>80.8420468856442</v>
+        <v>80.8420468856444</v>
       </c>
       <c r="H45"/>
     </row>
@@ -58366,7 +57834,7 @@
         <v>57.5724679727907</v>
       </c>
       <c r="G46" t="n">
-        <v>92.2493322163269</v>
+        <v>92.2493322163271</v>
       </c>
       <c r="H46"/>
     </row>
@@ -58388,7 +57856,7 @@
         <v>59.0428508029851</v>
       </c>
       <c r="G47" t="n">
-        <v>93.9745806637975</v>
+        <v>93.9745806637976</v>
       </c>
       <c r="H47"/>
     </row>
@@ -58432,7 +57900,7 @@
         <v>58.1412928258319</v>
       </c>
       <c r="G49" t="n">
-        <v>72.4598168171145</v>
+        <v>72.4598168171143</v>
       </c>
       <c r="H49"/>
     </row>
@@ -58454,7 +57922,7 @@
         <v>57.2496749410041</v>
       </c>
       <c r="G50" t="n">
-        <v>78.4290580830351</v>
+        <v>78.4290580830353</v>
       </c>
       <c r="H50"/>
     </row>
@@ -58476,7 +57944,7 @@
         <v>58.9935998610504</v>
       </c>
       <c r="G51" t="n">
-        <v>75.6427530958432</v>
+        <v>75.6427530958431</v>
       </c>
       <c r="H51"/>
     </row>
@@ -58498,7 +57966,7 @@
         <v>59.7880207834673</v>
       </c>
       <c r="G52" t="n">
-        <v>91.7495849726348</v>
+        <v>91.7495849726346</v>
       </c>
       <c r="H52"/>
     </row>
@@ -58608,7 +58076,7 @@
         <v>62.5457930208471</v>
       </c>
       <c r="G57" t="n">
-        <v>136.194659089154</v>
+        <v>136.194659089155</v>
       </c>
       <c r="H57"/>
     </row>
@@ -58652,7 +58120,7 @@
         <v>64.3320141084303</v>
       </c>
       <c r="G59" t="n">
-        <v>145.705423416739</v>
+        <v>145.70542341674</v>
       </c>
       <c r="H59"/>
     </row>
@@ -58838,7 +58306,7 @@
         <v>68.0334355619786</v>
       </c>
       <c r="G67" t="n">
-        <v>196.43783233916</v>
+        <v>196.437832339159</v>
       </c>
       <c r="H67" t="n">
         <v>106.20586692832</v>
@@ -58934,7 +58402,7 @@
         <v>67.6288849284461</v>
       </c>
       <c r="G71" t="n">
-        <v>204.869973108076</v>
+        <v>204.869973108077</v>
       </c>
       <c r="H71" t="n">
         <v>109.319624191602</v>
@@ -59054,7 +58522,7 @@
         <v>70.4198048982248</v>
       </c>
       <c r="G76" t="n">
-        <v>172.0208728389</v>
+        <v>172.020872838901</v>
       </c>
       <c r="H76" t="n">
         <v>106.934509092741</v>
@@ -59150,7 +58618,7 @@
         <v>69.087512178922</v>
       </c>
       <c r="G80" t="n">
-        <v>164.88541255992</v>
+        <v>164.885412559921</v>
       </c>
       <c r="H80" t="n">
         <v>105.624912271454</v>
@@ -59472,7 +58940,7 @@
         <v>67.9809519255659</v>
       </c>
       <c r="G93" t="n">
-        <v>185.256429056007</v>
+        <v>185.256429056008</v>
       </c>
       <c r="H93" t="n">
         <v>106.119907422545</v>
@@ -59524,7 +58992,7 @@
         <v>67.6714224665581</v>
       </c>
       <c r="G95" t="n">
-        <v>191.17662977513</v>
+        <v>191.176629775129</v>
       </c>
       <c r="H95" t="n">
         <v>105.491528281118</v>
@@ -59576,7 +59044,7 @@
         <v>69.7466083213932</v>
       </c>
       <c r="G97" t="n">
-        <v>193.177983688479</v>
+        <v>193.17798368848</v>
       </c>
       <c r="H97" t="n">
         <v>106.874546828057</v>
@@ -59602,7 +59070,7 @@
         <v>67.0285185497215</v>
       </c>
       <c r="G98" t="n">
-        <v>222.184557813375</v>
+        <v>222.184557813376</v>
       </c>
       <c r="H98" t="n">
         <v>107.401438343919</v>
@@ -59654,7 +59122,7 @@
         <v>64.8226175155385</v>
       </c>
       <c r="G100" t="n">
-        <v>222.10383207341</v>
+        <v>222.103832073409</v>
       </c>
       <c r="H100" t="n">
         <v>106.795614657934</v>
@@ -60044,7 +59512,7 @@
         <v>74.6876220703125</v>
       </c>
       <c r="G115" t="n">
-        <v>241.144156052488</v>
+        <v>241.144156052487</v>
       </c>
       <c r="H115" t="n">
         <v>111.576261379766</v>
@@ -60070,7 +59538,7 @@
         <v>74.9036331176758</v>
       </c>
       <c r="G116" t="n">
-        <v>257.658953805693</v>
+        <v>257.658953805694</v>
       </c>
       <c r="H116" t="n">
         <v>111.548367314421</v>
@@ -60122,7 +59590,7 @@
         <v>76.31689453125</v>
       </c>
       <c r="G118" t="n">
-        <v>290.650216840126</v>
+        <v>290.650216840127</v>
       </c>
       <c r="H118" t="n">
         <v>113.563387284039</v>
@@ -60278,7 +59746,7 @@
         <v>76.7981872558594</v>
       </c>
       <c r="G124" t="n">
-        <v>331.994921930565</v>
+        <v>331.994921930566</v>
       </c>
       <c r="H124" t="n">
         <v>116.024452852191</v>
@@ -60486,7 +59954,7 @@
         <v>81.8722534179688</v>
       </c>
       <c r="G132" t="n">
-        <v>375.909668573678</v>
+        <v>375.909668573679</v>
       </c>
       <c r="H132" t="n">
         <v>120.388175772312</v>
@@ -60538,7 +60006,7 @@
         <v>85.1487045288086</v>
       </c>
       <c r="G134" t="n">
-        <v>416.822971947014</v>
+        <v>416.822971947013</v>
       </c>
       <c r="H134" t="n">
         <v>121.657971922287</v>
@@ -60590,7 +60058,7 @@
         <v>85.3585891723633</v>
       </c>
       <c r="G136" t="n">
-        <v>401.555039297703</v>
+        <v>401.555039297704</v>
       </c>
       <c r="H136" t="n">
         <v>122.296021073706</v>
@@ -60642,7 +60110,7 @@
         <v>84.9697418212891</v>
       </c>
       <c r="G138" t="n">
-        <v>429.272952936529</v>
+        <v>429.272952936528</v>
       </c>
       <c r="H138" t="n">
         <v>124.280013256051</v>
@@ -60668,7 +60136,7 @@
         <v>85.9269638061523</v>
       </c>
       <c r="G139" t="n">
-        <v>429.349191914501</v>
+        <v>429.3491919145</v>
       </c>
       <c r="H139" t="n">
         <v>124.325996860955</v>
@@ -60694,7 +60162,7 @@
         <v>84.5964660644531</v>
       </c>
       <c r="G140" t="n">
-        <v>445.882103839945</v>
+        <v>445.882103839944</v>
       </c>
       <c r="H140" t="n">
         <v>121.63060924901</v>
@@ -61006,7 +60474,7 @@
         <v>94.2794723510742</v>
       </c>
       <c r="G152" t="n">
-        <v>424.839914731363</v>
+        <v>424.839914731362</v>
       </c>
       <c r="H152" t="n">
         <v>132.443834089471</v>
@@ -61032,7 +60500,7 @@
         <v>94.6048202514648</v>
       </c>
       <c r="G153" t="n">
-        <v>408.999097033915</v>
+        <v>408.999097033916</v>
       </c>
       <c r="H153" t="n">
         <v>132.944471782329</v>
@@ -61084,7 +60552,7 @@
         <v>93.9198455810547</v>
       </c>
       <c r="G155" t="n">
-        <v>462.626076574791</v>
+        <v>462.626076574792</v>
       </c>
       <c r="H155" t="n">
         <v>134.025615658193</v>
@@ -61240,7 +60708,7 @@
         <v>96.0263595581055</v>
       </c>
       <c r="G161" t="n">
-        <v>519.001394057854</v>
+        <v>519.001394057856</v>
       </c>
       <c r="H161" t="n">
         <v>136.242781846702</v>
@@ -61344,7 +60812,7 @@
         <v>91.8904037475586</v>
       </c>
       <c r="G165" t="n">
-        <v>529.062783378813</v>
+        <v>529.062783378811</v>
       </c>
       <c r="H165" t="n">
         <v>135.260106820793</v>
@@ -61370,7 +60838,7 @@
         <v>92.642951965332</v>
       </c>
       <c r="G166" t="n">
-        <v>470.408608477343</v>
+        <v>470.408608477344</v>
       </c>
       <c r="H166" t="n">
         <v>135.561736859003</v>
@@ -61500,7 +60968,7 @@
         <v>87.3976287841797</v>
       </c>
       <c r="G171" t="n">
-        <v>206.821495823248</v>
+        <v>206.821495823247</v>
       </c>
       <c r="H171" t="n">
         <v>135.501948411566</v>
@@ -61552,7 +61020,7 @@
         <v>89.4139938354492</v>
       </c>
       <c r="G173" t="n">
-        <v>264.693635340251</v>
+        <v>264.693635340252</v>
       </c>
       <c r="H173" t="n">
         <v>136.249498135143</v>
@@ -61578,7 +61046,7 @@
         <v>89.8660736083984</v>
       </c>
       <c r="G174" t="n">
-        <v>305.69232782834</v>
+        <v>305.692327828341</v>
       </c>
       <c r="H174" t="n">
         <v>136.635084214866</v>
@@ -61682,7 +61150,7 @@
         <v>91.1535415649414</v>
       </c>
       <c r="G178" t="n">
-        <v>323.874381991398</v>
+        <v>323.874381991397</v>
       </c>
       <c r="H178" t="n">
         <v>138.120360710403</v>
@@ -61760,7 +61228,7 @@
         <v>94.0013046264648</v>
       </c>
       <c r="G181" t="n">
-        <v>348.027280885619</v>
+        <v>348.027280885618</v>
       </c>
       <c r="H181" t="n">
         <v>139.178524221502</v>
@@ -61812,7 +61280,7 @@
         <v>95.7192459106445</v>
       </c>
       <c r="G183" t="n">
-        <v>356.31614243135</v>
+        <v>356.316142431349</v>
       </c>
       <c r="H183" t="n">
         <v>140.866051858334</v>
@@ -61838,7 +61306,7 @@
         <v>96.9096527099609</v>
       </c>
       <c r="G184" t="n">
-        <v>378.150517662722</v>
+        <v>378.150517662723</v>
       </c>
       <c r="H184" t="n">
         <v>142.873393097315</v>
@@ -61890,7 +61358,7 @@
         <v>94.3085556030273</v>
       </c>
       <c r="G186" t="n">
-        <v>342.949516351264</v>
+        <v>342.949516351265</v>
       </c>
       <c r="H186" t="n">
         <v>143.480698514328</v>
@@ -62150,7 +61618,7 @@
         <v>100.17716217041</v>
       </c>
       <c r="G196" t="n">
-        <v>437.144781455405</v>
+        <v>437.144781455403</v>
       </c>
       <c r="H196" t="n">
         <v>150.792293794582</v>
@@ -62202,7 +61670,7 @@
         <v>99.6928482055664</v>
       </c>
       <c r="G198" t="n">
-        <v>413.009292743841</v>
+        <v>413.00929274384</v>
       </c>
       <c r="H198" t="n">
         <v>151.229669089538</v>
@@ -62228,7 +61696,7 @@
         <v>101.605499267578</v>
       </c>
       <c r="G199" t="n">
-        <v>387.341541075231</v>
+        <v>387.34154107523</v>
       </c>
       <c r="H199" t="n">
         <v>152.498486013199</v>
@@ -62280,7 +61748,7 @@
         <v>98.8581695556641</v>
       </c>
       <c r="G201" t="n">
-        <v>358.96215617611</v>
+        <v>358.962156176111</v>
       </c>
       <c r="H201" t="n">
         <v>153.984002084423</v>
@@ -62436,7 +61904,7 @@
         <v>99.8771591186523</v>
       </c>
       <c r="G207" t="n">
-        <v>449.505386792615</v>
+        <v>449.505386792614</v>
       </c>
       <c r="H207" t="n">
         <v>153.97204685395</v>
@@ -62462,7 +61930,7 @@
         <v>101.083480834961</v>
       </c>
       <c r="G208" t="n">
-        <v>467.889355408494</v>
+        <v>467.889355408493</v>
       </c>
       <c r="H208" t="n">
         <v>154.102923093776</v>
@@ -62514,7 +61982,7 @@
         <v>102.208679199219</v>
       </c>
       <c r="G210" t="n">
-        <v>418.020657323971</v>
+        <v>418.020657323972</v>
       </c>
       <c r="H210" t="n">
         <v>155.786532648632</v>
@@ -62670,7 +62138,7 @@
         <v>102.848419189453</v>
       </c>
       <c r="G216" t="n">
-        <v>418.738691000236</v>
+        <v>418.738691000235</v>
       </c>
       <c r="H216" t="n">
         <v>156.937372106745</v>
@@ -62748,7 +62216,7 @@
         <v>106.433670043945</v>
       </c>
       <c r="G219" t="n">
-        <v>430.719432270171</v>
+        <v>430.719432270169</v>
       </c>
       <c r="H219" t="n">
         <v>160.88138440259</v>
@@ -62826,7 +62294,7 @@
         <v>108.46216583252</v>
       </c>
       <c r="G222" t="n">
-        <v>431.856740480751</v>
+        <v>431.85674048075</v>
       </c>
       <c r="H222" t="n">
         <v>162.652388343826</v>
@@ -62904,7 +62372,7 @@
         <v>107.576789855957</v>
       </c>
       <c r="G225" t="n">
-        <v>410.628833999784</v>
+        <v>410.628833999783</v>
       </c>
       <c r="H225" t="n">
         <v>163.745163077314</v>
@@ -63060,7 +62528,7 @@
         <v>109.54354095459</v>
       </c>
       <c r="G231" t="n">
-        <v>406.211349515929</v>
+        <v>406.211349515931</v>
       </c>
       <c r="H231" t="n">
         <v>167.820878290679</v>
@@ -63086,7 +62554,7 @@
         <v>109.191749572754</v>
       </c>
       <c r="G232" t="n">
-        <v>400.511455824967</v>
+        <v>400.511455824969</v>
       </c>
       <c r="H232" t="n">
         <v>167.015338074884</v>
@@ -63112,7 +62580,7 @@
         <v>108.53564453125</v>
       </c>
       <c r="G233" t="n">
-        <v>404.660573204323</v>
+        <v>404.660573204325</v>
       </c>
       <c r="H233" t="n">
         <v>167.508033322205</v>
@@ -63164,7 +62632,7 @@
         <v>109.798309326172</v>
       </c>
       <c r="G235" t="n">
-        <v>415.117781462886</v>
+        <v>415.117781462887</v>
       </c>
       <c r="H235" t="n">
         <v>169.369132448735</v>
@@ -63190,7 +62658,7 @@
         <v>105.489685058594</v>
       </c>
       <c r="G236" t="n">
-        <v>402.300409612435</v>
+        <v>402.300409612433</v>
       </c>
       <c r="H236" t="n">
         <v>167.782143677691</v>
@@ -63268,7 +62736,7 @@
         <v>110.840049743652</v>
       </c>
       <c r="G239" t="n">
-        <v>358.237642938385</v>
+        <v>358.237642938384</v>
       </c>
       <c r="H239" t="n">
         <v>171.826771819594</v>
@@ -63476,7 +62944,7 @@
         <v>115.204376220703</v>
       </c>
       <c r="G247" t="n">
-        <v>260.955205132106</v>
+        <v>260.955205132105</v>
       </c>
       <c r="H247" t="n">
         <v>173.362484445503</v>
@@ -63632,7 +63100,7 @@
         <v>118.224243164062</v>
       </c>
       <c r="G253" t="n">
-        <v>165.973889681544</v>
+        <v>165.973889681545</v>
       </c>
       <c r="H253" t="n">
         <v>173.491174462718</v>
@@ -63788,7 +63256,7 @@
         <v>122.956680297852</v>
       </c>
       <c r="G259" t="n">
-        <v>216.218715144388</v>
+        <v>216.218715144387</v>
       </c>
       <c r="H259" t="n">
         <v>180.390932905564</v>
@@ -63840,7 +63308,7 @@
         <v>120.225364685059</v>
       </c>
       <c r="G261" t="n">
-        <v>194.98793606818</v>
+        <v>194.987936068181</v>
       </c>
       <c r="H261" t="n">
         <v>179.472202515644</v>
@@ -64516,7 +63984,7 @@
         <v>133.859741210938</v>
       </c>
       <c r="G287" t="n">
-        <v>292.747866117343</v>
+        <v>292.747866117342</v>
       </c>
       <c r="H287" t="n">
         <v>197.637650406867</v>
@@ -64594,7 +64062,7 @@
         <v>135.845260620117</v>
       </c>
       <c r="G290" t="n">
-        <v>215.962318794469</v>
+        <v>215.962318794468</v>
       </c>
       <c r="H290" t="n">
         <v>200.636449909271</v>
@@ -64698,7 +64166,7 @@
         <v>138.851989746094</v>
       </c>
       <c r="G294" t="n">
-        <v>245.16660680623</v>
+        <v>245.166606806231</v>
       </c>
       <c r="H294" t="n">
         <v>199.75813474939</v>
@@ -64750,7 +64218,7 @@
         <v>139.371200561523</v>
       </c>
       <c r="G296" t="n">
-        <v>230.095957497607</v>
+        <v>230.095957497606</v>
       </c>
       <c r="H296" t="n">
         <v>203.53881769442</v>
@@ -64776,7 +64244,7 @@
         <v>136.012954711914</v>
       </c>
       <c r="G297" t="n">
-        <v>217.35324470722</v>
+        <v>217.353244707219</v>
       </c>
       <c r="H297" t="n">
         <v>201.698826782463</v>
@@ -64984,7 +64452,7 @@
         <v>110.917060852051</v>
       </c>
       <c r="G305" t="n">
-        <v>67.0818449689149</v>
+        <v>67.0818449689151</v>
       </c>
       <c r="H305" t="n">
         <v>167.563490714004</v>
@@ -65140,7 +64608,7 @@
         <v>133.437698364258</v>
       </c>
       <c r="G311" t="n">
-        <v>151.972210844884</v>
+        <v>151.972210844883</v>
       </c>
       <c r="H311" t="n">
         <v>197.589930631163</v>
@@ -65166,7 +64634,7 @@
         <v>143.751281738281</v>
       </c>
       <c r="G312" t="n">
-        <v>156.571470290939</v>
+        <v>156.571470290938</v>
       </c>
       <c r="H312" t="n">
         <v>204.373192949731</v>
@@ -65296,7 +64764,7 @@
         <v>158.720367431641</v>
       </c>
       <c r="G317" t="n">
-        <v>227.867564846153</v>
+        <v>227.867564846154</v>
       </c>
       <c r="H317" t="n">
         <v>211.046930401826</v>
@@ -65400,7 +64868,7 @@
         <v>168.009979248047</v>
       </c>
       <c r="G321" t="n">
-        <v>243.227742428768</v>
+        <v>243.227742428767</v>
       </c>
       <c r="H321" t="n">
         <v>214.251548690107</v>
@@ -65582,7 +65050,7 @@
         <v>174.161117553711</v>
       </c>
       <c r="G328" t="n">
-        <v>384.482709455254</v>
+        <v>384.482709455253</v>
       </c>
       <c r="H328" t="n">
         <v>223.030302233428</v>
@@ -65764,7 +65232,7 @@
         <v>177.934204101562</v>
       </c>
       <c r="G335" t="n">
-        <v>328.35539195552</v>
+        <v>328.355391955521</v>
       </c>
       <c r="H335" t="n">
         <v>229.89384726212</v>
@@ -65842,7 +65310,7 @@
         <v>173.863494873047</v>
       </c>
       <c r="G338" t="n">
-        <v>280.020759305536</v>
+        <v>280.020759305535</v>
       </c>
       <c r="H338" t="n">
         <v>231.746794904534</v>
@@ -65946,7 +65414,7 @@
         <v>177.636566162109</v>
       </c>
       <c r="G342" t="n">
-        <v>270.028504456526</v>
+        <v>270.028504456527</v>
       </c>
       <c r="H342" t="n">
         <v>235.071258542857</v>
@@ -65972,7 +65440,7 @@
         <v>175.036041259766</v>
       </c>
       <c r="G343" t="n">
-        <v>272.109380371227</v>
+        <v>272.109380371226</v>
       </c>
       <c r="H343" t="n">
         <v>235.050102129588</v>
@@ -66024,7 +65492,7 @@
         <v>180.442352294922</v>
       </c>
       <c r="G345" t="n">
-        <v>311.999891259368</v>
+        <v>311.999891259367</v>
       </c>
       <c r="H345" t="n">
         <v>235.961512097277</v>
@@ -66284,7 +65752,7 @@
         <v>177.94775390625</v>
       </c>
       <c r="G355" t="n">
-        <v>297.666770239201</v>
+        <v>297.6667702392</v>
       </c>
       <c r="H355" t="n">
         <v>230.908282194142</v>
@@ -66414,7 +65882,7 @@
         <v>177.879852294922</v>
       </c>
       <c r="G360" t="n">
-        <v>257.155637517415</v>
+        <v>257.155637517414</v>
       </c>
       <c r="H360" t="n">
         <v>230.831534725482</v>
@@ -66466,7 +65934,7 @@
         <v>178.046020507812</v>
       </c>
       <c r="G362" t="n">
-        <v>263.884633407971</v>
+        <v>263.884633407972</v>
       </c>
       <c r="H362" t="n">
         <v>233.713916142526</v>
@@ -66564,7 +66032,7 @@
         <v>181.141464233398</v>
       </c>
       <c r="G366" t="n">
-        <v>215.451922549565</v>
+        <v>215.451922549564</v>
       </c>
       <c r="H366" t="n">
         <v>237.7994804017</v>
@@ -66743,118 +66211,36 @@
         <v>46023</v>
       </c>
       <c r="B374"/>
-      <c r="C374" t="n">
-        <v>101.4454</v>
-      </c>
-      <c r="D374" t="n">
-        <v>131.9332</v>
-      </c>
-      <c r="E374" t="n">
-        <v>190.224792480469</v>
-      </c>
-      <c r="F374" t="n">
-        <v>190.224792480469</v>
-      </c>
-      <c r="G374" t="n">
-        <v>183.62362029226</v>
-      </c>
-      <c r="H374" t="n">
-        <v>243.663461137109</v>
-      </c>
+      <c r="C374"/>
+      <c r="D374"/>
+      <c r="E374"/>
+      <c r="F374"/>
+      <c r="G374"/>
+      <c r="H374"/>
     </row>
     <row r="375">
       <c r="A375" s="1" t="n">
         <v>46054</v>
       </c>
       <c r="B375"/>
-      <c r="C375" t="n">
-        <v>101.0048</v>
-      </c>
-      <c r="D375" t="n">
-        <v>131.8368</v>
-      </c>
-      <c r="E375" t="n">
-        <v>190.592468261719</v>
-      </c>
-      <c r="F375" t="n">
-        <v>190.592468261719</v>
-      </c>
-      <c r="G375" t="n">
-        <v>193.378794762268</v>
-      </c>
-      <c r="H375" t="n">
-        <v>243.814532483014</v>
-      </c>
+      <c r="C375"/>
+      <c r="D375"/>
+      <c r="E375"/>
+      <c r="F375"/>
+      <c r="G375"/>
+      <c r="H375"/>
     </row>
     <row r="376">
       <c r="A376" s="1" t="n">
         <v>46082</v>
       </c>
       <c r="B376"/>
-      <c r="C376" t="n">
-        <v>99.12529</v>
-      </c>
-      <c r="D376" t="n">
-        <v>115.1959</v>
-      </c>
-      <c r="E376" t="n">
-        <v>169.402206420898</v>
-      </c>
-      <c r="F376" t="n">
-        <v>169.402206420898</v>
-      </c>
-      <c r="G376" t="n">
-        <v>274.027774258465</v>
-      </c>
-      <c r="H376" t="n">
-        <v>229.329511108198</v>
-      </c>
-    </row>
-    <row r="377">
-      <c r="A377" s="1" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B377"/>
-      <c r="C377" t="n">
-        <v>98.68008</v>
-      </c>
-      <c r="D377" t="n">
-        <v>128.9337</v>
-      </c>
-      <c r="E377"/>
-      <c r="F377"/>
-      <c r="G377" t="n">
-        <v>287.80193070092</v>
-      </c>
-      <c r="H377" t="n">
-        <v>237.589960098316</v>
-      </c>
-    </row>
-    <row r="378">
-      <c r="A378" s="1" t="n">
-        <v>46143</v>
-      </c>
-      <c r="B378"/>
-      <c r="C378"/>
-      <c r="D378"/>
-      <c r="E378"/>
-      <c r="F378"/>
-      <c r="G378"/>
-      <c r="H378" t="n">
-        <v>240.177314763786</v>
-      </c>
-    </row>
-    <row r="379">
-      <c r="A379" s="1" t="n">
-        <v>46174</v>
-      </c>
-      <c r="B379"/>
-      <c r="C379"/>
-      <c r="D379"/>
-      <c r="E379"/>
-      <c r="F379"/>
-      <c r="G379"/>
-      <c r="H379"/>
+      <c r="C376"/>
+      <c r="D376"/>
+      <c r="E376"/>
+      <c r="F376"/>
+      <c r="G376"/>
+      <c r="H376"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -73107,97 +72493,31 @@
       <c r="A374" s="1" t="n">
         <v>46023</v>
       </c>
-      <c r="B374" t="n">
-        <v>11259.0451294922</v>
-      </c>
-      <c r="C374" t="n">
-        <v>4390.89990234375</v>
-      </c>
-      <c r="D374" t="n">
-        <v>0.0292618356943701</v>
-      </c>
-      <c r="E374" t="n">
-        <v>0.81520341629167</v>
-      </c>
-      <c r="F374" t="n">
-        <v>0.791349067866654</v>
-      </c>
+      <c r="B374"/>
+      <c r="C374"/>
+      <c r="D374"/>
+      <c r="E374"/>
+      <c r="F374"/>
     </row>
     <row r="375">
       <c r="A375" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="B375" t="n">
-        <v>11391.0915647095</v>
-      </c>
-      <c r="C375" t="n">
-        <v>4387.2998046875</v>
-      </c>
-      <c r="D375" t="n">
-        <v>0.0233371899427152</v>
-      </c>
-      <c r="E375" t="n">
-        <v>0.812104684205702</v>
-      </c>
-      <c r="F375" t="n">
-        <v>0.793152442937024</v>
-      </c>
+      <c r="B375"/>
+      <c r="C375"/>
+      <c r="D375"/>
+      <c r="E375"/>
+      <c r="F375"/>
     </row>
     <row r="376">
       <c r="A376" s="1" t="n">
         <v>46082</v>
       </c>
-      <c r="B376" t="n">
-        <v>11832.5404129962</v>
-      </c>
-      <c r="C376" t="n">
-        <v>4045.69995117188</v>
-      </c>
-      <c r="D376" t="n">
-        <v>0.0250989259468626</v>
-      </c>
-      <c r="E376" t="n">
-        <v>0.81094709819382</v>
-      </c>
-      <c r="F376" t="n">
-        <v>0.790593197029431</v>
-      </c>
-    </row>
-    <row r="377">
-      <c r="A377" s="1" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B377" t="n">
-        <v>0</v>
-      </c>
-      <c r="C377" t="n">
-        <v>0</v>
-      </c>
-      <c r="D377"/>
-      <c r="E377"/>
-      <c r="F377"/>
-    </row>
-    <row r="378">
-      <c r="A378" s="1" t="n">
-        <v>46143</v>
-      </c>
-      <c r="B378" t="n">
-        <v>0</v>
-      </c>
-      <c r="C378"/>
-      <c r="D378"/>
-      <c r="E378"/>
-      <c r="F378"/>
-    </row>
-    <row r="379">
-      <c r="A379" s="1" t="n">
-        <v>46174</v>
-      </c>
-      <c r="B379"/>
-      <c r="C379"/>
-      <c r="D379"/>
-      <c r="E379"/>
-      <c r="F379"/>
+      <c r="B376"/>
+      <c r="C376"/>
+      <c r="D376"/>
+      <c r="E376"/>
+      <c r="F376"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -79572,78 +78892,19 @@
       <c r="A375" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="B375" t="n">
-        <v>4153.8735</v>
-      </c>
-      <c r="C375" t="n">
-        <v>4123.553</v>
-      </c>
-      <c r="D375" t="n">
-        <v>22892.9231578947</v>
-      </c>
-      <c r="E375" t="n">
-        <v>6893.80631578947</v>
-      </c>
+      <c r="B375"/>
+      <c r="C375"/>
+      <c r="D375"/>
+      <c r="E375"/>
     </row>
     <row r="376">
       <c r="A376" s="1" t="n">
         <v>46082</v>
       </c>
-      <c r="B376" t="n">
-        <v>4232.50052631579</v>
-      </c>
-      <c r="C376" t="n">
-        <v>4173.91842105263</v>
-      </c>
-      <c r="D376" t="n">
-        <v>22130.0377272727</v>
-      </c>
-      <c r="E376" t="n">
-        <v>6654.41909090909</v>
-      </c>
-    </row>
-    <row r="377">
-      <c r="A377" s="1" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B377" t="n">
-        <v>4378.935625</v>
-      </c>
-      <c r="C377" t="n">
-        <v>4290.18125</v>
-      </c>
-      <c r="D377" t="n">
-        <v>23677.0528571429</v>
-      </c>
-      <c r="E377" t="n">
-        <v>6957.00761904762</v>
-      </c>
-    </row>
-    <row r="378">
-      <c r="A378" s="1" t="n">
-        <v>46143</v>
-      </c>
-      <c r="B378" t="n">
-        <v>4481.98222222222</v>
-      </c>
-      <c r="C378" t="n">
-        <v>4404.32411764706</v>
-      </c>
-      <c r="D378" t="n">
-        <v>25991.6</v>
-      </c>
-      <c r="E378" t="n">
-        <v>7379.95333333333</v>
-      </c>
-    </row>
-    <row r="379">
-      <c r="A379" s="1" t="n">
-        <v>46174</v>
-      </c>
-      <c r="B379"/>
-      <c r="C379"/>
-      <c r="D379"/>
-      <c r="E379"/>
+      <c r="B376"/>
+      <c r="C376"/>
+      <c r="D376"/>
+      <c r="E376"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -79679,7 +78940,7 @@
         <v>3.01171428571429</v>
       </c>
       <c r="D2" t="n">
-        <v>48897.0597168861</v>
+        <v>48897.0597168862</v>
       </c>
     </row>
     <row r="3">
@@ -79727,7 +78988,7 @@
         <v>3.0042380952381</v>
       </c>
       <c r="D6" t="n">
-        <v>60960.8788644685</v>
+        <v>60960.8788644686</v>
       </c>
     </row>
     <row r="7">
@@ -79751,7 +79012,7 @@
         <v>2.95528571428571</v>
       </c>
       <c r="D8" t="n">
-        <v>55448.8165973634</v>
+        <v>55448.8165973633</v>
       </c>
     </row>
     <row r="9">
@@ -79763,7 +79024,7 @@
         <v>3.03078260869565</v>
       </c>
       <c r="D9" t="n">
-        <v>51214.4309267803</v>
+        <v>51214.4309267802</v>
       </c>
     </row>
     <row r="10">
@@ -79835,7 +79096,7 @@
         <v>3.11314285714286</v>
       </c>
       <c r="D15" t="n">
-        <v>60252.7687014487</v>
+        <v>60252.7687014488</v>
       </c>
     </row>
     <row r="16">
@@ -79907,7 +79168,7 @@
         <v>3.14613636363636</v>
       </c>
       <c r="D21" t="n">
-        <v>55406.9160788428</v>
+        <v>55406.9160788427</v>
       </c>
     </row>
     <row r="22">
@@ -79919,7 +79180,7 @@
         <v>3.16689473684211</v>
       </c>
       <c r="D22" t="n">
-        <v>59632.3199706047</v>
+        <v>59632.3199706048</v>
       </c>
     </row>
     <row r="23">
@@ -79955,7 +79216,7 @@
         <v>3.27647368421053</v>
       </c>
       <c r="D25" t="n">
-        <v>67385.97174369</v>
+        <v>67385.9717436901</v>
       </c>
     </row>
     <row r="26">
@@ -79967,7 +79228,7 @@
         <v>3.27613636363636</v>
       </c>
       <c r="D26" t="n">
-        <v>74772.3862858126</v>
+        <v>74772.3862858125</v>
       </c>
     </row>
     <row r="27">
@@ -79991,7 +79252,7 @@
         <v>3.36655555555556</v>
       </c>
       <c r="D28" t="n">
-        <v>90507.1047193996</v>
+        <v>90507.1047193997</v>
       </c>
     </row>
     <row r="29">
@@ -80539,7 +79800,7 @@
         <v>4.1052380952381</v>
       </c>
       <c r="D71" t="n">
-        <v>135910.824427753</v>
+        <v>135910.824427754</v>
       </c>
     </row>
     <row r="72">
@@ -80693,7 +79954,7 @@
         <v>4.32246666666667</v>
       </c>
       <c r="D82" t="n">
-        <v>157574.65046252</v>
+        <v>157574.650462521</v>
       </c>
     </row>
     <row r="83">
@@ -80721,7 +79982,7 @@
         <v>4.23886363636364</v>
       </c>
       <c r="D84" t="n">
-        <v>146899.71752521</v>
+        <v>146899.717525211</v>
       </c>
     </row>
     <row r="85">
@@ -80833,7 +80094,7 @@
         <v>4.72095454545455</v>
       </c>
       <c r="D92" t="n">
-        <v>164990.753627147</v>
+        <v>164990.753627148</v>
       </c>
     </row>
     <row r="93">
@@ -81001,7 +80262,7 @@
         <v>4.37095652173913</v>
       </c>
       <c r="D104" t="n">
-        <v>150976.164676932</v>
+        <v>150976.164676931</v>
       </c>
     </row>
     <row r="105">
@@ -81029,7 +80290,7 @@
         <v>4.46485714285714</v>
       </c>
       <c r="D106" t="n">
-        <v>160112.960043881</v>
+        <v>160112.96004388</v>
       </c>
     </row>
     <row r="107">
@@ -81043,7 +80304,7 @@
         <v>4.448</v>
       </c>
       <c r="D107" t="n">
-        <v>157381.512227711</v>
+        <v>157381.51222771</v>
       </c>
     </row>
     <row r="108">
@@ -81169,7 +80430,7 @@
         <v>4.4912380952381</v>
       </c>
       <c r="D116" t="n">
-        <v>166361.313646571</v>
+        <v>166361.313646572</v>
       </c>
     </row>
     <row r="117">
@@ -81505,7 +80766,7 @@
         <v>4.43280952380952</v>
       </c>
       <c r="D140" t="n">
-        <v>168601.790933211</v>
+        <v>168601.79093321</v>
       </c>
     </row>
     <row r="141">
@@ -81561,7 +80822,7 @@
         <v>4.30090476190476</v>
       </c>
       <c r="D144" t="n">
-        <v>169523.943055479</v>
+        <v>169523.943055478</v>
       </c>
     </row>
     <row r="145">
@@ -81715,7 +80976,7 @@
         <v>4.01386363636364</v>
       </c>
       <c r="D155" t="n">
-        <v>155423.645749609</v>
+        <v>155423.64574961</v>
       </c>
     </row>
     <row r="156">
@@ -81925,7 +81186,7 @@
         <v>3.91333333333333</v>
       </c>
       <c r="D170" t="n">
-        <v>211378.503161843</v>
+        <v>211378.503161842</v>
       </c>
     </row>
     <row r="171">
@@ -82107,7 +81368,7 @@
         <v>3.74655</v>
       </c>
       <c r="D183" t="n">
-        <v>283275.649332662</v>
+        <v>283275.649332661</v>
       </c>
     </row>
     <row r="184">
@@ -82289,7 +81550,7 @@
         <v>3.56272727272727</v>
       </c>
       <c r="D196" t="n">
-        <v>316740.328683286</v>
+        <v>316740.328683285</v>
       </c>
     </row>
     <row r="197">
@@ -82401,7 +81662,7 @@
         <v>3.72545454545455</v>
       </c>
       <c r="D204" t="n">
-        <v>329180.776617796</v>
+        <v>329180.776617797</v>
       </c>
     </row>
     <row r="205">
@@ -82443,7 +81704,7 @@
         <v>3.74080952380952</v>
       </c>
       <c r="D207" t="n">
-        <v>339096.306159305</v>
+        <v>339096.306159304</v>
       </c>
     </row>
     <row r="208">
@@ -82457,7 +81718,7 @@
         <v>3.7632</v>
       </c>
       <c r="D208" t="n">
-        <v>339364.444574928</v>
+        <v>339364.444574927</v>
       </c>
     </row>
     <row r="209">
@@ -82499,7 +81760,7 @@
         <v>3.89276190476191</v>
       </c>
       <c r="D211" t="n">
-        <v>340526.763111631</v>
+        <v>340526.763111632</v>
       </c>
     </row>
     <row r="212">
@@ -82765,7 +82026,7 @@
         <v>3.49336363636364</v>
       </c>
       <c r="D230" t="n">
-        <v>332032.633630418</v>
+        <v>332032.633630419</v>
       </c>
     </row>
     <row r="231">
@@ -82849,7 +82110,7 @@
         <v>3.42152173913043</v>
       </c>
       <c r="D236" t="n">
-        <v>338416.952185358</v>
+        <v>338416.952185357</v>
       </c>
     </row>
     <row r="237">
@@ -82905,7 +82166,7 @@
         <v>3.829</v>
       </c>
       <c r="D240" t="n">
-        <v>376294.794865855</v>
+        <v>376294.794865856</v>
       </c>
     </row>
     <row r="241">
@@ -83031,7 +82292,7 @@
         <v>3.84485714285714</v>
       </c>
       <c r="D249" t="n">
-        <v>390315.285971506</v>
+        <v>390315.285971505</v>
       </c>
     </row>
     <row r="250">
@@ -83115,7 +82376,7 @@
         <v>3.90804761904762</v>
       </c>
       <c r="D255" t="n">
-        <v>410528.875202698</v>
+        <v>410528.875202699</v>
       </c>
     </row>
     <row r="256">
@@ -83171,7 +82432,7 @@
         <v>3.85663636363636</v>
       </c>
       <c r="D259" t="n">
-        <v>428535.593914487</v>
+        <v>428535.593914486</v>
       </c>
     </row>
     <row r="260">
@@ -83185,7 +82446,7 @@
         <v>3.85742857142857</v>
       </c>
       <c r="D260" t="n">
-        <v>430248.834550396</v>
+        <v>430248.834550395</v>
       </c>
     </row>
     <row r="261">
@@ -83199,7 +82460,7 @@
         <v>3.79539130434783</v>
       </c>
       <c r="D261" t="n">
-        <v>425627.042406776</v>
+        <v>425627.042406777</v>
       </c>
     </row>
     <row r="262">
@@ -83213,7 +82474,7 @@
         <v>3.76572727272727</v>
       </c>
       <c r="D262" t="n">
-        <v>426201.957412054</v>
+        <v>426201.957412053</v>
       </c>
     </row>
     <row r="263">
@@ -83227,7 +82488,7 @@
         <v>3.82173333333333</v>
       </c>
       <c r="D263" t="n">
-        <v>429626.255853898</v>
+        <v>429626.255853897</v>
       </c>
     </row>
     <row r="264">
@@ -83241,7 +82502,7 @@
         <v>3.84286363636364</v>
       </c>
       <c r="D264" t="n">
-        <v>430047.458197768</v>
+        <v>430047.458197769</v>
       </c>
     </row>
     <row r="265">
@@ -83255,7 +82516,7 @@
         <v>3.82838095238095</v>
       </c>
       <c r="D265" t="n">
-        <v>434250.354217066</v>
+        <v>434250.354217065</v>
       </c>
     </row>
     <row r="266">
@@ -83325,7 +82586,7 @@
         <v>3.59742105263158</v>
       </c>
       <c r="D270" t="n">
-        <v>441931.713397877</v>
+        <v>441931.713397878</v>
       </c>
     </row>
     <row r="271">
@@ -83381,7 +82642,7 @@
         <v>3.53735294117647</v>
       </c>
       <c r="D274" t="n">
-        <v>451255.473637515</v>
+        <v>451255.473637514</v>
       </c>
     </row>
     <row r="275">
@@ -83437,7 +82698,7 @@
         <v>3.42322727272727</v>
       </c>
       <c r="D278" t="n">
-        <v>464388.389663389</v>
+        <v>464388.389663388</v>
       </c>
     </row>
     <row r="279">
@@ -83451,7 +82712,7 @@
         <v>3.4791</v>
       </c>
       <c r="D279" t="n">
-        <v>466168.618399343</v>
+        <v>466168.618399342</v>
       </c>
     </row>
     <row r="280">
@@ -83465,7 +82726,7 @@
         <v>3.47515384615385</v>
       </c>
       <c r="D280" t="n">
-        <v>463584.447505786</v>
+        <v>463584.447505787</v>
       </c>
     </row>
     <row r="281">
@@ -83493,7 +82754,7 @@
         <v>3.59104545454545</v>
       </c>
       <c r="D282" t="n">
-        <v>468949.801130137</v>
+        <v>468949.801130136</v>
       </c>
     </row>
     <row r="283">
@@ -83549,7 +82810,7 @@
         <v>3.59253333333333</v>
       </c>
       <c r="D286" t="n">
-        <v>470848.664234666</v>
+        <v>470848.664234665</v>
       </c>
     </row>
     <row r="287">
@@ -83577,7 +82838,7 @@
         <v>3.70545454545455</v>
       </c>
       <c r="D288" t="n">
-        <v>483957.547920097</v>
+        <v>483957.547920098</v>
       </c>
     </row>
     <row r="289">
@@ -83605,7 +82866,7 @@
         <v>3.68704545454545</v>
       </c>
       <c r="D290" t="n">
-        <v>496466.949161156</v>
+        <v>496466.949161155</v>
       </c>
     </row>
     <row r="291">
@@ -83633,7 +82894,7 @@
         <v>3.61863157894737</v>
       </c>
       <c r="D292" t="n">
-        <v>484622.255100765</v>
+        <v>484622.255100766</v>
       </c>
     </row>
     <row r="293">
@@ -83661,7 +82922,7 @@
         <v>3.5932380952381</v>
       </c>
       <c r="D294" t="n">
-        <v>476106.775399862</v>
+        <v>476106.775399863</v>
       </c>
     </row>
     <row r="295">
@@ -83703,7 +82964,7 @@
         <v>3.51122727272727</v>
       </c>
       <c r="D297" t="n">
-        <v>475159.109424955</v>
+        <v>475159.109424954</v>
       </c>
     </row>
     <row r="298">
@@ -83717,7 +82978,7 @@
         <v>3.52405263157895</v>
       </c>
       <c r="D298" t="n">
-        <v>476472.957285468</v>
+        <v>476472.957285469</v>
       </c>
     </row>
     <row r="299">
@@ -83801,7 +83062,7 @@
         <v>3.61789473684211</v>
       </c>
       <c r="D304" t="n">
-        <v>516172.387258474</v>
+        <v>516172.387258475</v>
       </c>
     </row>
     <row r="305">
@@ -83843,7 +83104,7 @@
         <v>3.45831818181818</v>
       </c>
       <c r="D307" t="n">
-        <v>581270.048262609</v>
+        <v>581270.048262608</v>
       </c>
     </row>
     <row r="308">
@@ -83871,7 +83132,7 @@
         <v>3.40090476190476</v>
       </c>
       <c r="D309" t="n">
-        <v>626045.231958415</v>
+        <v>626045.231958414</v>
       </c>
     </row>
     <row r="310">
@@ -83899,7 +83160,7 @@
         <v>3.39504545454545</v>
       </c>
       <c r="D311" t="n">
-        <v>620095.576231558</v>
+        <v>620095.576231557</v>
       </c>
     </row>
     <row r="312">
@@ -83913,7 +83174,7 @@
         <v>3.35938095238095</v>
       </c>
       <c r="D312" t="n">
-        <v>638515.328631112</v>
+        <v>638515.328631111</v>
       </c>
     </row>
     <row r="313">
@@ -83941,7 +83202,7 @@
         <v>3.2221</v>
       </c>
       <c r="D314" t="n">
-        <v>659797.96304969</v>
+        <v>659797.963049691</v>
       </c>
     </row>
     <row r="315">
@@ -83955,7 +83216,7 @@
         <v>3.26973684210526</v>
       </c>
       <c r="D315" t="n">
-        <v>688198.728747345</v>
+        <v>688198.728747344</v>
       </c>
     </row>
     <row r="316">
@@ -83997,7 +83258,7 @@
         <v>3.26226315789474</v>
       </c>
       <c r="D318" t="n">
-        <v>726510.662280606</v>
+        <v>726510.662280607</v>
       </c>
     </row>
     <row r="319">
@@ -84011,7 +83272,7 @@
         <v>3.25172727272727</v>
       </c>
       <c r="D319" t="n">
-        <v>730106.537437314</v>
+        <v>730106.537437313</v>
       </c>
     </row>
     <row r="320">
@@ -84249,7 +83510,7 @@
         <v>3.47957142857143</v>
       </c>
       <c r="D336" t="n">
-        <v>714407.55818467</v>
+        <v>714407.558184671</v>
       </c>
     </row>
     <row r="337">
@@ -84277,7 +83538,7 @@
         <v>3.44528571428571</v>
       </c>
       <c r="D338" t="n">
-        <v>726971.535551199</v>
+        <v>726971.535551198</v>
       </c>
     </row>
     <row r="339">
@@ -84305,7 +83566,7 @@
         <v>3.61995238095238</v>
       </c>
       <c r="D340" t="n">
-        <v>755285.266191809</v>
+        <v>755285.266191808</v>
       </c>
     </row>
     <row r="341">
@@ -84347,7 +83608,7 @@
         <v>3.64463636363636</v>
       </c>
       <c r="D343" t="n">
-        <v>758359.131196613</v>
+        <v>758359.131196612</v>
       </c>
     </row>
     <row r="344">
@@ -84375,7 +83636,7 @@
         <v>3.74575862068965</v>
       </c>
       <c r="D345" t="n">
-        <v>777219.258548574</v>
+        <v>777219.258548572</v>
       </c>
     </row>
     <row r="346">
@@ -84403,7 +83664,7 @@
         <v>3.97827272727273</v>
       </c>
       <c r="D347" t="n">
-        <v>775222.645586667</v>
+        <v>775222.645586668</v>
       </c>
     </row>
     <row r="348">
@@ -84487,7 +83748,7 @@
         <v>3.74331578947368</v>
       </c>
       <c r="D353" t="n">
-        <v>782660.43474021</v>
+        <v>782660.434740209</v>
       </c>
     </row>
     <row r="354">
@@ -84515,7 +83776,7 @@
         <v>3.72473684210526</v>
       </c>
       <c r="D355" t="n">
-        <v>784700.819419682</v>
+        <v>784700.819419681</v>
       </c>
     </row>
     <row r="356">
@@ -84529,7 +83790,7 @@
         <v>3.6814347826087</v>
       </c>
       <c r="D356" t="n">
-        <v>783562.69629524</v>
+        <v>783562.696295241</v>
       </c>
     </row>
     <row r="357">
@@ -84543,7 +83804,7 @@
         <v>3.73176190476191</v>
       </c>
       <c r="D357" t="n">
-        <v>800788.757895909</v>
+        <v>800788.75789591</v>
       </c>
     </row>
     <row r="358">
@@ -84571,7 +83832,7 @@
         <v>3.75158823529412</v>
       </c>
       <c r="D359" t="n">
-        <v>797990.400989339</v>
+        <v>797990.40098934</v>
       </c>
     </row>
     <row r="360">
@@ -84585,7 +83846,7 @@
         <v>3.71880952380952</v>
       </c>
       <c r="D360" t="n">
-        <v>797699.682587047</v>
+        <v>797699.682587046</v>
       </c>
     </row>
     <row r="361">
@@ -84599,7 +83860,7 @@
         <v>3.61766666666667</v>
       </c>
       <c r="D361" t="n">
-        <v>769081.912192987</v>
+        <v>769081.912192988</v>
       </c>
     </row>
     <row r="362">
@@ -84613,7 +83874,7 @@
         <v>3.61527272727273</v>
       </c>
       <c r="D362" t="n">
-        <v>769602.162750309</v>
+        <v>769602.16275031</v>
       </c>
     </row>
     <row r="363">
@@ -84655,7 +83916,7 @@
         <v>3.68778947368421</v>
       </c>
       <c r="D365" t="n">
-        <v>777937.579866252</v>
+        <v>777937.579866251</v>
       </c>
     </row>
     <row r="366">
@@ -84711,7 +83972,7 @@
         <v>3.3957619047619</v>
       </c>
       <c r="D369" t="n">
-        <v>735511.600127959</v>
+        <v>735511.600127958</v>
       </c>
     </row>
     <row r="370">
@@ -84767,7 +84028,7 @@
         <v>3.21514285714286</v>
       </c>
       <c r="D373" t="n">
-        <v>697754.275234418</v>
+        <v>697754.275234419</v>
       </c>
     </row>
     <row r="374">
@@ -84780,69 +84041,23 @@
       <c r="C374" t="n">
         <v>3.14557142857143</v>
       </c>
-      <c r="D374" t="n">
-        <v>695375.306320011</v>
-      </c>
+      <c r="D374"/>
     </row>
     <row r="375">
       <c r="A375" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="B375" t="n">
-        <v>77.28355225601</v>
-      </c>
-      <c r="C375" t="n">
-        <v>3.10265</v>
-      </c>
-      <c r="D375" t="n">
-        <v>689204.984396135</v>
-      </c>
+      <c r="B375"/>
+      <c r="C375"/>
+      <c r="D375"/>
     </row>
     <row r="376">
       <c r="A376" s="1" t="n">
         <v>46082</v>
       </c>
-      <c r="B376" t="n">
-        <v>76.9850344553139</v>
-      </c>
-      <c r="C376" t="n">
-        <v>3.1156</v>
-      </c>
-      <c r="D376" t="n">
-        <v>674232.032723773</v>
-      </c>
-    </row>
-    <row r="377">
-      <c r="A377" s="1" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B377"/>
-      <c r="C377" t="n">
-        <v>3.01525</v>
-      </c>
-      <c r="D377" t="n">
-        <v>663096.795908659</v>
-      </c>
-    </row>
-    <row r="378">
-      <c r="A378" s="1" t="n">
-        <v>46143</v>
-      </c>
-      <c r="B378" t="n">
-        <v>77.9850344553139</v>
-      </c>
-      <c r="C378" t="n">
-        <v>2.914375</v>
-      </c>
-      <c r="D378"/>
-    </row>
-    <row r="379">
-      <c r="A379" s="1" t="n">
-        <v>46174</v>
-      </c>
-      <c r="B379"/>
-      <c r="C379"/>
-      <c r="D379"/>
+      <c r="B376"/>
+      <c r="C376"/>
+      <c r="D376"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
